--- a/biodym_mfa_tool/studies/case_study_bachelor_thesis/results/Case_study_results_MC_mean.xlsx
+++ b/biodym_mfa_tool/studies/case_study_bachelor_thesis/results/Case_study_results_MC_mean.xlsx
@@ -630,88 +630,88 @@
         <v>2020</v>
       </c>
       <c r="B2">
-        <v>100.6403865688288</v>
+        <v>101.1611302294817</v>
       </c>
       <c r="C2">
-        <v>4.056962783841528</v>
+        <v>5.683869009590482</v>
       </c>
       <c r="D2">
-        <v>50.0336253681736</v>
+        <v>50.44158908528594</v>
       </c>
       <c r="E2">
-        <v>2.584793726329579</v>
+        <v>3.172779106219868</v>
       </c>
       <c r="F2">
-        <v>50.60676120065523</v>
+        <v>50.71954114419577</v>
       </c>
       <c r="G2">
-        <v>2.662599466909347</v>
+        <v>3.417907390598832</v>
       </c>
       <c r="H2">
-        <v>15.08489566962486</v>
+        <v>15.19821828270453</v>
       </c>
       <c r="I2">
-        <v>0.8885442635143215</v>
+        <v>1.117649054432708</v>
       </c>
       <c r="J2">
-        <v>15.20631614824232</v>
+        <v>15.23225417789508</v>
       </c>
       <c r="K2">
-        <v>1.191010779202271</v>
+        <v>1.191502224258184</v>
       </c>
       <c r="L2">
-        <v>5.160675200272165</v>
+        <v>5.082776460318481</v>
       </c>
       <c r="M2">
-        <v>0.453364169885097</v>
+        <v>0.4419418440478126</v>
       </c>
       <c r="N2">
-        <v>10.08444457704735</v>
+        <v>10.138613805425</v>
       </c>
       <c r="O2">
-        <v>0.6793821805808953</v>
+        <v>0.8756762122986189</v>
       </c>
       <c r="P2">
-        <v>5.070429605468534</v>
+        <v>5.067678417852673</v>
       </c>
       <c r="Q2">
-        <v>0.4313717702867806</v>
+        <v>0.4890762736815</v>
       </c>
       <c r="R2">
-        <v>15.08489566962486</v>
+        <v>15.19821828270453</v>
       </c>
       <c r="S2">
-        <v>0.8885442635143215</v>
+        <v>1.117649054432708</v>
       </c>
       <c r="T2">
-        <v>10.63308157967123</v>
+        <v>10.67718030693303</v>
       </c>
       <c r="U2">
-        <v>0.8615662173317238</v>
+        <v>0.9546634984290052</v>
       </c>
       <c r="V2">
-        <v>2.300401236674583</v>
+        <v>2.275534474075004</v>
       </c>
       <c r="W2">
-        <v>0.2687353349647911</v>
+        <v>0.2357288020652988</v>
       </c>
       <c r="X2">
-        <v>2.272833331896503</v>
+        <v>2.279539396887054</v>
       </c>
       <c r="Y2">
-        <v>0.2592255986680573</v>
+        <v>0.2526553750825796</v>
       </c>
       <c r="Z2">
-        <v>5.160675200272165</v>
+        <v>5.082776460318481</v>
       </c>
       <c r="AA2">
-        <v>0.453364169885097</v>
+        <v>0.4419418440478126</v>
       </c>
       <c r="AB2">
-        <v>10.08444457704735</v>
+        <v>10.138613805425</v>
       </c>
       <c r="AC2">
-        <v>0.6793821805808953</v>
+        <v>0.8756762122986189</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -725,94 +725,94 @@
         <v>2021</v>
       </c>
       <c r="B3">
-        <v>109.707197948252</v>
+        <v>110.3779653849749</v>
       </c>
       <c r="C3">
-        <v>5.600001281764813</v>
+        <v>5.468618113188383</v>
       </c>
       <c r="D3">
-        <v>54.88528218102728</v>
+        <v>55.12774569178221</v>
       </c>
       <c r="E3">
-        <v>3.814345276896495</v>
+        <v>3.089053355445273</v>
       </c>
       <c r="F3">
-        <v>54.8219157672247</v>
+        <v>55.25021969319268</v>
       </c>
       <c r="G3">
-        <v>3.337221790741664</v>
+        <v>3.310947741828199</v>
       </c>
       <c r="H3">
-        <v>16.50556507218209</v>
+        <v>16.5852371911688</v>
       </c>
       <c r="I3">
-        <v>1.17480551694136</v>
+        <v>1.102600623671369</v>
       </c>
       <c r="J3">
-        <v>16.41047995979266</v>
+        <v>16.55932289211358</v>
       </c>
       <c r="K3">
-        <v>1.349135753726936</v>
+        <v>1.244306867790606</v>
       </c>
       <c r="L3">
-        <v>5.488499033788274</v>
+        <v>5.519635742858928</v>
       </c>
       <c r="M3">
-        <v>0.4685944001703194</v>
+        <v>0.4876287283290878</v>
       </c>
       <c r="N3">
-        <v>10.93911938527347</v>
+        <v>11.06232687725065</v>
       </c>
       <c r="O3">
-        <v>0.8297115254532789</v>
+        <v>0.8378804661309744</v>
       </c>
       <c r="P3">
-        <v>5.478252316188206</v>
+        <v>5.523696989800705</v>
       </c>
       <c r="Q3">
-        <v>0.4238342256434968</v>
+        <v>0.4330877817063417</v>
       </c>
       <c r="R3">
-        <v>16.50556507218209</v>
+        <v>16.5852371911688</v>
       </c>
       <c r="S3">
-        <v>1.17480551694136</v>
+        <v>1.102600623671369</v>
       </c>
       <c r="T3">
-        <v>11.44836149977372</v>
+        <v>11.54311062107545</v>
       </c>
       <c r="U3">
-        <v>1.06037475863937</v>
+        <v>0.9882949065794145</v>
       </c>
       <c r="V3">
-        <v>2.488658157901453</v>
+        <v>2.494927642017148</v>
       </c>
       <c r="W3">
-        <v>0.2622986861775511</v>
+        <v>0.2520654990080258</v>
       </c>
       <c r="X3">
-        <v>2.473460302117485</v>
+        <v>2.52128462902098</v>
       </c>
       <c r="Y3">
-        <v>0.2705255710472279</v>
+        <v>0.2730655880562716</v>
       </c>
       <c r="Z3">
-        <v>5.488499033788274</v>
+        <v>5.519635742858928</v>
       </c>
       <c r="AA3">
-        <v>0.4685944001703194</v>
+        <v>0.4876287283290878</v>
       </c>
       <c r="AB3">
-        <v>10.93911938527347</v>
+        <v>11.06232687725065</v>
       </c>
       <c r="AC3">
-        <v>0.8297115254532789</v>
+        <v>0.8378804661309744</v>
       </c>
       <c r="AD3">
-        <v>8.145441325734485</v>
+        <v>8.197793661098542</v>
       </c>
       <c r="AE3">
-        <v>0.6854890023616238</v>
+        <v>0.7407762271655169</v>
       </c>
     </row>
     <row r="4" spans="1:31">
@@ -820,94 +820,94 @@
         <v>2022</v>
       </c>
       <c r="B4">
-        <v>121.1751965132662</v>
+        <v>120.0981575339995</v>
       </c>
       <c r="C4">
-        <v>5.242792029086821</v>
+        <v>5.42148506025385</v>
       </c>
       <c r="D4">
-        <v>60.39157475059026</v>
+        <v>59.87691742482658</v>
       </c>
       <c r="E4">
-        <v>3.08948858569708</v>
+        <v>2.882371914159329</v>
       </c>
       <c r="F4">
-        <v>60.78362176267596</v>
+        <v>60.22124010917288</v>
       </c>
       <c r="G4">
-        <v>3.32012347839391</v>
+        <v>3.536908986650282</v>
       </c>
       <c r="H4">
-        <v>18.36650353140548</v>
+        <v>18.03586350466836</v>
       </c>
       <c r="I4">
-        <v>1.36063057102117</v>
+        <v>1.29874768129343</v>
       </c>
       <c r="J4">
-        <v>18.3170618892905</v>
+        <v>18.00836428825568</v>
       </c>
       <c r="K4">
-        <v>1.248207508997669</v>
+        <v>1.146989723970737</v>
       </c>
       <c r="L4">
-        <v>5.908768465629979</v>
+        <v>6.057711562075772</v>
       </c>
       <c r="M4">
-        <v>0.5080695878834797</v>
+        <v>0.5519325472542083</v>
       </c>
       <c r="N4">
-        <v>12.1479269865022</v>
+        <v>12.06351961401438</v>
       </c>
       <c r="O4">
-        <v>0.7495047471716796</v>
+        <v>0.9496589312992814</v>
       </c>
       <c r="P4">
-        <v>6.043360889847785</v>
+        <v>6.055781140158704</v>
       </c>
       <c r="Q4">
-        <v>0.5353084161761348</v>
+        <v>0.4761421323177711</v>
       </c>
       <c r="R4">
-        <v>18.36650353140548</v>
+        <v>18.03586350466836</v>
       </c>
       <c r="S4">
-        <v>1.36063057102117</v>
+        <v>1.29874768129343</v>
       </c>
       <c r="T4">
-        <v>13.00125974533451</v>
+        <v>12.50539345609225</v>
       </c>
       <c r="U4">
-        <v>0.9175246200953349</v>
+        <v>1.01404725392116</v>
       </c>
       <c r="V4">
-        <v>2.672638853686346</v>
+        <v>2.758127419674229</v>
       </c>
       <c r="W4">
-        <v>0.3302600471623399</v>
+        <v>0.2635408157520963</v>
       </c>
       <c r="X4">
-        <v>2.643163290269645</v>
+        <v>2.744843412489206</v>
       </c>
       <c r="Y4">
-        <v>0.3186622331203489</v>
+        <v>0.3042888853399384</v>
       </c>
       <c r="Z4">
-        <v>5.908768465629979</v>
+        <v>6.057711562075772</v>
       </c>
       <c r="AA4">
-        <v>0.5080695878834797</v>
+        <v>0.5519325472542083</v>
       </c>
       <c r="AB4">
-        <v>12.1479269865022</v>
+        <v>12.06351961401438</v>
       </c>
       <c r="AC4">
-        <v>0.7495047471716796</v>
+        <v>0.9496589312992814</v>
       </c>
       <c r="AD4">
-        <v>11.78263359053208</v>
+        <v>11.94491436235232</v>
       </c>
       <c r="AE4">
-        <v>0.6910499037910857</v>
+        <v>0.7991670106820571</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -915,94 +915,94 @@
         <v>2023</v>
       </c>
       <c r="B5">
-        <v>131.2054100305348</v>
+        <v>128.6447184694571</v>
       </c>
       <c r="C5">
-        <v>8.116993265021959</v>
+        <v>5.85746301856603</v>
       </c>
       <c r="D5">
-        <v>65.37674470455526</v>
+        <v>64.54549619407467</v>
       </c>
       <c r="E5">
-        <v>4.383919590805982</v>
+        <v>4.200496060684776</v>
       </c>
       <c r="F5">
-        <v>65.82866532597947</v>
+        <v>64.09922227538237</v>
       </c>
       <c r="G5">
-        <v>5.043569035986869</v>
+        <v>3.811302124891907</v>
       </c>
       <c r="H5">
-        <v>19.79027532300575</v>
+        <v>19.2969195857408</v>
       </c>
       <c r="I5">
-        <v>1.852285994619337</v>
+        <v>1.305194458883397</v>
       </c>
       <c r="J5">
-        <v>19.67884467846289</v>
+        <v>19.25664295117028</v>
       </c>
       <c r="K5">
-        <v>1.710560976693991</v>
+        <v>1.326906672050682</v>
       </c>
       <c r="L5">
-        <v>6.582455009570723</v>
+        <v>6.380850483796555</v>
       </c>
       <c r="M5">
-        <v>0.5536533763419272</v>
+        <v>0.5657647370243871</v>
       </c>
       <c r="N5">
-        <v>13.16358045612916</v>
+        <v>12.81416311483685</v>
       </c>
       <c r="O5">
-        <v>1.159109180215018</v>
+        <v>1.143530292548063</v>
       </c>
       <c r="P5">
-        <v>6.613509858810958</v>
+        <v>6.350646139837908</v>
       </c>
       <c r="Q5">
-        <v>0.6497249480812332</v>
+        <v>0.524814554904839</v>
       </c>
       <c r="R5">
-        <v>19.79027532300575</v>
+        <v>19.2969195857408</v>
       </c>
       <c r="S5">
-        <v>1.852285994619337</v>
+        <v>1.305194458883397</v>
       </c>
       <c r="T5">
-        <v>13.69548413625282</v>
+        <v>13.39613713752278</v>
       </c>
       <c r="U5">
-        <v>1.381058060463542</v>
+        <v>1.153758327205616</v>
       </c>
       <c r="V5">
-        <v>2.986019621453599</v>
+        <v>2.943401713750514</v>
       </c>
       <c r="W5">
-        <v>0.3016099263224518</v>
+        <v>0.2537980991967082</v>
       </c>
       <c r="X5">
-        <v>2.997340920756467</v>
+        <v>2.917104099896993</v>
       </c>
       <c r="Y5">
-        <v>0.3057035537517128</v>
+        <v>0.2734859159585566</v>
       </c>
       <c r="Z5">
-        <v>6.582455009570723</v>
+        <v>6.380850483796555</v>
       </c>
       <c r="AA5">
-        <v>0.5536533763419272</v>
+        <v>0.5657647370243871</v>
       </c>
       <c r="AB5">
-        <v>13.16358045612916</v>
+        <v>12.81416311483685</v>
       </c>
       <c r="AC5">
-        <v>1.159109180215018</v>
+        <v>1.143530292548063</v>
       </c>
       <c r="AD5">
-        <v>13.92010459445073</v>
+        <v>13.95199541200906</v>
       </c>
       <c r="AE5">
-        <v>0.8105229448820823</v>
+        <v>0.6003308391849537</v>
       </c>
     </row>
     <row r="6" spans="1:31">
@@ -1010,94 +1010,94 @@
         <v>2024</v>
       </c>
       <c r="B6">
-        <v>138.4781808844324</v>
+        <v>140.5670136754738</v>
       </c>
       <c r="C6">
-        <v>6.608691183778803</v>
+        <v>7.339321225275858</v>
       </c>
       <c r="D6">
-        <v>69.22265045851476</v>
+        <v>69.76851365200785</v>
       </c>
       <c r="E6">
-        <v>3.861725991315873</v>
+        <v>4.104393661440275</v>
       </c>
       <c r="F6">
-        <v>69.25553042591753</v>
+        <v>70.79850002346588</v>
       </c>
       <c r="G6">
-        <v>4.032105200116379</v>
+        <v>4.672212659821131</v>
       </c>
       <c r="H6">
-        <v>20.80213024661373</v>
+        <v>21.28818588095664</v>
       </c>
       <c r="I6">
-        <v>1.514020549337848</v>
+        <v>1.713069952941228</v>
       </c>
       <c r="J6">
-        <v>20.69399521361503</v>
+        <v>21.08938183902098</v>
       </c>
       <c r="K6">
-        <v>1.611685415482329</v>
+        <v>1.469246606553422</v>
       </c>
       <c r="L6">
-        <v>6.893885716448566</v>
+        <v>7.061229945165913</v>
       </c>
       <c r="M6">
-        <v>0.5883234689141176</v>
+        <v>0.6204143656090217</v>
       </c>
       <c r="N6">
-        <v>13.93201632147551</v>
+        <v>14.1893266521806</v>
       </c>
       <c r="O6">
-        <v>0.9756411007417036</v>
+        <v>1.160468332159097</v>
       </c>
       <c r="P6">
-        <v>6.9335029277647</v>
+        <v>7.170375706141776</v>
       </c>
       <c r="Q6">
-        <v>0.6194686978181358</v>
+        <v>0.6604656735860782</v>
       </c>
       <c r="R6">
-        <v>20.80213024661373</v>
+        <v>21.28818588095664</v>
       </c>
       <c r="S6">
-        <v>1.514020549337848</v>
+        <v>1.713069952941228</v>
       </c>
       <c r="T6">
-        <v>14.56260082834332</v>
+        <v>14.7960166504985</v>
       </c>
       <c r="U6">
-        <v>1.179844489639878</v>
+        <v>1.163523555998329</v>
       </c>
       <c r="V6">
-        <v>3.05772223964645</v>
+        <v>3.14950738013488</v>
       </c>
       <c r="W6">
-        <v>0.3395007362303014</v>
+        <v>0.4094462221416348</v>
       </c>
       <c r="X6">
-        <v>3.07367214562526</v>
+        <v>3.143857808387595</v>
       </c>
       <c r="Y6">
-        <v>0.3624294001673468</v>
+        <v>0.3385378146377007</v>
       </c>
       <c r="Z6">
-        <v>6.893885716448566</v>
+        <v>7.061229945165913</v>
       </c>
       <c r="AA6">
-        <v>0.5883234689141176</v>
+        <v>0.6204143656090217</v>
       </c>
       <c r="AB6">
-        <v>13.93201632147551</v>
+        <v>14.1893266521806</v>
       </c>
       <c r="AC6">
-        <v>0.9756411007417036</v>
+        <v>1.160468332159097</v>
       </c>
       <c r="AD6">
-        <v>15.54900028584319</v>
+        <v>15.64600682586078</v>
       </c>
       <c r="AE6">
-        <v>0.6958198363738696</v>
+        <v>0.8912644934883214</v>
       </c>
     </row>
     <row r="7" spans="1:31">
@@ -1105,94 +1105,94 @@
         <v>2025</v>
       </c>
       <c r="B7">
-        <v>149.5579464704375</v>
+        <v>151.1374413750536</v>
       </c>
       <c r="C7">
-        <v>7.747688827093858</v>
+        <v>7.417218703956479</v>
       </c>
       <c r="D7">
-        <v>74.823240145325</v>
+        <v>75.63193522600477</v>
       </c>
       <c r="E7">
-        <v>4.561285773060686</v>
+        <v>4.666109819758304</v>
       </c>
       <c r="F7">
-        <v>74.73470632511253</v>
+        <v>75.50550614904891</v>
       </c>
       <c r="G7">
-        <v>4.532882862286606</v>
+        <v>4.203120259854809</v>
       </c>
       <c r="H7">
-        <v>22.40833719967301</v>
+        <v>22.48503460087376</v>
       </c>
       <c r="I7">
-        <v>1.525767013042533</v>
+        <v>1.633116971819138</v>
       </c>
       <c r="J7">
-        <v>22.37818528454978</v>
+        <v>22.62307660266333</v>
       </c>
       <c r="K7">
-        <v>1.775687821594246</v>
+        <v>1.633375195218912</v>
       </c>
       <c r="L7">
-        <v>7.528236486663773</v>
+        <v>7.553418647746001</v>
       </c>
       <c r="M7">
-        <v>0.644694569565913</v>
+        <v>0.5162709371962634</v>
       </c>
       <c r="N7">
-        <v>14.9731836614055</v>
+        <v>15.23106295007443</v>
       </c>
       <c r="O7">
-        <v>1.189332554976774</v>
+        <v>1.095518029548678</v>
       </c>
       <c r="P7">
-        <v>7.446763692820443</v>
+        <v>7.612913347691386</v>
       </c>
       <c r="Q7">
-        <v>0.648819439345996</v>
+        <v>0.5799454231828362</v>
       </c>
       <c r="R7">
-        <v>22.40833719967301</v>
+        <v>22.48503460087376</v>
       </c>
       <c r="S7">
-        <v>1.525767013042533</v>
+        <v>1.633116971819138</v>
       </c>
       <c r="T7">
-        <v>15.5773265123503</v>
+        <v>15.69813439868214</v>
       </c>
       <c r="U7">
-        <v>1.466430837235251</v>
+        <v>1.198495032360426</v>
       </c>
       <c r="V7">
-        <v>3.431613274974648</v>
+        <v>3.467852093395293</v>
       </c>
       <c r="W7">
-        <v>0.4500020557153877</v>
+        <v>0.3598047473465713</v>
       </c>
       <c r="X7">
-        <v>3.36924549722484</v>
+        <v>3.457090110585895</v>
       </c>
       <c r="Y7">
-        <v>0.4262868247239823</v>
+        <v>0.3730858980846808</v>
       </c>
       <c r="Z7">
-        <v>7.528236486663773</v>
+        <v>7.553418647746001</v>
       </c>
       <c r="AA7">
-        <v>0.644694569565913</v>
+        <v>0.5162709371962634</v>
       </c>
       <c r="AB7">
-        <v>14.9731836614055</v>
+        <v>15.23106295007443</v>
       </c>
       <c r="AC7">
-        <v>1.189332554976774</v>
+        <v>1.095518029548678</v>
       </c>
       <c r="AD7">
-        <v>17.03407692948743</v>
+        <v>16.7456146639077</v>
       </c>
       <c r="AE7">
-        <v>0.8602674710753158</v>
+        <v>0.7609423413372302</v>
       </c>
     </row>
     <row r="8" spans="1:31">
@@ -1200,94 +1200,94 @@
         <v>2026</v>
       </c>
       <c r="B8">
-        <v>159.7501370621347</v>
+        <v>160.1644543503816</v>
       </c>
       <c r="C8">
-        <v>7.193633993623568</v>
+        <v>7.684584213699437</v>
       </c>
       <c r="D8">
-        <v>79.60134766598752</v>
+        <v>79.52613223862038</v>
       </c>
       <c r="E8">
-        <v>4.317286795918008</v>
+        <v>3.927581726313675</v>
       </c>
       <c r="F8">
-        <v>80.14878939614718</v>
+        <v>80.63832211176121</v>
       </c>
       <c r="G8">
-        <v>5.00926148249895</v>
+        <v>5.019011981901428</v>
       </c>
       <c r="H8">
-        <v>24.12774684780427</v>
+        <v>24.0019358599407</v>
       </c>
       <c r="I8">
-        <v>1.703010218489755</v>
+        <v>1.613930630658148</v>
       </c>
       <c r="J8">
-        <v>23.85187516977221</v>
+        <v>24.47257186034599</v>
       </c>
       <c r="K8">
-        <v>1.707668321206136</v>
+        <v>2.081280869086795</v>
       </c>
       <c r="L8">
-        <v>7.978557593855401</v>
+        <v>8.013124876461106</v>
       </c>
       <c r="M8">
-        <v>0.722326357597139</v>
+        <v>0.5970375009593359</v>
       </c>
       <c r="N8">
-        <v>16.05313539791384</v>
+        <v>16.02845061070118</v>
       </c>
       <c r="O8">
-        <v>1.436900858796063</v>
+        <v>1.244273872410903</v>
       </c>
       <c r="P8">
-        <v>8.137474386801449</v>
+        <v>8.122238904312242</v>
       </c>
       <c r="Q8">
-        <v>0.6179138987464504</v>
+        <v>0.661797949560782</v>
       </c>
       <c r="R8">
-        <v>24.12774684780427</v>
+        <v>24.0019358599407</v>
       </c>
       <c r="S8">
-        <v>1.703010218489755</v>
+        <v>1.613930630658148</v>
       </c>
       <c r="T8">
-        <v>16.77989045898098</v>
+        <v>17.14423751778831</v>
       </c>
       <c r="U8">
-        <v>1.112161779695143</v>
+        <v>1.42932512954841</v>
       </c>
       <c r="V8">
-        <v>3.52887461659744</v>
+        <v>3.652113859305754</v>
       </c>
       <c r="W8">
-        <v>0.4442198839518614</v>
+        <v>0.5160749319320873</v>
       </c>
       <c r="X8">
-        <v>3.543110094193791</v>
+        <v>3.676220483251925</v>
       </c>
       <c r="Y8">
-        <v>0.471740909670426</v>
+        <v>0.4701527565060802</v>
       </c>
       <c r="Z8">
-        <v>7.978557593855401</v>
+        <v>8.013124876461106</v>
       </c>
       <c r="AA8">
-        <v>0.722326357597139</v>
+        <v>0.5970375009593359</v>
       </c>
       <c r="AB8">
-        <v>16.05313539791384</v>
+        <v>16.02845061070118</v>
       </c>
       <c r="AC8">
-        <v>1.436900858796063</v>
+        <v>1.244273872410903</v>
       </c>
       <c r="AD8">
-        <v>18.49376550815364</v>
+        <v>18.2772187079948</v>
       </c>
       <c r="AE8">
-        <v>0.7392438033404323</v>
+        <v>0.6774854287921688</v>
       </c>
     </row>
     <row r="9" spans="1:31">
@@ -1295,94 +1295,94 @@
         <v>2027</v>
       </c>
       <c r="B9">
-        <v>169.5359863310549</v>
+        <v>170.0082401738343</v>
       </c>
       <c r="C9">
-        <v>7.840530835392824</v>
+        <v>8.054901087028606</v>
       </c>
       <c r="D9">
-        <v>84.79233301725377</v>
+        <v>84.82974752655393</v>
       </c>
       <c r="E9">
-        <v>5.35509961237626</v>
+        <v>5.281882919770375</v>
       </c>
       <c r="F9">
-        <v>84.74365331380109</v>
+        <v>85.17848963812622</v>
       </c>
       <c r="G9">
-        <v>4.535013010975676</v>
+        <v>4.957651064336239</v>
       </c>
       <c r="H9">
-        <v>25.36977774331421</v>
+        <v>25.7270109293463</v>
       </c>
       <c r="I9">
-        <v>1.533188030931857</v>
+        <v>1.862583653121678</v>
       </c>
       <c r="J9">
-        <v>25.54364833262409</v>
+        <v>25.28987723221036</v>
       </c>
       <c r="K9">
-        <v>1.793031214792107</v>
+        <v>1.888795364172771</v>
       </c>
       <c r="L9">
-        <v>8.385549846478147</v>
+        <v>8.603519934233468</v>
       </c>
       <c r="M9">
-        <v>0.642754223566259</v>
+        <v>0.8309481084991238</v>
       </c>
       <c r="N9">
-        <v>16.95300152578353</v>
+        <v>16.97651722102736</v>
       </c>
       <c r="O9">
-        <v>1.297492715672742</v>
+        <v>1.141012571946009</v>
       </c>
       <c r="P9">
-        <v>8.491675865601144</v>
+        <v>8.581564321308763</v>
       </c>
       <c r="Q9">
-        <v>0.735242053870342</v>
+        <v>0.7677243825372798</v>
       </c>
       <c r="R9">
-        <v>25.36977774331421</v>
+        <v>25.7270109293463</v>
       </c>
       <c r="S9">
-        <v>1.533188030931857</v>
+        <v>1.862583653121678</v>
       </c>
       <c r="T9">
-        <v>17.9113844028785</v>
+        <v>17.80363213219942</v>
       </c>
       <c r="U9">
-        <v>1.420529097958285</v>
+        <v>1.448834716090893</v>
       </c>
       <c r="V9">
-        <v>3.801067256639805</v>
+        <v>3.744808120074696</v>
       </c>
       <c r="W9">
-        <v>0.4121490534573972</v>
+        <v>0.4581945762391037</v>
       </c>
       <c r="X9">
-        <v>3.83119667310576</v>
+        <v>3.741436979936249</v>
       </c>
       <c r="Y9">
-        <v>0.4549782963768986</v>
+        <v>0.4136064781379423</v>
       </c>
       <c r="Z9">
-        <v>8.385549846478147</v>
+        <v>8.603519934233468</v>
       </c>
       <c r="AA9">
-        <v>0.642754223566259</v>
+        <v>0.8309481084991238</v>
       </c>
       <c r="AB9">
-        <v>16.95300152578353</v>
+        <v>16.97651722102736</v>
       </c>
       <c r="AC9">
-        <v>1.297492715672742</v>
+        <v>1.141012571946009</v>
       </c>
       <c r="AD9">
-        <v>19.78024101673869</v>
+        <v>19.67668418100878</v>
       </c>
       <c r="AE9">
-        <v>0.9821075683319498</v>
+        <v>1.015931994436633</v>
       </c>
     </row>
     <row r="10" spans="1:31">
@@ -1390,94 +1390,94 @@
         <v>2028</v>
       </c>
       <c r="B10">
-        <v>179.5928562187499</v>
+        <v>181.6124094027168</v>
       </c>
       <c r="C10">
-        <v>8.459205362288113</v>
+        <v>9.966543371824097</v>
       </c>
       <c r="D10">
-        <v>89.99151951960113</v>
+        <v>90.8688776437523</v>
       </c>
       <c r="E10">
-        <v>5.592691907133609</v>
+        <v>4.832816907420847</v>
       </c>
       <c r="F10">
-        <v>89.60133669914885</v>
+        <v>90.74353175896452</v>
       </c>
       <c r="G10">
-        <v>4.565694115098204</v>
+        <v>6.654376719469013</v>
       </c>
       <c r="H10">
-        <v>27.41007320597872</v>
+        <v>27.47490793516358</v>
       </c>
       <c r="I10">
-        <v>1.918046484018668</v>
+        <v>2.272633013323423</v>
       </c>
       <c r="J10">
-        <v>26.61443866670993</v>
+        <v>27.2184132177959</v>
       </c>
       <c r="K10">
-        <v>1.80041173665264</v>
+        <v>2.586346306566965</v>
       </c>
       <c r="L10">
-        <v>8.762841214160892</v>
+        <v>9.023125216954009</v>
       </c>
       <c r="M10">
-        <v>0.6587568615560411</v>
+        <v>0.7458706950029222</v>
       </c>
       <c r="N10">
-        <v>17.90415042624437</v>
+        <v>17.92533505609282</v>
       </c>
       <c r="O10">
-        <v>1.08593551549099</v>
+        <v>1.474545695461163</v>
       </c>
       <c r="P10">
-        <v>8.909833186054932</v>
+        <v>9.101750332958186</v>
       </c>
       <c r="Q10">
-        <v>0.6427649747902198</v>
+        <v>0.8478657497424956</v>
       </c>
       <c r="R10">
-        <v>27.41007320597872</v>
+        <v>27.47490793516358</v>
       </c>
       <c r="S10">
-        <v>1.918046484018668</v>
+        <v>2.272633013323423</v>
       </c>
       <c r="T10">
-        <v>18.69208550003964</v>
+        <v>18.94752157461</v>
       </c>
       <c r="U10">
-        <v>1.366282978962309</v>
+        <v>2.006168596431932</v>
       </c>
       <c r="V10">
-        <v>3.975163451166972</v>
+        <v>4.155258069458512</v>
       </c>
       <c r="W10">
-        <v>0.4149313151182608</v>
+        <v>0.4792400444640261</v>
       </c>
       <c r="X10">
-        <v>3.947189715503322</v>
+        <v>4.115633573727396</v>
       </c>
       <c r="Y10">
-        <v>0.4577298977062312</v>
+        <v>0.5186380403979541</v>
       </c>
       <c r="Z10">
-        <v>8.762841214160892</v>
+        <v>9.023125216954009</v>
       </c>
       <c r="AA10">
-        <v>0.6587568615560411</v>
+        <v>0.7458706950029222</v>
       </c>
       <c r="AB10">
-        <v>17.90415042624437</v>
+        <v>17.92533505609282</v>
       </c>
       <c r="AC10">
-        <v>1.08593551549099</v>
+        <v>1.474545695461163</v>
       </c>
       <c r="AD10">
-        <v>20.94292490947764</v>
+        <v>20.9672564226662</v>
       </c>
       <c r="AE10">
-        <v>0.8497780303697596</v>
+        <v>1.154695854882883</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -1485,94 +1485,94 @@
         <v>2029</v>
       </c>
       <c r="B11">
-        <v>190.5182792572138</v>
+        <v>191.306517887792</v>
       </c>
       <c r="C11">
-        <v>8.634354409744079</v>
+        <v>9.297793334446174</v>
       </c>
       <c r="D11">
-        <v>96.20086273848023</v>
+        <v>95.5494168004286</v>
       </c>
       <c r="E11">
-        <v>6.307482570279485</v>
+        <v>5.1327652454676</v>
       </c>
       <c r="F11">
-        <v>94.31741651873361</v>
+        <v>95.75710108736334</v>
       </c>
       <c r="G11">
-        <v>5.848449921258791</v>
+        <v>6.446879049035664</v>
       </c>
       <c r="H11">
-        <v>28.36738049356445</v>
+        <v>29.10848385912178</v>
       </c>
       <c r="I11">
-        <v>2.070218965167807</v>
+        <v>2.17122740467475</v>
       </c>
       <c r="J11">
-        <v>28.53780995450396</v>
+        <v>28.29316764287744</v>
       </c>
       <c r="K11">
-        <v>2.019233836286949</v>
+        <v>2.431008707277171</v>
       </c>
       <c r="L11">
-        <v>9.329805654090947</v>
+        <v>9.551850440637573</v>
       </c>
       <c r="M11">
-        <v>0.9205068480907442</v>
+        <v>0.7877712241688583</v>
       </c>
       <c r="N11">
-        <v>18.65977266481204</v>
+        <v>19.22698468806115</v>
       </c>
       <c r="O11">
-        <v>1.382606280207493</v>
+        <v>1.464228821942399</v>
       </c>
       <c r="P11">
-        <v>9.422647751762211</v>
+        <v>9.57661445666537</v>
       </c>
       <c r="Q11">
-        <v>1.026958380259368</v>
+        <v>0.8189483270036041</v>
       </c>
       <c r="R11">
-        <v>28.36738049356445</v>
+        <v>29.10848385912178</v>
       </c>
       <c r="S11">
-        <v>2.070218965167807</v>
+        <v>2.17122740467475</v>
       </c>
       <c r="T11">
-        <v>19.83892296341196</v>
+        <v>19.72117256061734</v>
       </c>
       <c r="U11">
-        <v>1.545915655453503</v>
+        <v>1.891752896996438</v>
       </c>
       <c r="V11">
-        <v>4.317896219812617</v>
+        <v>4.296250286232422</v>
       </c>
       <c r="W11">
-        <v>0.4614818868782464</v>
+        <v>0.4838323217860815</v>
       </c>
       <c r="X11">
-        <v>4.380990771279371</v>
+        <v>4.275744796027674</v>
       </c>
       <c r="Y11">
-        <v>0.454098511441366</v>
+        <v>0.4744391465900309</v>
       </c>
       <c r="Z11">
-        <v>9.329805654090947</v>
+        <v>9.551850440637573</v>
       </c>
       <c r="AA11">
-        <v>0.9205068480907442</v>
+        <v>0.7877712241688583</v>
       </c>
       <c r="AB11">
-        <v>18.65977266481204</v>
+        <v>19.22698468806115</v>
       </c>
       <c r="AC11">
-        <v>1.382606280207493</v>
+        <v>1.464228821942399</v>
       </c>
       <c r="AD11">
-        <v>22.38405371969056</v>
+        <v>22.27709200526461</v>
       </c>
       <c r="AE11">
-        <v>1.028057269222813</v>
+        <v>0.9273972148694812</v>
       </c>
     </row>
     <row r="12" spans="1:31">
@@ -1580,94 +1580,94 @@
         <v>2030</v>
       </c>
       <c r="B12">
-        <v>199.8836094534406</v>
+        <v>200.3394532006388</v>
       </c>
       <c r="C12">
-        <v>7.78385735548061</v>
+        <v>10.44872545978033</v>
       </c>
       <c r="D12">
-        <v>99.49319704361611</v>
+        <v>100.0165314198888</v>
       </c>
       <c r="E12">
-        <v>4.651662286092257</v>
+        <v>6.989704136375872</v>
       </c>
       <c r="F12">
-        <v>100.3904124098245</v>
+        <v>100.32292178075</v>
       </c>
       <c r="G12">
-        <v>5.588181423818395</v>
+        <v>6.120994222235011</v>
       </c>
       <c r="H12">
-        <v>30.29449498028398</v>
+        <v>30.10027904666348</v>
       </c>
       <c r="I12">
-        <v>2.055982358703981</v>
+        <v>2.309410047512928</v>
       </c>
       <c r="J12">
-        <v>29.93685878477212</v>
+        <v>30.31912803572577</v>
       </c>
       <c r="K12">
-        <v>2.239797988320535</v>
+        <v>2.370573480569627</v>
       </c>
       <c r="L12">
-        <v>9.962237180443097</v>
+        <v>10.01359239663773</v>
       </c>
       <c r="M12">
-        <v>0.84634784625934</v>
+        <v>0.8007626946808382</v>
       </c>
       <c r="N12">
-        <v>20.02429232688875</v>
+        <v>19.9160112685385</v>
       </c>
       <c r="O12">
-        <v>1.340358561713614</v>
+        <v>1.519851386698655</v>
       </c>
       <c r="P12">
-        <v>10.17252913743659</v>
+        <v>9.973911033184528</v>
       </c>
       <c r="Q12">
-        <v>0.7512832979047136</v>
+        <v>0.8951027444367129</v>
       </c>
       <c r="R12">
-        <v>30.29449498028398</v>
+        <v>30.10027904666348</v>
       </c>
       <c r="S12">
-        <v>2.055982358703981</v>
+        <v>2.309410047512928</v>
       </c>
       <c r="T12">
-        <v>21.0074288982952</v>
+        <v>21.16330137053808</v>
       </c>
       <c r="U12">
-        <v>1.634345671812459</v>
+        <v>1.882319261841243</v>
       </c>
       <c r="V12">
-        <v>4.461660978171627</v>
+        <v>4.589992910558041</v>
       </c>
       <c r="W12">
-        <v>0.5292843468862031</v>
+        <v>0.5162002082615244</v>
       </c>
       <c r="X12">
-        <v>4.467768908305294</v>
+        <v>4.56583375462966</v>
       </c>
       <c r="Y12">
-        <v>0.5188156163577634</v>
+        <v>0.478100352044337</v>
       </c>
       <c r="Z12">
-        <v>9.962237180443097</v>
+        <v>10.01359239663773</v>
       </c>
       <c r="AA12">
-        <v>0.84634784625934</v>
+        <v>0.8007626946808382</v>
       </c>
       <c r="AB12">
-        <v>20.02429232688875</v>
+        <v>19.9160112685385</v>
       </c>
       <c r="AC12">
-        <v>1.340358561713614</v>
+        <v>1.519851386698655</v>
       </c>
       <c r="AD12">
-        <v>23.54953965161856</v>
+        <v>23.54283603561003</v>
       </c>
       <c r="AE12">
-        <v>0.9122841611698583</v>
+        <v>1.116846005764225</v>
       </c>
     </row>
     <row r="13" spans="1:31">
@@ -1675,94 +1675,94 @@
         <v>2031</v>
       </c>
       <c r="B13">
-        <v>10.03102287016553</v>
+        <v>10.07304181400216</v>
       </c>
       <c r="C13">
-        <v>0.5443836842336359</v>
+        <v>0.4809635701910406</v>
       </c>
       <c r="D13">
-        <v>5.034852664688315</v>
+        <v>5.056506560749505</v>
       </c>
       <c r="E13">
-        <v>0.3215102335926248</v>
+        <v>0.3158310320702611</v>
       </c>
       <c r="F13">
-        <v>4.996170205477211</v>
+        <v>5.016535253252652</v>
       </c>
       <c r="G13">
-        <v>0.3213515928619303</v>
+        <v>0.304303773968989</v>
       </c>
       <c r="H13">
-        <v>1.497506347457914</v>
+        <v>1.503696736066199</v>
       </c>
       <c r="I13">
-        <v>0.116718815957407</v>
+        <v>0.1120234253195272</v>
       </c>
       <c r="J13">
-        <v>1.519160266689835</v>
+        <v>1.510219190990305</v>
       </c>
       <c r="K13">
-        <v>0.1147973229073277</v>
+        <v>0.1090065676191951</v>
       </c>
       <c r="L13">
-        <v>0.4900566294261982</v>
+        <v>0.5103008637526376</v>
       </c>
       <c r="M13">
-        <v>0.04311346261550086</v>
+        <v>0.04835301146734095</v>
       </c>
       <c r="N13">
-        <v>1.0008128319849</v>
+        <v>0.9928007164165112</v>
       </c>
       <c r="O13">
-        <v>0.08113039858379265</v>
+        <v>0.08466999476565802</v>
       </c>
       <c r="P13">
-        <v>0.488634129918365</v>
+        <v>0.4995177460269995</v>
       </c>
       <c r="Q13">
-        <v>0.04022006517907811</v>
+        <v>0.04915520185644703</v>
       </c>
       <c r="R13">
-        <v>1.497506347457914</v>
+        <v>1.503696736066199</v>
       </c>
       <c r="S13">
-        <v>0.116718815957407</v>
+        <v>0.1120234253195272</v>
       </c>
       <c r="T13">
-        <v>1.055154446230241</v>
+        <v>1.060004732499515</v>
       </c>
       <c r="U13">
-        <v>0.09364978934941852</v>
+        <v>0.07640945877105353</v>
       </c>
       <c r="V13">
-        <v>0.2318979918880623</v>
+        <v>0.2256313534642641</v>
       </c>
       <c r="W13">
-        <v>0.02266163657518803</v>
+        <v>0.0270989707105821</v>
       </c>
       <c r="X13">
-        <v>0.232107828571531</v>
+        <v>0.2245831050265253</v>
       </c>
       <c r="Y13">
-        <v>0.02474247993098665</v>
+        <v>0.0277148201560915</v>
       </c>
       <c r="Z13">
-        <v>0.4900566294261982</v>
+        <v>0.5103008637526376</v>
       </c>
       <c r="AA13">
-        <v>0.04311346261550086</v>
+        <v>0.04835301146734095</v>
       </c>
       <c r="AB13">
-        <v>1.0008128319849</v>
+        <v>0.9928007164165112</v>
       </c>
       <c r="AC13">
-        <v>0.08113039858379265</v>
+        <v>0.08466999476565802</v>
       </c>
       <c r="AD13">
-        <v>24.77010441214048</v>
+        <v>24.69461403891093</v>
       </c>
       <c r="AE13">
-        <v>1.134343656537446</v>
+        <v>1.05129662415143</v>
       </c>
     </row>
     <row r="14" spans="1:31">
@@ -1770,94 +1770,94 @@
         <v>2032</v>
       </c>
       <c r="B14">
-        <v>219.3251347632988</v>
+        <v>219.858804092463</v>
       </c>
       <c r="C14">
-        <v>10.6367888283859</v>
+        <v>10.35465074631849</v>
       </c>
       <c r="D14">
-        <v>110.1881756583443</v>
+        <v>109.683813413783</v>
       </c>
       <c r="E14">
-        <v>6.574460869264921</v>
+        <v>6.297735857341409</v>
       </c>
       <c r="F14">
-        <v>109.1369591049545</v>
+        <v>110.1749906786801</v>
       </c>
       <c r="G14">
-        <v>6.732473316166803</v>
+        <v>6.33241914587899</v>
       </c>
       <c r="H14">
-        <v>32.78606132021898</v>
+        <v>33.09169025561516</v>
       </c>
       <c r="I14">
-        <v>2.625064106441558</v>
+        <v>2.614863230442781</v>
       </c>
       <c r="J14">
-        <v>32.57291507849209</v>
+        <v>32.87658778006402</v>
       </c>
       <c r="K14">
-        <v>2.503342204540523</v>
+        <v>2.626232413613802</v>
       </c>
       <c r="L14">
-        <v>11.03442667941683</v>
+        <v>10.98766126454764</v>
       </c>
       <c r="M14">
-        <v>0.9745794924362211</v>
+        <v>0.8496298852701675</v>
       </c>
       <c r="N14">
-        <v>21.71669062335756</v>
+        <v>22.16034473256471</v>
       </c>
       <c r="O14">
-        <v>1.611402976495356</v>
+        <v>1.540758739573111</v>
       </c>
       <c r="P14">
-        <v>11.02686540346899</v>
+        <v>11.05870664588856</v>
       </c>
       <c r="Q14">
-        <v>0.7655752384803146</v>
+        <v>0.7741773495376801</v>
       </c>
       <c r="R14">
-        <v>32.78606132021898</v>
+        <v>33.09169025561516</v>
       </c>
       <c r="S14">
-        <v>2.625064106441558</v>
+        <v>2.614863230442781</v>
       </c>
       <c r="T14">
-        <v>22.9287588880334</v>
+        <v>23.20268269681503</v>
       </c>
       <c r="U14">
-        <v>2.117374591148037</v>
+        <v>2.033885432147536</v>
       </c>
       <c r="V14">
-        <v>4.797490142976542</v>
+        <v>4.789323088279143</v>
       </c>
       <c r="W14">
-        <v>0.5542607219918291</v>
+        <v>0.4998993118706259</v>
       </c>
       <c r="X14">
-        <v>4.846666047482144</v>
+        <v>4.884581994969846</v>
       </c>
       <c r="Y14">
-        <v>0.528172138871399</v>
+        <v>0.5643610524964381</v>
       </c>
       <c r="Z14">
-        <v>11.03442667941683</v>
+        <v>10.98766126454764</v>
       </c>
       <c r="AA14">
-        <v>0.9745794924362211</v>
+        <v>0.8496298852701675</v>
       </c>
       <c r="AB14">
-        <v>21.71669062335756</v>
+        <v>22.16034473256471</v>
       </c>
       <c r="AC14">
-        <v>1.611402976495356</v>
+        <v>1.540758739573111</v>
       </c>
       <c r="AD14">
-        <v>9.636244132684487</v>
+        <v>9.60559855233476</v>
       </c>
       <c r="AE14">
-        <v>0.8403565304243213</v>
+        <v>0.8994416898651936</v>
       </c>
     </row>
     <row r="15" spans="1:31">
@@ -1865,94 +1865,94 @@
         <v>2033</v>
       </c>
       <c r="B15">
-        <v>228.5869164165639</v>
+        <v>229.7537131181953</v>
       </c>
       <c r="C15">
-        <v>10.78264700389407</v>
+        <v>11.663310491175</v>
       </c>
       <c r="D15">
-        <v>114.1698285244135</v>
+        <v>114.8695081490967</v>
       </c>
       <c r="E15">
-        <v>6.115110142787806</v>
+        <v>7.938562720369432</v>
       </c>
       <c r="F15">
-        <v>114.4170878921503</v>
+        <v>114.8842049690986</v>
       </c>
       <c r="G15">
-        <v>6.864368027420091</v>
+        <v>7.518769921842268</v>
       </c>
       <c r="H15">
-        <v>34.55260453359924</v>
+        <v>34.3504690528468</v>
       </c>
       <c r="I15">
-        <v>2.460049849630255</v>
+        <v>2.768172386859103</v>
       </c>
       <c r="J15">
-        <v>34.3132331615647</v>
+        <v>34.32332809803082</v>
       </c>
       <c r="K15">
-        <v>2.735007836609764</v>
+        <v>2.94341683195321</v>
       </c>
       <c r="L15">
-        <v>11.31874454292144</v>
+        <v>11.58820460938519</v>
       </c>
       <c r="M15">
-        <v>0.9300565362734418</v>
+        <v>0.8824217387657073</v>
       </c>
       <c r="N15">
-        <v>22.84474844645841</v>
+        <v>22.94270642327474</v>
       </c>
       <c r="O15">
-        <v>1.681587374175531</v>
+        <v>1.491646201245742</v>
       </c>
       <c r="P15">
-        <v>11.38775720760655</v>
+        <v>11.679496785561</v>
       </c>
       <c r="Q15">
-        <v>1.179878481142806</v>
+        <v>1.032824024613885</v>
       </c>
       <c r="R15">
-        <v>34.55260453359924</v>
+        <v>34.3504690528468</v>
       </c>
       <c r="S15">
-        <v>2.460049849630255</v>
+        <v>2.768172386859103</v>
       </c>
       <c r="T15">
-        <v>24.0246984807797</v>
+        <v>24.07017947042922</v>
       </c>
       <c r="U15">
-        <v>2.012238590913085</v>
+        <v>2.166246112628731</v>
       </c>
       <c r="V15">
-        <v>5.119887376475408</v>
+        <v>5.104426195643509</v>
       </c>
       <c r="W15">
-        <v>0.6360202344284307</v>
+        <v>0.6223431250867388</v>
       </c>
       <c r="X15">
-        <v>5.168647304309602</v>
+        <v>5.148722431958074</v>
       </c>
       <c r="Y15">
-        <v>0.6661360380584068</v>
+        <v>0.6001444163226841</v>
       </c>
       <c r="Z15">
-        <v>11.31874454292144</v>
+        <v>11.58820460938519</v>
       </c>
       <c r="AA15">
-        <v>0.9300565362734418</v>
+        <v>0.8824217387657073</v>
       </c>
       <c r="AB15">
-        <v>22.84474844645841</v>
+        <v>22.94270642327474</v>
       </c>
       <c r="AC15">
-        <v>1.681587374175531</v>
+        <v>1.491646201245742</v>
       </c>
       <c r="AD15">
-        <v>21.35404435493049</v>
+        <v>21.88898523029462</v>
       </c>
       <c r="AE15">
-        <v>1.056338940331217</v>
+        <v>1.478051895809845</v>
       </c>
     </row>
     <row r="16" spans="1:31">
@@ -1960,94 +1960,94 @@
         <v>2034</v>
       </c>
       <c r="B16">
-        <v>241.2035266057145</v>
+        <v>241.3322072910336</v>
       </c>
       <c r="C16">
-        <v>11.39676413245357</v>
+        <v>10.98812670786491</v>
       </c>
       <c r="D16">
-        <v>120.9115785252184</v>
+        <v>120.6701035268929</v>
       </c>
       <c r="E16">
-        <v>6.292735000800104</v>
+        <v>7.9929407324275</v>
       </c>
       <c r="F16">
-        <v>120.2919480804961</v>
+        <v>120.6621037641406</v>
       </c>
       <c r="G16">
-        <v>7.791325397822564</v>
+        <v>6.842484955379044</v>
       </c>
       <c r="H16">
-        <v>36.54383900098379</v>
+        <v>36.09386155714055</v>
       </c>
       <c r="I16">
-        <v>2.941883744157522</v>
+        <v>2.561875503669191</v>
       </c>
       <c r="J16">
-        <v>36.38612674701355</v>
+        <v>36.09996716985517</v>
       </c>
       <c r="K16">
-        <v>2.856151659781042</v>
+        <v>2.172706075454277</v>
       </c>
       <c r="L16">
-        <v>11.7562844770112</v>
+        <v>12.14648909051866</v>
       </c>
       <c r="M16">
-        <v>0.9730117077422595</v>
+        <v>1.122399413287218</v>
       </c>
       <c r="N16">
-        <v>23.69835776766359</v>
+        <v>24.16917813702939</v>
       </c>
       <c r="O16">
-        <v>1.935254290415513</v>
+        <v>1.951569176899174</v>
       </c>
       <c r="P16">
-        <v>11.90734008782399</v>
+        <v>12.15260780959685</v>
       </c>
       <c r="Q16">
-        <v>1.040214907440805</v>
+        <v>0.8936618992337902</v>
       </c>
       <c r="R16">
-        <v>36.54383900098379</v>
+        <v>36.09386155714055</v>
       </c>
       <c r="S16">
-        <v>2.941883744157522</v>
+        <v>2.561875503669191</v>
       </c>
       <c r="T16">
-        <v>25.33803515620602</v>
+        <v>25.18349842556115</v>
       </c>
       <c r="U16">
-        <v>2.06608037676627</v>
+        <v>1.97053129502679</v>
       </c>
       <c r="V16">
-        <v>5.542650739602935</v>
+        <v>5.448865118628691</v>
       </c>
       <c r="W16">
-        <v>0.6892634898789542</v>
+        <v>0.5946315061501772</v>
       </c>
       <c r="X16">
-        <v>5.505440851204591</v>
+        <v>5.467603625665351</v>
       </c>
       <c r="Y16">
-        <v>0.6973164814900846</v>
+        <v>0.666243196294496</v>
       </c>
       <c r="Z16">
-        <v>11.7562844770112</v>
+        <v>12.14648909051866</v>
       </c>
       <c r="AA16">
-        <v>0.9730117077422595</v>
+        <v>1.122399413287218</v>
       </c>
       <c r="AB16">
-        <v>23.69835776766359</v>
+        <v>24.16917813702939</v>
       </c>
       <c r="AC16">
-        <v>1.935254290415513</v>
+        <v>1.951569176899174</v>
       </c>
       <c r="AD16">
-        <v>26.28136179859146</v>
+        <v>26.31046133501425</v>
       </c>
       <c r="AE16">
-        <v>1.26625716955997</v>
+        <v>1.378957846987393</v>
       </c>
     </row>
     <row r="17" spans="1:31">
@@ -2055,94 +2055,94 @@
         <v>2035</v>
       </c>
       <c r="B17">
-        <v>252.3926285942676</v>
+        <v>249.4061572438759</v>
       </c>
       <c r="C17">
-        <v>13.75393600399752</v>
+        <v>12.20464358836315</v>
       </c>
       <c r="D17">
-        <v>126.6854902733556</v>
+        <v>125.5826992479481</v>
       </c>
       <c r="E17">
-        <v>7.212554576954148</v>
+        <v>7.485579397055638</v>
       </c>
       <c r="F17">
-        <v>125.707138320912</v>
+        <v>123.8234579959277</v>
       </c>
       <c r="G17">
-        <v>9.446911041703725</v>
+        <v>6.665569605679996</v>
       </c>
       <c r="H17">
-        <v>37.84575338966323</v>
+        <v>37.17059180999171</v>
       </c>
       <c r="I17">
-        <v>3.422036880724241</v>
+        <v>2.51649949505755</v>
       </c>
       <c r="J17">
-        <v>37.87256404004835</v>
+        <v>37.20284944799366</v>
       </c>
       <c r="K17">
-        <v>3.254425842582663</v>
+        <v>2.236523809282176</v>
       </c>
       <c r="L17">
-        <v>12.33184075338253</v>
+        <v>12.28588827615739</v>
       </c>
       <c r="M17">
-        <v>1.194746438162932</v>
+        <v>1.144644517107895</v>
       </c>
       <c r="N17">
-        <v>25.14384119648459</v>
+        <v>24.7605198154957</v>
       </c>
       <c r="O17">
-        <v>2.123665680467754</v>
+        <v>1.983596577773638</v>
       </c>
       <c r="P17">
-        <v>12.51313894133322</v>
+        <v>12.40360864628926</v>
       </c>
       <c r="Q17">
-        <v>1.04841199997707</v>
+        <v>0.9874791586065134</v>
       </c>
       <c r="R17">
-        <v>37.84575338966323</v>
+        <v>37.17059180999171</v>
       </c>
       <c r="S17">
-        <v>3.422036880724241</v>
+        <v>2.51649949505755</v>
       </c>
       <c r="T17">
-        <v>26.31950549566004</v>
+        <v>26.17649179689534</v>
       </c>
       <c r="U17">
-        <v>2.146116622049239</v>
+        <v>1.642203599035472</v>
       </c>
       <c r="V17">
-        <v>5.751183036167959</v>
+        <v>5.460083948873956</v>
       </c>
       <c r="W17">
-        <v>0.7396991459743012</v>
+        <v>0.6239074442181232</v>
       </c>
       <c r="X17">
-        <v>5.801875508220352</v>
+        <v>5.566273702224364</v>
       </c>
       <c r="Y17">
-        <v>0.7943681588744124</v>
+        <v>0.6359375630374285</v>
       </c>
       <c r="Z17">
-        <v>12.33184075338253</v>
+        <v>12.28588827615739</v>
       </c>
       <c r="AA17">
-        <v>1.194746438162932</v>
+        <v>1.144644517107895</v>
       </c>
       <c r="AB17">
-        <v>25.14384119648459</v>
+        <v>24.7605198154957</v>
       </c>
       <c r="AC17">
-        <v>2.123665680467754</v>
+        <v>1.983596577773638</v>
       </c>
       <c r="AD17">
-        <v>28.66069954198206</v>
+        <v>29.33435593745356</v>
       </c>
       <c r="AE17">
-        <v>1.381818955101963</v>
+        <v>1.421023086650693</v>
       </c>
     </row>
     <row r="18" spans="1:31">
@@ -2150,94 +2150,94 @@
         <v>2036</v>
       </c>
       <c r="B18">
-        <v>258.6581058099305</v>
+        <v>259.6919927244751</v>
       </c>
       <c r="C18">
-        <v>13.26700737573397</v>
+        <v>10.4995343490934</v>
       </c>
       <c r="D18">
-        <v>128.0364649514355</v>
+        <v>129.2803557218193</v>
       </c>
       <c r="E18">
-        <v>8.133443447914372</v>
+        <v>6.694712950547411</v>
       </c>
       <c r="F18">
-        <v>130.621640858495</v>
+        <v>130.4116370026559</v>
       </c>
       <c r="G18">
-        <v>8.30633699354189</v>
+        <v>7.093823053021899</v>
       </c>
       <c r="H18">
-        <v>39.40611767062969</v>
+        <v>39.05344733556723</v>
       </c>
       <c r="I18">
-        <v>2.905048771366013</v>
+        <v>2.494503725169233</v>
       </c>
       <c r="J18">
-        <v>38.83640025028139</v>
+        <v>38.93314264314068</v>
       </c>
       <c r="K18">
-        <v>2.854007702291298</v>
+        <v>2.630516498978689</v>
       </c>
       <c r="L18">
-        <v>13.19754854280539</v>
+        <v>13.14594298856377</v>
       </c>
       <c r="M18">
-        <v>1.141740503257863</v>
+        <v>1.012190305569828</v>
       </c>
       <c r="N18">
-        <v>26.07070388246726</v>
+        <v>26.15715627204534</v>
       </c>
       <c r="O18">
-        <v>1.879699988849146</v>
+        <v>2.026346074849433</v>
       </c>
       <c r="P18">
-        <v>13.11087051231128</v>
+        <v>13.12194776333885</v>
       </c>
       <c r="Q18">
-        <v>1.102299422209987</v>
+        <v>1.03243964962098</v>
       </c>
       <c r="R18">
-        <v>39.40611767062969</v>
+        <v>39.05344733556723</v>
       </c>
       <c r="S18">
-        <v>2.905048771366013</v>
+        <v>2.494503725169233</v>
       </c>
       <c r="T18">
-        <v>26.90085271680333</v>
+        <v>27.22930141388409</v>
       </c>
       <c r="U18">
-        <v>2.193166724462815</v>
+        <v>1.859965221024955</v>
       </c>
       <c r="V18">
-        <v>5.96741612617721</v>
+        <v>5.826715081026448</v>
       </c>
       <c r="W18">
-        <v>0.6957975798619251</v>
+        <v>0.715955973126676</v>
       </c>
       <c r="X18">
-        <v>5.968131407300851</v>
+        <v>5.877126148230148</v>
       </c>
       <c r="Y18">
-        <v>0.5786656214747021</v>
+        <v>0.6697087779661243</v>
       </c>
       <c r="Z18">
-        <v>13.19754854280539</v>
+        <v>13.14594298856377</v>
       </c>
       <c r="AA18">
-        <v>1.141740503257863</v>
+        <v>1.012190305569828</v>
       </c>
       <c r="AB18">
-        <v>26.07070388246726</v>
+        <v>26.15715627204534</v>
       </c>
       <c r="AC18">
-        <v>1.879699988849146</v>
+        <v>2.026346074849433</v>
       </c>
       <c r="AD18">
-        <v>30.80132938749169</v>
+        <v>30.99646291182011</v>
       </c>
       <c r="AE18">
-        <v>1.492468402434688</v>
+        <v>1.410994189303072</v>
       </c>
     </row>
     <row r="19" spans="1:31">
@@ -2245,94 +2245,94 @@
         <v>2037</v>
       </c>
       <c r="B19">
-        <v>269.4756893572456</v>
+        <v>269.9910549046571</v>
       </c>
       <c r="C19">
-        <v>12.76560850105919</v>
+        <v>13.51226042675681</v>
       </c>
       <c r="D19">
-        <v>135.2202483110052</v>
+        <v>134.9306678169997</v>
       </c>
       <c r="E19">
-        <v>8.642332270980875</v>
+        <v>7.857274564812534</v>
       </c>
       <c r="F19">
-        <v>134.2554410462403</v>
+        <v>135.0603870876574</v>
       </c>
       <c r="G19">
-        <v>6.753051451430523</v>
+        <v>8.382923670742811</v>
       </c>
       <c r="H19">
-        <v>40.25493165780733</v>
+        <v>40.29352118765351</v>
       </c>
       <c r="I19">
-        <v>2.350544725420522</v>
+        <v>2.8877156423686</v>
       </c>
       <c r="J19">
-        <v>40.22421193746814</v>
+        <v>40.37971291347199</v>
       </c>
       <c r="K19">
-        <v>2.562377778041068</v>
+        <v>3.492189665148056</v>
       </c>
       <c r="L19">
-        <v>13.48231723018475</v>
+        <v>13.65957566657123</v>
       </c>
       <c r="M19">
-        <v>0.8976722448455615</v>
+        <v>1.028174316502158</v>
       </c>
       <c r="N19">
-        <v>26.90521819202925</v>
+        <v>26.81237287035609</v>
       </c>
       <c r="O19">
-        <v>2.026310320701457</v>
+        <v>2.025466227461269</v>
       </c>
       <c r="P19">
-        <v>13.38876202875087</v>
+        <v>13.91520444960469</v>
       </c>
       <c r="Q19">
-        <v>1.141340987644304</v>
+        <v>1.154216389119472</v>
       </c>
       <c r="R19">
-        <v>40.25493165780733</v>
+        <v>40.29352118765351</v>
       </c>
       <c r="S19">
-        <v>2.350544725420522</v>
+        <v>2.8877156423686</v>
       </c>
       <c r="T19">
-        <v>28.02176025326649</v>
+        <v>28.27961534024166</v>
       </c>
       <c r="U19">
-        <v>2.166617783790343</v>
+        <v>2.659035680780191</v>
       </c>
       <c r="V19">
-        <v>6.110466933315581</v>
+        <v>6.028172896706641</v>
       </c>
       <c r="W19">
-        <v>0.5040963567265895</v>
+        <v>0.7075502045090742</v>
       </c>
       <c r="X19">
-        <v>6.091984750886077</v>
+        <v>6.071924676523686</v>
       </c>
       <c r="Y19">
-        <v>0.4799532532772439</v>
+        <v>0.7585008034504985</v>
       </c>
       <c r="Z19">
-        <v>13.48231723018475</v>
+        <v>13.65957566657123</v>
       </c>
       <c r="AA19">
-        <v>0.8976722448455615</v>
+        <v>1.028174316502158</v>
       </c>
       <c r="AB19">
-        <v>26.90521819202925</v>
+        <v>26.81237287035609</v>
       </c>
       <c r="AC19">
-        <v>2.026310320701457</v>
+        <v>2.025466227461269</v>
       </c>
       <c r="AD19">
-        <v>32.1114711158643</v>
+        <v>32.34738383504492</v>
       </c>
       <c r="AE19">
-        <v>1.586697590581737</v>
+        <v>1.460338983119478</v>
       </c>
     </row>
     <row r="20" spans="1:31">
@@ -2340,94 +2340,94 @@
         <v>2038</v>
       </c>
       <c r="B20">
-        <v>279.3373421017232</v>
+        <v>281.6554372506126</v>
       </c>
       <c r="C20">
-        <v>15.73740064407725</v>
+        <v>12.65215060532087</v>
       </c>
       <c r="D20">
-        <v>141.0461372254723</v>
+        <v>141.3291958063654</v>
       </c>
       <c r="E20">
-        <v>9.756221514738273</v>
+        <v>7.786356316402387</v>
       </c>
       <c r="F20">
-        <v>138.2912048762508</v>
+        <v>140.326241444247</v>
       </c>
       <c r="G20">
-        <v>8.738209548243667</v>
+        <v>8.558486577848235</v>
       </c>
       <c r="H20">
-        <v>41.53670724209366</v>
+        <v>42.37051625398775</v>
       </c>
       <c r="I20">
-        <v>3.544625601402149</v>
+        <v>3.316715001150367</v>
       </c>
       <c r="J20">
-        <v>41.80425113952093</v>
+        <v>41.83540016507322</v>
       </c>
       <c r="K20">
-        <v>3.391083189978238</v>
+        <v>2.719134680803285</v>
       </c>
       <c r="L20">
-        <v>13.52067390786488</v>
+        <v>14.12323925293383</v>
       </c>
       <c r="M20">
-        <v>1.246111645968557</v>
+        <v>1.418180161127612</v>
       </c>
       <c r="N20">
-        <v>27.68647301358285</v>
+        <v>27.86103191138854</v>
       </c>
       <c r="O20">
-        <v>1.898620795617301</v>
+        <v>1.988485515768988</v>
       </c>
       <c r="P20">
-        <v>13.74309957318855</v>
+        <v>14.13605386086364</v>
       </c>
       <c r="Q20">
-        <v>1.265231554255073</v>
+        <v>1.485739884603961</v>
       </c>
       <c r="R20">
-        <v>41.53670724209366</v>
+        <v>42.37051625398775</v>
       </c>
       <c r="S20">
-        <v>3.544625601402149</v>
+        <v>3.316715001150367</v>
       </c>
       <c r="T20">
-        <v>29.39195643647531</v>
+        <v>29.18112695810714</v>
       </c>
       <c r="U20">
-        <v>2.558977583667447</v>
+        <v>2.071480003143416</v>
       </c>
       <c r="V20">
-        <v>6.1241105721918</v>
+        <v>6.344836778730002</v>
       </c>
       <c r="W20">
-        <v>0.7221987274198942</v>
+        <v>0.6694921564762395</v>
       </c>
       <c r="X20">
-        <v>6.288184130853799</v>
+        <v>6.309436428236092</v>
       </c>
       <c r="Y20">
-        <v>0.723867837872305</v>
+        <v>0.6664104376955512</v>
       </c>
       <c r="Z20">
-        <v>13.52067390786488</v>
+        <v>14.12323925293383</v>
       </c>
       <c r="AA20">
-        <v>1.246111645968557</v>
+        <v>1.418180161127612</v>
       </c>
       <c r="AB20">
-        <v>27.68647301358285</v>
+        <v>27.86103191138854</v>
       </c>
       <c r="AC20">
-        <v>1.898620795617301</v>
+        <v>1.988485515768988</v>
       </c>
       <c r="AD20">
-        <v>33.47266392190529</v>
+        <v>33.75126330880285</v>
       </c>
       <c r="AE20">
-        <v>1.767156864419818</v>
+        <v>1.765698967897193</v>
       </c>
     </row>
     <row r="21" spans="1:31">
@@ -2435,94 +2435,94 @@
         <v>2039</v>
       </c>
       <c r="B21">
-        <v>288.5725310903781</v>
+        <v>290.8919845605562</v>
       </c>
       <c r="C21">
-        <v>12.97848735408828</v>
+        <v>12.58137561943287</v>
       </c>
       <c r="D21">
-        <v>144.3851681554447</v>
+        <v>145.4415193531615</v>
       </c>
       <c r="E21">
-        <v>7.545617962740461</v>
+        <v>7.676795328288339</v>
       </c>
       <c r="F21">
-        <v>144.1873629349334</v>
+        <v>145.4504652073946</v>
       </c>
       <c r="G21">
-        <v>8.483386422426731</v>
+        <v>8.690800045909208</v>
       </c>
       <c r="H21">
-        <v>43.47623415104587</v>
+        <v>43.71451687617818</v>
       </c>
       <c r="I21">
-        <v>3.337438598601046</v>
+        <v>3.08500096493805</v>
       </c>
       <c r="J21">
-        <v>43.18347144804882</v>
+        <v>43.61896946586469</v>
       </c>
       <c r="K21">
-        <v>2.980097671756825</v>
+        <v>3.345049064611401</v>
       </c>
       <c r="L21">
-        <v>14.39210447609536</v>
+        <v>14.47866067566899</v>
       </c>
       <c r="M21">
-        <v>1.232665862611602</v>
+        <v>1.067922079302543</v>
       </c>
       <c r="N21">
-        <v>28.73115656717914</v>
+        <v>29.12621280765818</v>
       </c>
       <c r="O21">
-        <v>1.952833574611439</v>
+        <v>2.101108241501171</v>
       </c>
       <c r="P21">
-        <v>14.40439629256414</v>
+        <v>14.51210538202463</v>
       </c>
       <c r="Q21">
-        <v>1.224225835812796</v>
+        <v>1.354898596038425</v>
       </c>
       <c r="R21">
-        <v>43.47623415104587</v>
+        <v>43.71451687617818</v>
       </c>
       <c r="S21">
-        <v>3.337438598601046</v>
+        <v>3.08500096493805</v>
       </c>
       <c r="T21">
-        <v>30.05598847386051</v>
+        <v>30.43762223787243</v>
       </c>
       <c r="U21">
-        <v>2.173872387896236</v>
+        <v>2.47696110413096</v>
       </c>
       <c r="V21">
-        <v>6.586201226257025</v>
+        <v>6.62837717250008</v>
       </c>
       <c r="W21">
-        <v>0.7277908030647346</v>
+        <v>0.7713132625677362</v>
       </c>
       <c r="X21">
-        <v>6.541281747931266</v>
+        <v>6.552970055492167</v>
       </c>
       <c r="Y21">
-        <v>0.7837316587308233</v>
+        <v>0.8305572932864788</v>
       </c>
       <c r="Z21">
-        <v>14.39210447609536</v>
+        <v>14.47866067566899</v>
       </c>
       <c r="AA21">
-        <v>1.232665862611602</v>
+        <v>1.067922079302543</v>
       </c>
       <c r="AB21">
-        <v>28.73115656717914</v>
+        <v>29.12621280765818</v>
       </c>
       <c r="AC21">
-        <v>1.952833574611439</v>
+        <v>2.101108241501171</v>
       </c>
       <c r="AD21">
-        <v>34.84934155448439</v>
+        <v>35.26513542598485</v>
       </c>
       <c r="AE21">
-        <v>1.558374448772369</v>
+        <v>1.39913276977437</v>
       </c>
     </row>
     <row r="22" spans="1:31">
@@ -2530,94 +2530,94 @@
         <v>2040</v>
       </c>
       <c r="B22">
-        <v>300.3431790166694</v>
+        <v>297.6940565426704</v>
       </c>
       <c r="C22">
-        <v>18.06898295140154</v>
+        <v>14.43939179042465</v>
       </c>
       <c r="D22">
-        <v>149.6309601850286</v>
+        <v>148.2978775799508</v>
       </c>
       <c r="E22">
-        <v>11.11627888808195</v>
+        <v>8.566745661928362</v>
       </c>
       <c r="F22">
-        <v>150.7122188316408</v>
+        <v>149.3961789627196</v>
       </c>
       <c r="G22">
-        <v>9.81260875991739</v>
+        <v>9.580669169901009</v>
       </c>
       <c r="H22">
-        <v>45.16384414210624</v>
+        <v>44.71269121900657</v>
       </c>
       <c r="I22">
-        <v>3.382135936228701</v>
+        <v>3.218584055788421</v>
       </c>
       <c r="J22">
-        <v>45.36525052589753</v>
+        <v>45.44245899230172</v>
       </c>
       <c r="K22">
-        <v>3.313697723831983</v>
+        <v>3.514994382601821</v>
       </c>
       <c r="L22">
-        <v>15.18677631212014</v>
+        <v>14.6899470572417</v>
       </c>
       <c r="M22">
-        <v>1.467066946376302</v>
+        <v>1.587818357177859</v>
       </c>
       <c r="N22">
-        <v>29.95402318501982</v>
+        <v>29.62935418558569</v>
       </c>
       <c r="O22">
-        <v>2.518679638227309</v>
+        <v>2.234209866368623</v>
       </c>
       <c r="P22">
-        <v>15.04232466649709</v>
+        <v>14.92172750858389</v>
       </c>
       <c r="Q22">
-        <v>1.458054523353026</v>
+        <v>1.320180534117118</v>
       </c>
       <c r="R22">
-        <v>45.16384414210624</v>
+        <v>44.71269121900657</v>
       </c>
       <c r="S22">
-        <v>3.382135936228701</v>
+        <v>3.218584055788421</v>
       </c>
       <c r="T22">
-        <v>31.81228215479011</v>
+        <v>31.96114340568009</v>
       </c>
       <c r="U22">
-        <v>2.736731449797407</v>
+        <v>2.83001057630086</v>
       </c>
       <c r="V22">
-        <v>6.739112569650174</v>
+        <v>6.681455903492053</v>
       </c>
       <c r="W22">
-        <v>0.7979414889739638</v>
+        <v>0.8554374771827594</v>
       </c>
       <c r="X22">
-        <v>6.81385580145724</v>
+        <v>6.799859683129557</v>
       </c>
       <c r="Y22">
-        <v>0.7398791915519396</v>
+        <v>0.8987882587126459</v>
       </c>
       <c r="Z22">
-        <v>15.18677631212014</v>
+        <v>14.6899470572417</v>
       </c>
       <c r="AA22">
-        <v>1.467066946376302</v>
+        <v>1.587818357177859</v>
       </c>
       <c r="AB22">
-        <v>29.95402318501982</v>
+        <v>29.62935418558569</v>
       </c>
       <c r="AC22">
-        <v>2.518679638227309</v>
+        <v>2.234209866368623</v>
       </c>
       <c r="AD22">
-        <v>35.9622227058607</v>
+        <v>36.40703505016783</v>
       </c>
       <c r="AE22">
-        <v>2.002671071566923</v>
+        <v>1.809521333674022</v>
       </c>
     </row>
   </sheetData>
@@ -2700,64 +2700,64 @@
         <v>2020</v>
       </c>
       <c r="B2">
-        <v>50.0336253681736</v>
+        <v>50.44158908528594</v>
       </c>
       <c r="C2">
-        <v>2.584793726329579</v>
+        <v>3.172779106219868</v>
       </c>
       <c r="D2">
-        <v>50.0336253681736</v>
+        <v>50.44158908528594</v>
       </c>
       <c r="E2">
-        <v>2.584793726329579</v>
+        <v>3.172779106219868</v>
       </c>
       <c r="F2">
-        <v>5.070429605468534</v>
+        <v>5.067678417852673</v>
       </c>
       <c r="G2">
-        <v>0.4313717702867806</v>
+        <v>0.4890762736815</v>
       </c>
       <c r="H2">
-        <v>5.070429605468534</v>
+        <v>5.067678417852673</v>
       </c>
       <c r="I2">
-        <v>0.4313717702867806</v>
+        <v>0.4890762736815</v>
       </c>
       <c r="J2">
-        <v>25.7179772492961</v>
+        <v>25.87539858963754</v>
       </c>
       <c r="K2">
-        <v>1.439310435570558</v>
+        <v>1.828869476897282</v>
       </c>
       <c r="L2">
-        <v>25.7179772492961</v>
+        <v>25.87539858963754</v>
       </c>
       <c r="M2">
-        <v>1.439310435570558</v>
+        <v>1.828869476897282</v>
       </c>
       <c r="N2">
-        <v>17.54552101399409</v>
+        <v>17.49692473981849</v>
       </c>
       <c r="O2">
-        <v>1.041564990890891</v>
+        <v>1.346917890275257</v>
       </c>
       <c r="P2">
-        <v>17.54552101399409</v>
+        <v>17.49692473981849</v>
       </c>
       <c r="Q2">
-        <v>1.041564990890891</v>
+        <v>1.346917890275257</v>
       </c>
       <c r="R2">
-        <v>2.272833331896503</v>
+        <v>2.279539396887054</v>
       </c>
       <c r="S2">
-        <v>0.2592255986680573</v>
+        <v>0.2526553750825796</v>
       </c>
       <c r="T2">
-        <v>2.272833331896503</v>
+        <v>2.279539396887054</v>
       </c>
       <c r="U2">
-        <v>0.2592255986680573</v>
+        <v>0.2526553750825796</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -2765,64 +2765,64 @@
         <v>2021</v>
       </c>
       <c r="B3">
-        <v>54.88528218102728</v>
+        <v>55.12774569178221</v>
       </c>
       <c r="C3">
-        <v>3.814345276896495</v>
+        <v>3.089053355445273</v>
       </c>
       <c r="D3">
-        <v>104.9189075492009</v>
+        <v>105.5693347770681</v>
       </c>
       <c r="E3">
-        <v>4.441884366710648</v>
+        <v>4.420506644319389</v>
       </c>
       <c r="F3">
-        <v>5.478252316188206</v>
+        <v>5.523696989800705</v>
       </c>
       <c r="G3">
-        <v>0.4238342256434968</v>
+        <v>0.4330877817063417</v>
       </c>
       <c r="H3">
-        <v>10.54868192165674</v>
+        <v>10.59137540765338</v>
       </c>
       <c r="I3">
-        <v>0.5591689692416502</v>
+        <v>0.6844881159331387</v>
       </c>
       <c r="J3">
-        <v>19.80848524622133</v>
+        <v>19.93055415114572</v>
       </c>
       <c r="K3">
-        <v>2.090006087703874</v>
+        <v>2.052498904565295</v>
       </c>
       <c r="L3">
-        <v>45.52646249551743</v>
+        <v>45.80595274078327</v>
       </c>
       <c r="M3">
-        <v>2.443723809720753</v>
+        <v>2.696215456323932</v>
       </c>
       <c r="N3">
-        <v>27.06171790269768</v>
+        <v>27.27468392322526</v>
       </c>
       <c r="O3">
-        <v>1.318339172594312</v>
+        <v>1.428678765943064</v>
       </c>
       <c r="P3">
-        <v>44.60723891669177</v>
+        <v>44.77160866304375</v>
       </c>
       <c r="Q3">
-        <v>1.640660958929644</v>
+        <v>1.92487650161046</v>
       </c>
       <c r="R3">
-        <v>2.473460302117485</v>
+        <v>2.52128462902098</v>
       </c>
       <c r="S3">
-        <v>0.2705255710472279</v>
+        <v>0.2730655880562716</v>
       </c>
       <c r="T3">
-        <v>4.746293634013987</v>
+        <v>4.800824025908032</v>
       </c>
       <c r="U3">
-        <v>0.3914839743864463</v>
+        <v>0.3808887960419303</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -2830,64 +2830,64 @@
         <v>2022</v>
       </c>
       <c r="B4">
-        <v>60.39157475059026</v>
+        <v>59.87691742482658</v>
       </c>
       <c r="C4">
-        <v>3.08948858569708</v>
+        <v>2.882371914159329</v>
       </c>
       <c r="D4">
-        <v>165.3104822997911</v>
+        <v>165.4462522018947</v>
       </c>
       <c r="E4">
-        <v>5.632496431813572</v>
+        <v>5.138485769981102</v>
       </c>
       <c r="F4">
-        <v>6.043360889847785</v>
+        <v>6.055781140158704</v>
       </c>
       <c r="G4">
-        <v>0.5353084161761348</v>
+        <v>0.4761421323177711</v>
       </c>
       <c r="H4">
-        <v>16.59204281150452</v>
+        <v>16.64715654781208</v>
       </c>
       <c r="I4">
-        <v>0.7205241366432036</v>
+        <v>0.7009276336261926</v>
       </c>
       <c r="J4">
-        <v>19.58512968620792</v>
+        <v>18.59634259840827</v>
       </c>
       <c r="K4">
-        <v>2.136781914006488</v>
+        <v>2.391167398120271</v>
       </c>
       <c r="L4">
-        <v>65.11159218172534</v>
+        <v>64.40229533919155</v>
       </c>
       <c r="M4">
-        <v>3.350998032764519</v>
+        <v>3.296339695067296</v>
       </c>
       <c r="N4">
-        <v>32.51196789635061</v>
+        <v>32.8242729581167</v>
       </c>
       <c r="O4">
-        <v>1.254773093533074</v>
+        <v>1.398954541610942</v>
       </c>
       <c r="P4">
-        <v>77.1192068130424</v>
+        <v>77.59588162116047</v>
       </c>
       <c r="Q4">
-        <v>2.143399094025114</v>
+        <v>2.158923171361854</v>
       </c>
       <c r="R4">
-        <v>2.643163290269645</v>
+        <v>2.744843412489206</v>
       </c>
       <c r="S4">
-        <v>0.3186622331203489</v>
+        <v>0.3042888853399384</v>
       </c>
       <c r="T4">
-        <v>7.389456924283628</v>
+        <v>7.545667438397236</v>
       </c>
       <c r="U4">
-        <v>0.5201165326425944</v>
+        <v>0.4221597719082749</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -2895,64 +2895,64 @@
         <v>2023</v>
       </c>
       <c r="B5">
-        <v>65.37674470455526</v>
+        <v>64.54549619407467</v>
       </c>
       <c r="C5">
-        <v>4.383919590805982</v>
+        <v>4.200496060684776</v>
       </c>
       <c r="D5">
-        <v>230.6872270043464</v>
+        <v>229.9917483959694</v>
       </c>
       <c r="E5">
-        <v>6.726284056123465</v>
+        <v>5.169466022324197</v>
       </c>
       <c r="F5">
-        <v>6.613509858810958</v>
+        <v>6.350646139837908</v>
       </c>
       <c r="G5">
-        <v>0.6497249480812332</v>
+        <v>0.524814554904839</v>
       </c>
       <c r="H5">
-        <v>23.20555267031549</v>
+        <v>22.99780268764999</v>
       </c>
       <c r="I5">
-        <v>1.035639557348036</v>
+        <v>0.8538930271747295</v>
       </c>
       <c r="J5">
-        <v>19.56565486480785</v>
+        <v>18.7410613112545</v>
       </c>
       <c r="K5">
-        <v>3.174396218383766</v>
+        <v>2.245216593420156</v>
       </c>
       <c r="L5">
-        <v>84.6772470465332</v>
+        <v>83.14335665044604</v>
       </c>
       <c r="M5">
-        <v>4.401836859227135</v>
+        <v>3.865528304676493</v>
       </c>
       <c r="N5">
-        <v>36.6521596816042</v>
+        <v>36.09041072439299</v>
       </c>
       <c r="O5">
-        <v>1.791718059454783</v>
+        <v>1.878217364801057</v>
       </c>
       <c r="P5">
-        <v>113.7713664946466</v>
+        <v>113.6862923455535</v>
       </c>
       <c r="Q5">
-        <v>2.768479850396493</v>
+        <v>3.003690005137176</v>
       </c>
       <c r="R5">
-        <v>2.997340920756467</v>
+        <v>2.917104099896993</v>
       </c>
       <c r="S5">
-        <v>0.3057035537517128</v>
+        <v>0.2734859159585566</v>
       </c>
       <c r="T5">
-        <v>10.3867978450401</v>
+        <v>10.46277153829423</v>
       </c>
       <c r="U5">
-        <v>0.6128791537441828</v>
+        <v>0.5256499464764441</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -2960,64 +2960,64 @@
         <v>2024</v>
       </c>
       <c r="B6">
-        <v>69.22265045851476</v>
+        <v>69.76851365200785</v>
       </c>
       <c r="C6">
-        <v>3.861725991315873</v>
+        <v>4.104393661440275</v>
       </c>
       <c r="D6">
-        <v>299.9098774628612</v>
+        <v>299.7602620479773</v>
       </c>
       <c r="E6">
-        <v>6.929733264629414</v>
+        <v>6.308183724256041</v>
       </c>
       <c r="F6">
-        <v>6.9335029277647</v>
+        <v>7.170375706141776</v>
       </c>
       <c r="G6">
-        <v>0.6194686978181358</v>
+        <v>0.6604656735860782</v>
       </c>
       <c r="H6">
-        <v>30.13905559808018</v>
+        <v>30.16817839379176</v>
       </c>
       <c r="I6">
-        <v>1.225638544830604</v>
+        <v>1.113761627200664</v>
       </c>
       <c r="J6">
-        <v>19.81573078911387</v>
+        <v>20.43819570559436</v>
       </c>
       <c r="K6">
-        <v>2.621646207157242</v>
+        <v>2.862838365096098</v>
       </c>
       <c r="L6">
-        <v>104.492977835647</v>
+        <v>103.5815523560404</v>
       </c>
       <c r="M6">
-        <v>5.210652874996104</v>
+        <v>4.363575284969275</v>
       </c>
       <c r="N6">
-        <v>39.43262456341371</v>
+        <v>40.04607080334216</v>
       </c>
       <c r="O6">
-        <v>1.622670594048049</v>
+        <v>1.907813716830349</v>
       </c>
       <c r="P6">
-        <v>153.2039910580603</v>
+        <v>153.7323631488956</v>
       </c>
       <c r="Q6">
-        <v>3.189747669016322</v>
+        <v>3.117947027473501</v>
       </c>
       <c r="R6">
-        <v>3.07367214562526</v>
+        <v>3.143857808387595</v>
       </c>
       <c r="S6">
-        <v>0.3624294001673468</v>
+        <v>0.3385378146377007</v>
       </c>
       <c r="T6">
-        <v>13.46046999066536</v>
+        <v>13.60662934668183</v>
       </c>
       <c r="U6">
-        <v>0.6776169420101651</v>
+        <v>0.5780057197679813</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -3025,64 +3025,64 @@
         <v>2025</v>
       </c>
       <c r="B7">
-        <v>74.823240145325</v>
+        <v>75.63193522600477</v>
       </c>
       <c r="C7">
-        <v>4.561285773060686</v>
+        <v>4.666109819758304</v>
       </c>
       <c r="D7">
-        <v>374.7331176081862</v>
+        <v>375.392197273982</v>
       </c>
       <c r="E7">
-        <v>8.38591506525527</v>
+        <v>7.548320986227053</v>
       </c>
       <c r="F7">
-        <v>7.446763692820443</v>
+        <v>7.612913347691386</v>
       </c>
       <c r="G7">
-        <v>0.648819439345996</v>
+        <v>0.5799454231828362</v>
       </c>
       <c r="H7">
-        <v>37.58581929090062</v>
+        <v>37.78109174148313</v>
       </c>
       <c r="I7">
-        <v>1.347739241548284</v>
+        <v>1.337131249355129</v>
       </c>
       <c r="J7">
-        <v>20.95158678253589</v>
+        <v>21.43755433564818</v>
       </c>
       <c r="K7">
-        <v>2.580118111349082</v>
+        <v>2.63235158014535</v>
       </c>
       <c r="L7">
-        <v>125.4445646181829</v>
+        <v>125.0191066916886</v>
       </c>
       <c r="M7">
-        <v>5.88594542212585</v>
+        <v>5.124464548339563</v>
       </c>
       <c r="N7">
-        <v>42.96711035253136</v>
+        <v>42.99794835512343</v>
       </c>
       <c r="O7">
-        <v>2.072186176845936</v>
+        <v>1.769902011715402</v>
       </c>
       <c r="P7">
-        <v>196.1711014105916</v>
+        <v>196.7303115040191</v>
       </c>
       <c r="Q7">
-        <v>4.207005339343267</v>
+        <v>3.839328575186234</v>
       </c>
       <c r="R7">
-        <v>3.36924549722484</v>
+        <v>3.457090110585895</v>
       </c>
       <c r="S7">
-        <v>0.4262868247239823</v>
+        <v>0.3730858980846808</v>
       </c>
       <c r="T7">
-        <v>16.8297154878902</v>
+        <v>17.06371945726772</v>
       </c>
       <c r="U7">
-        <v>0.7638937489848806</v>
+        <v>0.6620353627977723</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -3090,64 +3090,64 @@
         <v>2026</v>
       </c>
       <c r="B8">
-        <v>79.60134766598752</v>
+        <v>79.52613223862038</v>
       </c>
       <c r="C8">
-        <v>4.317286795918008</v>
+        <v>3.927581726313675</v>
       </c>
       <c r="D8">
-        <v>454.3344652741736</v>
+        <v>454.9183295126025</v>
       </c>
       <c r="E8">
-        <v>9.130281221032865</v>
+        <v>8.047516509520291</v>
       </c>
       <c r="F8">
-        <v>8.137474386801449</v>
+        <v>8.122238904312242</v>
       </c>
       <c r="G8">
-        <v>0.6179138987464504</v>
+        <v>0.661797949560782</v>
       </c>
       <c r="H8">
-        <v>45.72329367770207</v>
+        <v>45.90333064579539</v>
       </c>
       <c r="I8">
-        <v>1.470672485716542</v>
+        <v>1.45655523805895</v>
       </c>
       <c r="J8">
-        <v>22.41387179863164</v>
+        <v>22.86895466973421</v>
       </c>
       <c r="K8">
-        <v>2.584897599376977</v>
+        <v>2.909906964382201</v>
       </c>
       <c r="L8">
-        <v>147.8584364168146</v>
+        <v>147.8880613614228</v>
       </c>
       <c r="M8">
-        <v>5.784909601084522</v>
+        <v>6.047336607525363</v>
       </c>
       <c r="N8">
-        <v>46.05433311652032</v>
+        <v>45.97090805446283</v>
       </c>
       <c r="O8">
-        <v>2.370678036952516</v>
+        <v>1.969240398593954</v>
       </c>
       <c r="P8">
-        <v>242.225434527112</v>
+        <v>242.7012195584818</v>
       </c>
       <c r="Q8">
-        <v>4.902034290697125</v>
+        <v>3.773108827162911</v>
       </c>
       <c r="R8">
-        <v>3.543110094193791</v>
+        <v>3.676220483251925</v>
       </c>
       <c r="S8">
-        <v>0.471740909670426</v>
+        <v>0.4701527565060802</v>
       </c>
       <c r="T8">
-        <v>20.37282558208399</v>
+        <v>20.73993994051964</v>
       </c>
       <c r="U8">
-        <v>0.827867189054576</v>
+        <v>0.7337244202662366</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -3155,64 +3155,64 @@
         <v>2027</v>
       </c>
       <c r="B9">
-        <v>84.79233301725377</v>
+        <v>84.82974752655393</v>
       </c>
       <c r="C9">
-        <v>5.35509961237626</v>
+        <v>5.281882919770375</v>
       </c>
       <c r="D9">
-        <v>539.1267982914273</v>
+        <v>539.7480770391564</v>
       </c>
       <c r="E9">
-        <v>10.45624200093057</v>
+        <v>9.413387657485472</v>
       </c>
       <c r="F9">
-        <v>8.491675865601144</v>
+        <v>8.581564321308763</v>
       </c>
       <c r="G9">
-        <v>0.735242053870342</v>
+        <v>0.7677243825372798</v>
       </c>
       <c r="H9">
-        <v>54.21496954330321</v>
+        <v>54.48489496710417</v>
       </c>
       <c r="I9">
-        <v>1.658077929334075</v>
+        <v>1.651679521937299</v>
       </c>
       <c r="J9">
-        <v>23.50092112945403</v>
+        <v>23.85395888053694</v>
       </c>
       <c r="K9">
-        <v>2.833672042518555</v>
+        <v>3.230385693187841</v>
       </c>
       <c r="L9">
-        <v>171.3593575462685</v>
+        <v>171.7420202419598</v>
       </c>
       <c r="M9">
-        <v>6.896901959636407</v>
+        <v>6.849939690542467</v>
       </c>
       <c r="N9">
-        <v>48.91985964564018</v>
+        <v>49.00152945634431</v>
       </c>
       <c r="O9">
-        <v>1.790101230797801</v>
+        <v>1.959350098302506</v>
       </c>
       <c r="P9">
-        <v>291.1452941727521</v>
+        <v>291.7027490148262</v>
       </c>
       <c r="Q9">
-        <v>5.525998123949819</v>
+        <v>4.094517593572295</v>
       </c>
       <c r="R9">
-        <v>3.83119667310576</v>
+        <v>3.741436979936249</v>
       </c>
       <c r="S9">
-        <v>0.4549782963768986</v>
+        <v>0.4136064781379423</v>
       </c>
       <c r="T9">
-        <v>24.20402225518976</v>
+        <v>24.48137692045589</v>
       </c>
       <c r="U9">
-        <v>1.028644023430529</v>
+        <v>0.8402007698527324</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -3220,64 +3220,64 @@
         <v>2028</v>
       </c>
       <c r="B10">
-        <v>89.99151951960113</v>
+        <v>90.8688776437523</v>
       </c>
       <c r="C10">
-        <v>5.592691907133609</v>
+        <v>4.832816907420847</v>
       </c>
       <c r="D10">
-        <v>629.1183178110285</v>
+        <v>630.6169546829085</v>
       </c>
       <c r="E10">
-        <v>11.65714452387685</v>
+        <v>10.46160501646553</v>
       </c>
       <c r="F10">
-        <v>8.909833186054932</v>
+        <v>9.101750332958186</v>
       </c>
       <c r="G10">
-        <v>0.6427649747902198</v>
+        <v>0.8478657497424956</v>
       </c>
       <c r="H10">
-        <v>63.12480272935814</v>
+        <v>63.58664530006236</v>
       </c>
       <c r="I10">
-        <v>1.730828885580657</v>
+        <v>1.511132261817062</v>
       </c>
       <c r="J10">
-        <v>25.15923379654071</v>
+        <v>25.45517308710738</v>
       </c>
       <c r="K10">
-        <v>3.012771809192495</v>
+        <v>4.032865378312207</v>
       </c>
       <c r="L10">
-        <v>196.5185913428093</v>
+        <v>197.1971933290671</v>
       </c>
       <c r="M10">
-        <v>7.760716053665978</v>
+        <v>8.186005723232899</v>
       </c>
       <c r="N10">
-        <v>51.58508000104987</v>
+        <v>52.07097476517154</v>
       </c>
       <c r="O10">
-        <v>1.855191115052647</v>
+        <v>2.441105058925723</v>
       </c>
       <c r="P10">
-        <v>342.730374173802</v>
+        <v>343.7737237799978</v>
       </c>
       <c r="Q10">
-        <v>5.645697449393573</v>
+        <v>3.971909359978328</v>
       </c>
       <c r="R10">
-        <v>3.947189715503322</v>
+        <v>4.115633573727396</v>
       </c>
       <c r="S10">
-        <v>0.4577298977062312</v>
+        <v>0.5186380403979541</v>
       </c>
       <c r="T10">
-        <v>28.15121197069307</v>
+        <v>28.59701049418329</v>
       </c>
       <c r="U10">
-        <v>1.212365728360612</v>
+        <v>1.02642706094995</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -3285,64 +3285,64 @@
         <v>2029</v>
       </c>
       <c r="B11">
-        <v>96.20086273848023</v>
+        <v>95.5494168004286</v>
       </c>
       <c r="C11">
-        <v>6.307482570279485</v>
+        <v>5.1327652454676</v>
       </c>
       <c r="D11">
-        <v>725.3191805495089</v>
+        <v>726.1663714833372</v>
       </c>
       <c r="E11">
-        <v>13.81446470871512</v>
+        <v>11.12149034631081</v>
       </c>
       <c r="F11">
-        <v>9.422647751762211</v>
+        <v>9.57661445666537</v>
       </c>
       <c r="G11">
-        <v>1.026958380259368</v>
+        <v>0.8189483270036041</v>
       </c>
       <c r="H11">
-        <v>72.54745048112038</v>
+        <v>73.16325975672767</v>
       </c>
       <c r="I11">
-        <v>2.040406771134653</v>
+        <v>1.79358314143571</v>
       </c>
       <c r="J11">
-        <v>25.82224973728584</v>
+        <v>26.55256441447451</v>
       </c>
       <c r="K11">
-        <v>3.088419040592255</v>
+        <v>3.674626190753934</v>
       </c>
       <c r="L11">
-        <v>222.3408410800952</v>
+        <v>223.7497577435416</v>
       </c>
       <c r="M11">
-        <v>8.170085347770872</v>
+        <v>8.869362890389493</v>
       </c>
       <c r="N11">
-        <v>54.69152825840616</v>
+        <v>55.35217742019576</v>
       </c>
       <c r="O11">
-        <v>2.532866978470969</v>
+        <v>2.548459151574294</v>
       </c>
       <c r="P11">
-        <v>397.4219024322081</v>
+        <v>399.1259012001935</v>
       </c>
       <c r="Q11">
-        <v>5.955482442457446</v>
+        <v>5.442337201822756</v>
       </c>
       <c r="R11">
-        <v>4.380990771279371</v>
+        <v>4.275744796027674</v>
       </c>
       <c r="S11">
-        <v>0.454098511441366</v>
+        <v>0.4744391465900309</v>
       </c>
       <c r="T11">
-        <v>32.53220274197245</v>
+        <v>32.87275529021095</v>
       </c>
       <c r="U11">
-        <v>1.284671891911388</v>
+        <v>1.197207005861579</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -3350,64 +3350,64 @@
         <v>2030</v>
       </c>
       <c r="B12">
-        <v>99.49319704361611</v>
+        <v>100.0165314198888</v>
       </c>
       <c r="C12">
-        <v>4.651662286092257</v>
+        <v>6.989704136375872</v>
       </c>
       <c r="D12">
-        <v>824.812377593125</v>
+        <v>826.1829029032258</v>
       </c>
       <c r="E12">
-        <v>14.96217728664171</v>
+        <v>14.29735016885977</v>
       </c>
       <c r="F12">
-        <v>10.17252913743659</v>
+        <v>9.973911033184528</v>
       </c>
       <c r="G12">
-        <v>0.7512832979047136</v>
+        <v>0.8951027444367129</v>
       </c>
       <c r="H12">
-        <v>82.71997961855693</v>
+        <v>83.13717078991223</v>
       </c>
       <c r="I12">
-        <v>2.24868896324348</v>
+        <v>1.88057665375376</v>
       </c>
       <c r="J12">
-        <v>27.75238422696063</v>
+        <v>27.72074438159151</v>
       </c>
       <c r="K12">
-        <v>3.504216695103415</v>
+        <v>4.022855894396981</v>
       </c>
       <c r="L12">
-        <v>250.0932253070558</v>
+        <v>251.4705021251332</v>
       </c>
       <c r="M12">
-        <v>9.521484763062675</v>
+        <v>10.43199399337385</v>
       </c>
       <c r="N12">
-        <v>57.99773013712204</v>
+        <v>58.0624326113443</v>
       </c>
       <c r="O12">
-        <v>2.326198942388799</v>
+        <v>2.369814149914797</v>
       </c>
       <c r="P12">
-        <v>455.4196325693302</v>
+        <v>457.1883338115379</v>
       </c>
       <c r="Q12">
-        <v>6.819226109570339</v>
+        <v>6.072785068474686</v>
       </c>
       <c r="R12">
-        <v>4.467768908305294</v>
+        <v>4.56583375462966</v>
       </c>
       <c r="S12">
-        <v>0.5188156163577634</v>
+        <v>0.478100352044337</v>
       </c>
       <c r="T12">
-        <v>36.99997165027775</v>
+        <v>37.43858904484063</v>
       </c>
       <c r="U12">
-        <v>1.521957539457721</v>
+        <v>1.41153275171783</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -3415,64 +3415,64 @@
         <v>2031</v>
       </c>
       <c r="B13">
-        <v>5.034852664688315</v>
+        <v>5.056506560749505</v>
       </c>
       <c r="C13">
-        <v>0.3215102335926248</v>
+        <v>0.3158310320702611</v>
       </c>
       <c r="D13">
-        <v>829.8472302578134</v>
+        <v>831.2394094639756</v>
       </c>
       <c r="E13">
-        <v>14.93481226545649</v>
+        <v>14.30348069734862</v>
       </c>
       <c r="F13">
-        <v>0.488634129918365</v>
+        <v>0.4995177460269995</v>
       </c>
       <c r="G13">
-        <v>0.04022006517907811</v>
+        <v>0.04915520185644703</v>
       </c>
       <c r="H13">
-        <v>83.20861374847533</v>
+        <v>83.63668853593923</v>
       </c>
       <c r="I13">
-        <v>2.245876549250243</v>
+        <v>1.882782031587203</v>
       </c>
       <c r="J13">
-        <v>-22.21744361845234</v>
+        <v>-22.13091257034521</v>
       </c>
       <c r="K13">
-        <v>1.121016707083125</v>
+        <v>1.104924448694028</v>
       </c>
       <c r="L13">
-        <v>227.8757816886035</v>
+        <v>229.3395895547879</v>
       </c>
       <c r="M13">
-        <v>9.453718018167713</v>
+        <v>10.5080203902913</v>
       </c>
       <c r="N13">
-        <v>26.49287186543965</v>
+        <v>26.42334697254434</v>
       </c>
       <c r="O13">
-        <v>1.149558905130166</v>
+        <v>1.059832172391634</v>
       </c>
       <c r="P13">
-        <v>481.9125044347697</v>
+        <v>483.611680784082</v>
       </c>
       <c r="Q13">
-        <v>6.882850475017121</v>
+        <v>6.195885633645605</v>
       </c>
       <c r="R13">
-        <v>0.232107828571531</v>
+        <v>0.2245831050265253</v>
       </c>
       <c r="S13">
-        <v>0.02474247993098665</v>
+        <v>0.0277148201560915</v>
       </c>
       <c r="T13">
-        <v>37.23207947884926</v>
+        <v>37.66317214986716</v>
       </c>
       <c r="U13">
-        <v>1.525468578520147</v>
+        <v>1.415155135423994</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -3480,64 +3480,64 @@
         <v>2032</v>
       </c>
       <c r="B14">
-        <v>110.1881756583443</v>
+        <v>109.683813413783</v>
       </c>
       <c r="C14">
-        <v>6.574460869264921</v>
+        <v>6.297735857341409</v>
       </c>
       <c r="D14">
-        <v>940.0354059161577</v>
+        <v>940.9232228777587</v>
       </c>
       <c r="E14">
-        <v>16.5184135063484</v>
+        <v>15.84138263924368</v>
       </c>
       <c r="F14">
-        <v>11.02686540346899</v>
+        <v>11.05870664588856</v>
       </c>
       <c r="G14">
-        <v>0.7655752384803146</v>
+        <v>0.7741773495376801</v>
       </c>
       <c r="H14">
-        <v>94.23547915194429</v>
+        <v>94.69539518182779</v>
       </c>
       <c r="I14">
-        <v>2.44248654190118</v>
+        <v>2.091880427103186</v>
       </c>
       <c r="J14">
-        <v>46.07857607556789</v>
+        <v>46.68877440009543</v>
       </c>
       <c r="K14">
-        <v>4.013998452338887</v>
+        <v>3.909821676541028</v>
       </c>
       <c r="L14">
-        <v>273.9543577641713</v>
+        <v>276.0283639548833</v>
       </c>
       <c r="M14">
-        <v>9.904128924359311</v>
+        <v>11.15507128519547</v>
       </c>
       <c r="N14">
-        <v>47.18485157843545</v>
+        <v>47.54292763772627</v>
       </c>
       <c r="O14">
-        <v>2.510007412038156</v>
+        <v>2.690580023116248</v>
       </c>
       <c r="P14">
-        <v>529.0973560132053</v>
+        <v>531.1546084218085</v>
       </c>
       <c r="Q14">
-        <v>7.719189841688086</v>
+        <v>6.247290526925278</v>
       </c>
       <c r="R14">
-        <v>4.846666047482144</v>
+        <v>4.884581994969846</v>
       </c>
       <c r="S14">
-        <v>0.528172138871399</v>
+        <v>0.5643610524964381</v>
       </c>
       <c r="T14">
-        <v>42.0787455263314</v>
+        <v>42.54775414483699</v>
       </c>
       <c r="U14">
-        <v>1.616926139828833</v>
+        <v>1.545161400634748</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -3545,64 +3545,64 @@
         <v>2033</v>
       </c>
       <c r="B15">
-        <v>114.1698285244135</v>
+        <v>114.8695081490967</v>
       </c>
       <c r="C15">
-        <v>6.115110142787806</v>
+        <v>7.938562720369432</v>
       </c>
       <c r="D15">
-        <v>1054.205234440571</v>
+        <v>1055.792731026855</v>
       </c>
       <c r="E15">
-        <v>18.62930344606055</v>
+        <v>16.82958564363878</v>
       </c>
       <c r="F15">
-        <v>11.38775720760655</v>
+        <v>11.679496785561</v>
       </c>
       <c r="G15">
-        <v>1.179878481142806</v>
+        <v>1.032824024613885</v>
       </c>
       <c r="H15">
-        <v>105.6232363595509</v>
+        <v>106.3748919673888</v>
       </c>
       <c r="I15">
-        <v>2.684244921536594</v>
+        <v>2.303987535941834</v>
       </c>
       <c r="J15">
-        <v>37.22325865944843</v>
+        <v>36.53166329298143</v>
       </c>
       <c r="K15">
-        <v>3.51881642054896</v>
+        <v>4.786483089030118</v>
       </c>
       <c r="L15">
-        <v>311.1776164236198</v>
+        <v>312.5600272478649</v>
       </c>
       <c r="M15">
-        <v>10.76790653804124</v>
+        <v>11.64065280672449</v>
       </c>
       <c r="N15">
-        <v>60.63742472078577</v>
+        <v>61.52432245859804</v>
       </c>
       <c r="O15">
-        <v>3.153998878065759</v>
+        <v>2.777649686268429</v>
       </c>
       <c r="P15">
-        <v>589.7347807339912</v>
+        <v>592.6789308804064</v>
       </c>
       <c r="Q15">
-        <v>9.321762869015616</v>
+        <v>6.435476989740825</v>
       </c>
       <c r="R15">
-        <v>5.168647304309602</v>
+        <v>5.148722431958074</v>
       </c>
       <c r="S15">
-        <v>0.6661360380584068</v>
+        <v>0.6001444163226841</v>
       </c>
       <c r="T15">
-        <v>47.24739283064102</v>
+        <v>47.69647657679509</v>
       </c>
       <c r="U15">
-        <v>1.767718930570887</v>
+        <v>1.631075499390749</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -3610,64 +3610,64 @@
         <v>2034</v>
       </c>
       <c r="B16">
-        <v>120.9115785252184</v>
+        <v>120.6701035268929</v>
       </c>
       <c r="C16">
-        <v>6.292735000800104</v>
+        <v>7.9929407324275</v>
       </c>
       <c r="D16">
-        <v>1175.11681296579</v>
+        <v>1176.462834553748</v>
       </c>
       <c r="E16">
-        <v>18.95376866996054</v>
+        <v>17.73935562412781</v>
       </c>
       <c r="F16">
-        <v>11.90734008782399</v>
+        <v>12.15260780959685</v>
       </c>
       <c r="G16">
-        <v>1.040214907440805</v>
+        <v>0.8936618992337902</v>
       </c>
       <c r="H16">
-        <v>117.5305764473748</v>
+        <v>118.5274997769857</v>
       </c>
       <c r="I16">
-        <v>3.070436385152675</v>
+        <v>2.673868534805953</v>
       </c>
       <c r="J16">
-        <v>35.60051235859834</v>
+        <v>34.96689864768744</v>
       </c>
       <c r="K16">
-        <v>4.375155213745185</v>
+        <v>4.008951778545793</v>
       </c>
       <c r="L16">
-        <v>346.7781287822182</v>
+        <v>347.5269258955522</v>
       </c>
       <c r="M16">
-        <v>11.67469007708417</v>
+        <v>12.90066427321229</v>
       </c>
       <c r="N16">
-        <v>67.27865478286921</v>
+        <v>68.074993681191</v>
       </c>
       <c r="O16">
-        <v>3.06624607534494</v>
+        <v>3.354880673139013</v>
       </c>
       <c r="P16">
-        <v>657.0134355168602</v>
+        <v>660.7539245615975</v>
       </c>
       <c r="Q16">
-        <v>9.504096750854798</v>
+        <v>7.298243891717566</v>
       </c>
       <c r="R16">
-        <v>5.505440851204591</v>
+        <v>5.467603625665351</v>
       </c>
       <c r="S16">
-        <v>0.6973164814900846</v>
+        <v>0.666243196294496</v>
       </c>
       <c r="T16">
-        <v>52.75283368184559</v>
+        <v>53.16408020246041</v>
       </c>
       <c r="U16">
-        <v>1.831121213037622</v>
+        <v>1.781000156060397</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -3675,64 +3675,64 @@
         <v>2035</v>
       </c>
       <c r="B17">
-        <v>126.6854902733556</v>
+        <v>125.5826992479481</v>
       </c>
       <c r="C17">
-        <v>7.212554576954148</v>
+        <v>7.485579397055638</v>
       </c>
       <c r="D17">
-        <v>1301.802303239145</v>
+        <v>1302.045533801696</v>
       </c>
       <c r="E17">
-        <v>20.11695562950943</v>
+        <v>19.03114505076482</v>
       </c>
       <c r="F17">
-        <v>12.51313894133322</v>
+        <v>12.40360864628926</v>
       </c>
       <c r="G17">
-        <v>1.04841199997707</v>
+        <v>0.9874791586065134</v>
       </c>
       <c r="H17">
-        <v>130.0437153887081</v>
+        <v>130.9311084232749</v>
       </c>
       <c r="I17">
-        <v>3.043574618530857</v>
+        <v>2.852481739647548</v>
       </c>
       <c r="J17">
-        <v>35.5045593433412</v>
+        <v>34.01272766943351</v>
       </c>
       <c r="K17">
-        <v>5.317928991418042</v>
+        <v>4.005238817374812</v>
       </c>
       <c r="L17">
-        <v>382.2826881255594</v>
+        <v>381.5396535649857</v>
       </c>
       <c r="M17">
-        <v>13.215969363325</v>
+        <v>14.39259664370783</v>
       </c>
       <c r="N17">
-        <v>71.88756452801712</v>
+        <v>71.8408479779806</v>
       </c>
       <c r="O17">
-        <v>3.591247736315078</v>
+        <v>2.88118893102044</v>
       </c>
       <c r="P17">
-        <v>728.9010000448773</v>
+        <v>732.5947725395782</v>
       </c>
       <c r="Q17">
-        <v>10.16760953738855</v>
+        <v>7.566381057197845</v>
       </c>
       <c r="R17">
-        <v>5.801875508220352</v>
+        <v>5.566273702224364</v>
       </c>
       <c r="S17">
-        <v>0.7943681588744124</v>
+        <v>0.6359375630374285</v>
       </c>
       <c r="T17">
-        <v>58.55470919006597</v>
+        <v>58.7303539046848</v>
       </c>
       <c r="U17">
-        <v>2.116330757332569</v>
+        <v>1.795143241456284</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -3740,64 +3740,64 @@
         <v>2036</v>
       </c>
       <c r="B18">
-        <v>128.0364649514355</v>
+        <v>129.2803557218193</v>
       </c>
       <c r="C18">
-        <v>8.133443447914372</v>
+        <v>6.694712950547411</v>
       </c>
       <c r="D18">
-        <v>1429.838768190581</v>
+        <v>1431.325889523516</v>
       </c>
       <c r="E18">
-        <v>21.28479208070671</v>
+        <v>19.06236055231761</v>
       </c>
       <c r="F18">
-        <v>13.11087051231128</v>
+        <v>13.12194776333885</v>
       </c>
       <c r="G18">
-        <v>1.102299422209987</v>
+        <v>1.03243964962098</v>
       </c>
       <c r="H18">
-        <v>143.1545859010193</v>
+        <v>144.0530561866138</v>
       </c>
       <c r="I18">
-        <v>3.387042106566853</v>
+        <v>2.956588818554026</v>
       </c>
       <c r="J18">
-        <v>35.50564099994132</v>
+        <v>35.28628583763122</v>
       </c>
       <c r="K18">
-        <v>5.004648593882504</v>
+        <v>4.042901942674177</v>
       </c>
       <c r="L18">
-        <v>417.7883291255008</v>
+        <v>416.8259394026169</v>
       </c>
       <c r="M18">
-        <v>15.14496692518865</v>
+        <v>15.08795114769327</v>
       </c>
       <c r="N18">
-        <v>76.03699793894157</v>
+        <v>76.12627725345568</v>
       </c>
       <c r="O18">
-        <v>3.399811550306125</v>
+        <v>3.209487886526141</v>
       </c>
       <c r="P18">
-        <v>804.9379979838188</v>
+        <v>808.7210497930338</v>
       </c>
       <c r="Q18">
-        <v>11.68162784966407</v>
+        <v>8.020500836407642</v>
       </c>
       <c r="R18">
-        <v>5.968131407300851</v>
+        <v>5.877126148230148</v>
       </c>
       <c r="S18">
-        <v>0.5786656214747021</v>
+        <v>0.6697087779661243</v>
       </c>
       <c r="T18">
-        <v>64.52284059736679</v>
+        <v>64.60748005291494</v>
       </c>
       <c r="U18">
-        <v>2.2683901074746</v>
+        <v>1.950994689038217</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -3805,64 +3805,64 @@
         <v>2037</v>
       </c>
       <c r="B19">
-        <v>135.2202483110052</v>
+        <v>134.9306678169997</v>
       </c>
       <c r="C19">
-        <v>8.642332270980875</v>
+        <v>7.857274564812534</v>
       </c>
       <c r="D19">
-        <v>1565.059016501585</v>
+        <v>1566.256557340515</v>
       </c>
       <c r="E19">
-        <v>23.38660301719108</v>
+        <v>21.48269776264068</v>
       </c>
       <c r="F19">
-        <v>13.38876202875087</v>
+        <v>13.91520444960469</v>
       </c>
       <c r="G19">
-        <v>1.141340987644304</v>
+        <v>1.154216389119472</v>
       </c>
       <c r="H19">
-        <v>156.5433479297702</v>
+        <v>157.9682606362184</v>
       </c>
       <c r="I19">
-        <v>3.37044248231498</v>
+        <v>3.398035315621935</v>
       </c>
       <c r="J19">
-        <v>36.1652207952095</v>
+        <v>36.22575269285026</v>
       </c>
       <c r="K19">
-        <v>4.301566135288085</v>
+        <v>4.853386162451794</v>
       </c>
       <c r="L19">
-        <v>453.9535499207102</v>
+        <v>453.0516920954671</v>
       </c>
       <c r="M19">
-        <v>15.60134663003281</v>
+        <v>15.72159792699168</v>
       </c>
       <c r="N19">
-        <v>78.6094734713939</v>
+        <v>78.84750526867889</v>
       </c>
       <c r="O19">
-        <v>2.976396084130595</v>
+        <v>3.131160118953186</v>
       </c>
       <c r="P19">
-        <v>883.5474714552126</v>
+        <v>887.5685550617126</v>
       </c>
       <c r="Q19">
-        <v>12.32513162718145</v>
+        <v>8.35673399794682</v>
       </c>
       <c r="R19">
-        <v>6.091984750886077</v>
+        <v>6.071924676523686</v>
       </c>
       <c r="S19">
-        <v>0.4799532532772439</v>
+        <v>0.7585008034504985</v>
       </c>
       <c r="T19">
-        <v>70.61482534825286</v>
+        <v>70.6794047294386</v>
       </c>
       <c r="U19">
-        <v>2.309658179016924</v>
+        <v>2.01466469238868</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -3870,64 +3870,64 @@
         <v>2038</v>
       </c>
       <c r="B20">
-        <v>141.0461372254723</v>
+        <v>141.3291958063654</v>
       </c>
       <c r="C20">
-        <v>9.756221514738273</v>
+        <v>7.786356316402387</v>
       </c>
       <c r="D20">
-        <v>1706.105153727059</v>
+        <v>1707.585753146881</v>
       </c>
       <c r="E20">
-        <v>28.48021201367469</v>
+        <v>24.97967991148016</v>
       </c>
       <c r="F20">
-        <v>13.74309957318855</v>
+        <v>14.13605386086364</v>
       </c>
       <c r="G20">
-        <v>1.265231554255073</v>
+        <v>1.485739884603961</v>
       </c>
       <c r="H20">
-        <v>170.2864475029588</v>
+        <v>172.1043144970821</v>
       </c>
       <c r="I20">
-        <v>3.860997386952461</v>
+        <v>3.9978109668542</v>
       </c>
       <c r="J20">
-        <v>37.45599975666367</v>
+        <v>37.80037990329205</v>
       </c>
       <c r="K20">
-        <v>5.204076384401596</v>
+        <v>5.15339732081963</v>
       </c>
       <c r="L20">
-        <v>491.4095496773739</v>
+        <v>490.8520719987595</v>
       </c>
       <c r="M20">
-        <v>16.45694106575012</v>
+        <v>15.88850071966528</v>
       </c>
       <c r="N20">
-        <v>80.80392141554485</v>
+        <v>82.08037125185521</v>
       </c>
       <c r="O20">
-        <v>3.867774560388998</v>
+        <v>3.324015692553622</v>
       </c>
       <c r="P20">
-        <v>964.351392870758</v>
+        <v>969.6489263135677</v>
       </c>
       <c r="Q20">
-        <v>13.9435334985089</v>
+        <v>9.381338574229854</v>
       </c>
       <c r="R20">
-        <v>6.288184130853799</v>
+        <v>6.309436428236092</v>
       </c>
       <c r="S20">
-        <v>0.723867837872305</v>
+        <v>0.6664104376955512</v>
       </c>
       <c r="T20">
-        <v>76.90300947910667</v>
+        <v>76.9888411576747</v>
       </c>
       <c r="U20">
-        <v>2.598816632717811</v>
+        <v>2.130291404899739</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -3935,64 +3935,64 @@
         <v>2039</v>
       </c>
       <c r="B21">
-        <v>144.3851681554447</v>
+        <v>145.4415193531615</v>
       </c>
       <c r="C21">
-        <v>7.545617962740461</v>
+        <v>7.676795328288339</v>
       </c>
       <c r="D21">
-        <v>1850.490321882502</v>
+        <v>1853.027272500042</v>
       </c>
       <c r="E21">
-        <v>28.11558877130384</v>
+        <v>26.7398655355345</v>
       </c>
       <c r="F21">
-        <v>14.40439629256414</v>
+        <v>14.51210538202463</v>
       </c>
       <c r="G21">
-        <v>1.224225835812796</v>
+        <v>1.354898596038425</v>
       </c>
       <c r="H21">
-        <v>184.6908437955229</v>
+        <v>186.6164198791067</v>
       </c>
       <c r="I21">
-        <v>3.903465659648022</v>
+        <v>4.399983558778215</v>
       </c>
       <c r="J21">
-        <v>38.68288107042201</v>
+        <v>38.88700368806578</v>
       </c>
       <c r="K21">
-        <v>5.250807578953673</v>
+        <v>4.811199963940071</v>
       </c>
       <c r="L21">
-        <v>530.092430747796</v>
+        <v>529.7390756868249</v>
       </c>
       <c r="M21">
-        <v>17.31142051287903</v>
+        <v>17.06883166970654</v>
       </c>
       <c r="N21">
-        <v>84.55880382401594</v>
+        <v>85.4983860818121</v>
       </c>
       <c r="O21">
-        <v>3.283951621661219</v>
+        <v>3.603437742709798</v>
       </c>
       <c r="P21">
-        <v>1048.910196694774</v>
+        <v>1055.14731239538</v>
       </c>
       <c r="Q21">
-        <v>14.51169701889111</v>
+        <v>10.01099643738347</v>
       </c>
       <c r="R21">
-        <v>6.541281747931266</v>
+        <v>6.552970055492167</v>
       </c>
       <c r="S21">
-        <v>0.7837316587308233</v>
+        <v>0.8305572932864788</v>
       </c>
       <c r="T21">
-        <v>83.44429122703795</v>
+        <v>83.54181121316688</v>
       </c>
       <c r="U21">
-        <v>2.71121241925157</v>
+        <v>2.438635265113493</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -4000,64 +4000,64 @@
         <v>2040</v>
       </c>
       <c r="B22">
-        <v>149.6309601850286</v>
+        <v>148.2978775799508</v>
       </c>
       <c r="C22">
-        <v>11.11627888808195</v>
+        <v>8.566745661928362</v>
       </c>
       <c r="D22">
-        <v>2000.121282067532</v>
+        <v>2001.325150079993</v>
       </c>
       <c r="E22">
-        <v>32.45321495189157</v>
+        <v>26.88017025711772</v>
       </c>
       <c r="F22">
-        <v>15.04232466649709</v>
+        <v>14.92172750858389</v>
       </c>
       <c r="G22">
-        <v>1.458054523353026</v>
+        <v>1.320180534117118</v>
       </c>
       <c r="H22">
-        <v>199.73316846202</v>
+        <v>201.5381473876906</v>
       </c>
       <c r="I22">
-        <v>4.509062876031763</v>
+        <v>4.71117199081534</v>
       </c>
       <c r="J22">
-        <v>41.01390359103568</v>
+        <v>40.26679957451883</v>
       </c>
       <c r="K22">
-        <v>5.902873946957387</v>
+        <v>5.82111984084383</v>
       </c>
       <c r="L22">
-        <v>571.1063343388316</v>
+        <v>570.0058752613438</v>
       </c>
       <c r="M22">
-        <v>18.72304570819672</v>
+        <v>19.23004263444943</v>
       </c>
       <c r="N22">
-        <v>87.84213477265084</v>
+        <v>87.40779219648726</v>
       </c>
       <c r="O22">
-        <v>4.257577177721902</v>
+        <v>3.974122709823363</v>
       </c>
       <c r="P22">
-        <v>1136.752331467424</v>
+        <v>1142.555104591867</v>
       </c>
       <c r="Q22">
-        <v>15.57188788580021</v>
+        <v>10.78005197895554</v>
       </c>
       <c r="R22">
-        <v>6.81385580145724</v>
+        <v>6.799859683129557</v>
       </c>
       <c r="S22">
-        <v>0.7398791915519396</v>
+        <v>0.8987882587126459</v>
       </c>
       <c r="T22">
-        <v>90.2581470284952</v>
+        <v>90.34167089629645</v>
       </c>
       <c r="U22">
-        <v>2.726091535039786</v>
+        <v>2.859931810836329</v>
       </c>
     </row>
   </sheetData>
@@ -4170,88 +4170,88 @@
         <v>2020</v>
       </c>
       <c r="B2">
-        <v>50.15709659747338</v>
+        <v>49.86446454619045</v>
       </c>
       <c r="C2">
-        <v>2.298016927555033</v>
+        <v>2.716187299556585</v>
       </c>
       <c r="D2">
-        <v>25.24457228895476</v>
+        <v>24.93369522757344</v>
       </c>
       <c r="E2">
-        <v>1.292897462832222</v>
+        <v>1.590028788623875</v>
       </c>
       <c r="F2">
-        <v>24.91252430851864</v>
+        <v>24.93076931861703</v>
       </c>
       <c r="G2">
-        <v>1.612979688921338</v>
+        <v>1.559704147673369</v>
       </c>
       <c r="H2">
-        <v>7.482989052508585</v>
+        <v>7.40385885771272</v>
       </c>
       <c r="I2">
-        <v>0.6049954505556686</v>
+        <v>0.5649338671585219</v>
       </c>
       <c r="J2">
-        <v>7.490055196866603</v>
+        <v>7.594872007646528</v>
       </c>
       <c r="K2">
-        <v>0.5556095259693711</v>
+        <v>0.5991256317475555</v>
       </c>
       <c r="L2">
-        <v>2.501863619362353</v>
+        <v>2.474324710456786</v>
       </c>
       <c r="M2">
-        <v>0.2366183359445581</v>
+        <v>0.2048784160531305</v>
       </c>
       <c r="N2">
-        <v>4.952744923622959</v>
+        <v>4.965771620005609</v>
       </c>
       <c r="O2">
-        <v>0.3833465705222328</v>
+        <v>0.3986945171377402</v>
       </c>
       <c r="P2">
-        <v>2.484871516158154</v>
+        <v>2.491942122795375</v>
       </c>
       <c r="Q2">
-        <v>0.2097810819799739</v>
+        <v>0.1899998456736323</v>
       </c>
       <c r="R2">
-        <v>7.482989052508585</v>
+        <v>7.40385885771272</v>
       </c>
       <c r="S2">
-        <v>0.6049954505556686</v>
+        <v>0.5649338671585219</v>
       </c>
       <c r="T2">
-        <v>5.1760405519452</v>
+        <v>5.328973837432422</v>
       </c>
       <c r="U2">
-        <v>0.4389695190626279</v>
+        <v>0.4677109171831094</v>
       </c>
       <c r="V2">
-        <v>1.145562339575095</v>
+        <v>1.129531595609416</v>
       </c>
       <c r="W2">
-        <v>0.1104824354414678</v>
+        <v>0.1250895579322613</v>
       </c>
       <c r="X2">
-        <v>1.168452305346305</v>
+        <v>1.13636657460469</v>
       </c>
       <c r="Y2">
-        <v>0.114166934431957</v>
+        <v>0.1179270492316192</v>
       </c>
       <c r="Z2">
-        <v>2.501863619362353</v>
+        <v>2.474324710456786</v>
       </c>
       <c r="AA2">
-        <v>0.2366183359445581</v>
+        <v>0.2048784160531305</v>
       </c>
       <c r="AB2">
-        <v>4.952744923622959</v>
+        <v>4.965771620005609</v>
       </c>
       <c r="AC2">
-        <v>0.3833465705222328</v>
+        <v>0.3986945171377402</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -4265,94 +4265,94 @@
         <v>2021</v>
       </c>
       <c r="B3">
-        <v>54.5749989591418</v>
+        <v>55.37560418356396</v>
       </c>
       <c r="C3">
-        <v>2.763180797607538</v>
+        <v>2.815436847739336</v>
       </c>
       <c r="D3">
-        <v>27.25683682824483</v>
+        <v>27.92612905479805</v>
       </c>
       <c r="E3">
-        <v>1.694331535370261</v>
+        <v>1.787898130014453</v>
       </c>
       <c r="F3">
-        <v>27.31816213089696</v>
+        <v>27.44947512876592</v>
       </c>
       <c r="G3">
-        <v>1.795154030645533</v>
+        <v>1.731899912148663</v>
       </c>
       <c r="H3">
-        <v>8.121812845747307</v>
+        <v>8.323936388341703</v>
       </c>
       <c r="I3">
-        <v>0.5187672539780153</v>
+        <v>0.6595092639881905</v>
       </c>
       <c r="J3">
-        <v>8.282444477884937</v>
+        <v>8.2681143129443</v>
       </c>
       <c r="K3">
-        <v>0.695643543160096</v>
+        <v>0.6656447424135159</v>
       </c>
       <c r="L3">
-        <v>2.742180556989529</v>
+        <v>2.706572449296695</v>
       </c>
       <c r="M3">
-        <v>0.2503635720142078</v>
+        <v>0.2229685020997031</v>
       </c>
       <c r="N3">
-        <v>5.448302090930329</v>
+        <v>5.474631487836107</v>
       </c>
       <c r="O3">
-        <v>0.4224908053716967</v>
+        <v>0.4260193841603172</v>
       </c>
       <c r="P3">
-        <v>2.723422159344876</v>
+        <v>2.676220490347101</v>
       </c>
       <c r="Q3">
-        <v>0.2450846217271386</v>
+        <v>0.2088956814597114</v>
       </c>
       <c r="R3">
-        <v>8.121812845747307</v>
+        <v>8.323936388341703</v>
       </c>
       <c r="S3">
-        <v>0.5187672539780153</v>
+        <v>0.6595092639881905</v>
       </c>
       <c r="T3">
-        <v>5.822299292722159</v>
+        <v>5.84041854272669</v>
       </c>
       <c r="U3">
-        <v>0.5224386465180186</v>
+        <v>0.4804602531706538</v>
       </c>
       <c r="V3">
-        <v>1.22427042875409</v>
+        <v>1.21457862859174</v>
       </c>
       <c r="W3">
-        <v>0.1387831678231171</v>
+        <v>0.1537527702547238</v>
       </c>
       <c r="X3">
-        <v>1.235874756408689</v>
+        <v>1.213117141625872</v>
       </c>
       <c r="Y3">
-        <v>0.1321268927049191</v>
+        <v>0.1528961677706777</v>
       </c>
       <c r="Z3">
-        <v>2.742180556989529</v>
+        <v>2.706572449296695</v>
       </c>
       <c r="AA3">
-        <v>0.2503635720142078</v>
+        <v>0.2229685020997031</v>
       </c>
       <c r="AB3">
-        <v>5.448302090930329</v>
+        <v>5.474631487836107</v>
       </c>
       <c r="AC3">
-        <v>0.4224908053716967</v>
+        <v>0.4260193841603172</v>
       </c>
       <c r="AD3">
-        <v>8.145441325734485</v>
+        <v>8.197793661098542</v>
       </c>
       <c r="AE3">
-        <v>0.6854890023616238</v>
+        <v>0.7407762271655169</v>
       </c>
     </row>
     <row r="4" spans="1:31">
@@ -4360,94 +4360,94 @@
         <v>2022</v>
       </c>
       <c r="B4">
-        <v>59.97962593672386</v>
+        <v>59.31480917687392</v>
       </c>
       <c r="C4">
-        <v>3.162922518716615</v>
+        <v>3.08963824262878</v>
       </c>
       <c r="D4">
-        <v>30.03334825807666</v>
+        <v>29.61222656201005</v>
       </c>
       <c r="E4">
-        <v>1.948460192300637</v>
+        <v>2.150513417462997</v>
       </c>
       <c r="F4">
-        <v>29.9462776786472</v>
+        <v>29.70258261486389</v>
       </c>
       <c r="G4">
-        <v>1.878936611593927</v>
+        <v>1.461750338681793</v>
       </c>
       <c r="H4">
-        <v>8.919046222012186</v>
+        <v>8.842782481933421</v>
       </c>
       <c r="I4">
-        <v>0.7106214800027341</v>
+        <v>0.5349740635105046</v>
       </c>
       <c r="J4">
-        <v>9.000600770379579</v>
+        <v>8.927408506682053</v>
       </c>
       <c r="K4">
-        <v>0.6298395447107982</v>
+        <v>0.5985771257345651</v>
       </c>
       <c r="L4">
-        <v>2.995195106497945</v>
+        <v>2.976363911815582</v>
       </c>
       <c r="M4">
-        <v>0.2170454228292127</v>
+        <v>0.1965982447687272</v>
       </c>
       <c r="N4">
-        <v>6.024547632248227</v>
+        <v>5.937891560206168</v>
       </c>
       <c r="O4">
-        <v>0.5039268752554852</v>
+        <v>0.4050273400439093</v>
       </c>
       <c r="P4">
-        <v>3.006887947509259</v>
+        <v>3.018136154226663</v>
       </c>
       <c r="Q4">
-        <v>0.2389280696980747</v>
+        <v>0.217434079800197</v>
       </c>
       <c r="R4">
-        <v>8.919046222012186</v>
+        <v>8.842782481933421</v>
       </c>
       <c r="S4">
-        <v>0.7106214800027341</v>
+        <v>0.5349740635105046</v>
       </c>
       <c r="T4">
-        <v>6.255897888587533</v>
+        <v>6.315800463451551</v>
       </c>
       <c r="U4">
-        <v>0.4897548966620001</v>
+        <v>0.478525875621131</v>
       </c>
       <c r="V4">
-        <v>1.374751935239492</v>
+        <v>1.294781421228286</v>
       </c>
       <c r="W4">
-        <v>0.1518780908890732</v>
+        <v>0.1241082958667155</v>
       </c>
       <c r="X4">
-        <v>1.369950946552552</v>
+        <v>1.316826622002215</v>
       </c>
       <c r="Y4">
-        <v>0.1225055319518751</v>
+        <v>0.1279129817570687</v>
       </c>
       <c r="Z4">
-        <v>2.995195106497945</v>
+        <v>2.976363911815582</v>
       </c>
       <c r="AA4">
-        <v>0.2170454228292127</v>
+        <v>0.1965982447687272</v>
       </c>
       <c r="AB4">
-        <v>6.024547632248227</v>
+        <v>5.937891560206168</v>
       </c>
       <c r="AC4">
-        <v>0.5039268752554852</v>
+        <v>0.4050273400439093</v>
       </c>
       <c r="AD4">
-        <v>11.78263359053208</v>
+        <v>11.94491436235232</v>
       </c>
       <c r="AE4">
-        <v>0.6910499037910857</v>
+        <v>0.7991670106820571</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -4455,94 +4455,94 @@
         <v>2023</v>
       </c>
       <c r="B5">
-        <v>65.29576091856751</v>
+        <v>65.37728096094321</v>
       </c>
       <c r="C5">
-        <v>3.238463163353375</v>
+        <v>3.357041646213097</v>
       </c>
       <c r="D5">
-        <v>32.85914439918344</v>
+        <v>32.86430365325857</v>
       </c>
       <c r="E5">
-        <v>2.117106146119645</v>
+        <v>1.748522882642226</v>
       </c>
       <c r="F5">
-        <v>32.43661651938409</v>
+        <v>32.5129773076846</v>
       </c>
       <c r="G5">
-        <v>1.836002902059692</v>
+        <v>2.229905758387538</v>
       </c>
       <c r="H5">
-        <v>9.659863826896551</v>
+        <v>9.856790260127582</v>
       </c>
       <c r="I5">
-        <v>0.7167527963599297</v>
+        <v>0.7914712884134543</v>
       </c>
       <c r="J5">
-        <v>9.768130723568456</v>
+        <v>9.698928074576115</v>
       </c>
       <c r="K5">
-        <v>0.6372721982188062</v>
+        <v>0.8242292955304413</v>
       </c>
       <c r="L5">
-        <v>3.261317649747267</v>
+        <v>3.206908200914581</v>
       </c>
       <c r="M5">
-        <v>0.266035036231522</v>
+        <v>0.2825871664904135</v>
       </c>
       <c r="N5">
-        <v>6.47715535425588</v>
+        <v>6.526197831683042</v>
       </c>
       <c r="O5">
-        <v>0.3934374528609071</v>
+        <v>0.5386627888132869</v>
       </c>
       <c r="P5">
-        <v>3.270148964915929</v>
+        <v>3.22415294038328</v>
       </c>
       <c r="Q5">
-        <v>0.2989070823864001</v>
+        <v>0.3063726819111079</v>
       </c>
       <c r="R5">
-        <v>9.659863826896551</v>
+        <v>9.856790260127582</v>
       </c>
       <c r="S5">
-        <v>0.7167527963599297</v>
+        <v>0.7914712884134543</v>
       </c>
       <c r="T5">
-        <v>6.849517615297292</v>
+        <v>6.78820760927856</v>
       </c>
       <c r="U5">
-        <v>0.5278478836707232</v>
+        <v>0.6728589433648788</v>
       </c>
       <c r="V5">
-        <v>1.452474739474561</v>
+        <v>1.461337286288044</v>
       </c>
       <c r="W5">
-        <v>0.1455870724882923</v>
+        <v>0.1567669285970029</v>
       </c>
       <c r="X5">
-        <v>1.466138368796604</v>
+        <v>1.449383179009512</v>
       </c>
       <c r="Y5">
-        <v>0.1321272348826124</v>
+        <v>0.1438978069184357</v>
       </c>
       <c r="Z5">
-        <v>3.261317649747267</v>
+        <v>3.206908200914581</v>
       </c>
       <c r="AA5">
-        <v>0.266035036231522</v>
+        <v>0.2825871664904135</v>
       </c>
       <c r="AB5">
-        <v>6.47715535425588</v>
+        <v>6.526197831683042</v>
       </c>
       <c r="AC5">
-        <v>0.3934374528609071</v>
+        <v>0.5386627888132869</v>
       </c>
       <c r="AD5">
-        <v>13.92010459445073</v>
+        <v>13.95199541200906</v>
       </c>
       <c r="AE5">
-        <v>0.8105229448820823</v>
+        <v>0.6003308391849537</v>
       </c>
     </row>
     <row r="6" spans="1:31">
@@ -4550,94 +4550,94 @@
         <v>2024</v>
       </c>
       <c r="B6">
-        <v>70.22223061637173</v>
+        <v>68.63099510040578</v>
       </c>
       <c r="C6">
-        <v>3.799543900878309</v>
+        <v>3.082571346936473</v>
       </c>
       <c r="D6">
-        <v>35.16400611814424</v>
+        <v>34.59721590316347</v>
       </c>
       <c r="E6">
-        <v>2.508619216375895</v>
+        <v>2.077633478016621</v>
       </c>
       <c r="F6">
-        <v>35.05822449822749</v>
+        <v>34.03377919724232</v>
       </c>
       <c r="G6">
-        <v>2.134504764707378</v>
+        <v>1.833609611414947</v>
       </c>
       <c r="H6">
-        <v>10.50960898198848</v>
+        <v>10.2420277575801</v>
       </c>
       <c r="I6">
-        <v>0.8629018622395902</v>
+        <v>0.6697053223013114</v>
       </c>
       <c r="J6">
-        <v>10.49714691871095</v>
+        <v>10.25194764768827</v>
       </c>
       <c r="K6">
-        <v>0.6281528099203586</v>
+        <v>0.6605424359687191</v>
       </c>
       <c r="L6">
-        <v>3.521308134344119</v>
+        <v>3.408592478857248</v>
       </c>
       <c r="M6">
-        <v>0.3085747156153228</v>
+        <v>0.305374896528268</v>
       </c>
       <c r="N6">
-        <v>7.016789717346946</v>
+        <v>6.777294079541336</v>
       </c>
       <c r="O6">
-        <v>0.50933708092061</v>
+        <v>0.4451096453225739</v>
       </c>
       <c r="P6">
-        <v>3.513370745836997</v>
+        <v>3.353917233575354</v>
       </c>
       <c r="Q6">
-        <v>0.3112305609813006</v>
+        <v>0.2989452746843664</v>
       </c>
       <c r="R6">
-        <v>10.50960898198848</v>
+        <v>10.2420277575801</v>
       </c>
       <c r="S6">
-        <v>0.8629018622395902</v>
+        <v>0.6697053223013114</v>
       </c>
       <c r="T6">
-        <v>7.37073631488117</v>
+        <v>7.153285079974036</v>
       </c>
       <c r="U6">
-        <v>0.521067874041966</v>
+        <v>0.5072050422114771</v>
       </c>
       <c r="V6">
-        <v>1.560167495665252</v>
+        <v>1.543148382963406</v>
       </c>
       <c r="W6">
-        <v>0.1537878421940386</v>
+        <v>0.1613212617471823</v>
       </c>
       <c r="X6">
-        <v>1.566243108164528</v>
+        <v>1.555514184750827</v>
       </c>
       <c r="Y6">
-        <v>0.1712629689624998</v>
+        <v>0.1573442342470988</v>
       </c>
       <c r="Z6">
-        <v>3.521308134344119</v>
+        <v>3.408592478857248</v>
       </c>
       <c r="AA6">
-        <v>0.3085747156153228</v>
+        <v>0.305374896528268</v>
       </c>
       <c r="AB6">
-        <v>7.016789717346946</v>
+        <v>6.777294079541336</v>
       </c>
       <c r="AC6">
-        <v>0.50933708092061</v>
+        <v>0.4451096453225739</v>
       </c>
       <c r="AD6">
-        <v>15.54900028584319</v>
+        <v>15.64600682586078</v>
       </c>
       <c r="AE6">
-        <v>0.6958198363738696</v>
+        <v>0.8912644934883214</v>
       </c>
     </row>
     <row r="7" spans="1:31">
@@ -4645,94 +4645,94 @@
         <v>2025</v>
       </c>
       <c r="B7">
-        <v>76.1619614880874</v>
+        <v>75.32351748334868</v>
       </c>
       <c r="C7">
-        <v>3.326452386358314</v>
+        <v>3.327154602938043</v>
       </c>
       <c r="D7">
-        <v>38.18852699382029</v>
+        <v>37.79767415513756</v>
       </c>
       <c r="E7">
-        <v>2.057279295579067</v>
+        <v>2.187334068987437</v>
       </c>
       <c r="F7">
-        <v>37.9734344942671</v>
+        <v>37.52584332821109</v>
       </c>
       <c r="G7">
-        <v>1.901416060030986</v>
+        <v>1.931832152478757</v>
       </c>
       <c r="H7">
-        <v>11.34889819480181</v>
+        <v>11.1862533253304</v>
       </c>
       <c r="I7">
-        <v>0.6839170658316788</v>
+        <v>0.6959726008015888</v>
       </c>
       <c r="J7">
-        <v>11.38561160510879</v>
+        <v>11.3854592717686</v>
       </c>
       <c r="K7">
-        <v>0.7480448053630848</v>
+        <v>0.7047658757546911</v>
       </c>
       <c r="L7">
-        <v>3.824776681926193</v>
+        <v>3.723002020518213</v>
       </c>
       <c r="M7">
-        <v>0.294802036711854</v>
+        <v>0.3443587184473128</v>
       </c>
       <c r="N7">
-        <v>7.557797818808463</v>
+        <v>7.507620035068514</v>
       </c>
       <c r="O7">
-        <v>0.5335924919835664</v>
+        <v>0.5230616874854792</v>
       </c>
       <c r="P7">
-        <v>3.856350193621868</v>
+        <v>3.72350867552538</v>
       </c>
       <c r="Q7">
-        <v>0.341385204407016</v>
+        <v>0.3205270362669346</v>
       </c>
       <c r="R7">
-        <v>11.34889819480181</v>
+        <v>11.1862533253304</v>
       </c>
       <c r="S7">
-        <v>0.6839170658316788</v>
+        <v>0.6959726008015888</v>
       </c>
       <c r="T7">
-        <v>7.986163204886675</v>
+        <v>7.957782630842359</v>
       </c>
       <c r="U7">
-        <v>0.5244050962440174</v>
+        <v>0.5197947552258454</v>
       </c>
       <c r="V7">
-        <v>1.699401933979777</v>
+        <v>1.718961061920265</v>
       </c>
       <c r="W7">
-        <v>0.1959502676748929</v>
+        <v>0.2067659092254243</v>
       </c>
       <c r="X7">
-        <v>1.700046466242333</v>
+        <v>1.708715579005971</v>
       </c>
       <c r="Y7">
-        <v>0.1932168817230498</v>
+        <v>0.194027726949354</v>
       </c>
       <c r="Z7">
-        <v>3.824776681926193</v>
+        <v>3.723002020518213</v>
       </c>
       <c r="AA7">
-        <v>0.294802036711854</v>
+        <v>0.3443587184473128</v>
       </c>
       <c r="AB7">
-        <v>7.557797818808463</v>
+        <v>7.507620035068514</v>
       </c>
       <c r="AC7">
-        <v>0.5335924919835664</v>
+        <v>0.5230616874854792</v>
       </c>
       <c r="AD7">
-        <v>17.03407692948743</v>
+        <v>16.7456146639077</v>
       </c>
       <c r="AE7">
-        <v>0.8602674710753158</v>
+        <v>0.7609423413372302</v>
       </c>
     </row>
     <row r="8" spans="1:31">
@@ -4740,94 +4740,94 @@
         <v>2026</v>
       </c>
       <c r="B8">
-        <v>80.07042977155169</v>
+        <v>79.8771522664876</v>
       </c>
       <c r="C8">
-        <v>3.747325721521246</v>
+        <v>3.705189356636641</v>
       </c>
       <c r="D8">
-        <v>39.93354781927816</v>
+        <v>39.95680617240585</v>
       </c>
       <c r="E8">
-        <v>2.336288837900946</v>
+        <v>2.418027437595694</v>
       </c>
       <c r="F8">
-        <v>40.13688195227352</v>
+        <v>39.92034609408174</v>
       </c>
       <c r="G8">
-        <v>2.330546742316618</v>
+        <v>2.393417302879214</v>
       </c>
       <c r="H8">
-        <v>12.04475827419671</v>
+        <v>12.08031591045786</v>
       </c>
       <c r="I8">
-        <v>0.8751815005506595</v>
+        <v>0.8627546898228455</v>
       </c>
       <c r="J8">
-        <v>12.1410259086794</v>
+        <v>12.00073829694394</v>
       </c>
       <c r="K8">
-        <v>0.8654491649177317</v>
+        <v>0.9443462665835617</v>
       </c>
       <c r="L8">
-        <v>3.917327279925857</v>
+        <v>3.910180181761032</v>
       </c>
       <c r="M8">
-        <v>0.2783852035883699</v>
+        <v>0.3806745444160974</v>
       </c>
       <c r="N8">
-        <v>8.025237632086203</v>
+        <v>8.000137596372646</v>
       </c>
       <c r="O8">
-        <v>0.6373719428663206</v>
+        <v>0.5706273767464192</v>
       </c>
       <c r="P8">
-        <v>4.008532857385351</v>
+        <v>3.928974108546273</v>
       </c>
       <c r="Q8">
-        <v>0.308942617972202</v>
+        <v>0.2636642645666054</v>
       </c>
       <c r="R8">
-        <v>12.04475827419671</v>
+        <v>12.08031591045786</v>
       </c>
       <c r="S8">
-        <v>0.8751815005506595</v>
+        <v>0.8627546898228455</v>
       </c>
       <c r="T8">
-        <v>8.466988725706047</v>
+        <v>8.385638438333082</v>
       </c>
       <c r="U8">
-        <v>0.6744095847421422</v>
+        <v>0.7012665709858624</v>
       </c>
       <c r="V8">
-        <v>1.824728761839668</v>
+        <v>1.797964111444224</v>
       </c>
       <c r="W8">
-        <v>0.1966614146984621</v>
+        <v>0.2223657426310412</v>
       </c>
       <c r="X8">
-        <v>1.849308421133686</v>
+        <v>1.817135747166626</v>
       </c>
       <c r="Y8">
-        <v>0.1766462304681818</v>
+        <v>0.2188167620735024</v>
       </c>
       <c r="Z8">
-        <v>3.917327279925857</v>
+        <v>3.910180181761032</v>
       </c>
       <c r="AA8">
-        <v>0.2783852035883699</v>
+        <v>0.3806745444160974</v>
       </c>
       <c r="AB8">
-        <v>8.025237632086203</v>
+        <v>8.000137596372646</v>
       </c>
       <c r="AC8">
-        <v>0.6373719428663206</v>
+        <v>0.5706273767464192</v>
       </c>
       <c r="AD8">
-        <v>18.49376550815364</v>
+        <v>18.2772187079948</v>
       </c>
       <c r="AE8">
-        <v>0.7392438033404323</v>
+        <v>0.6774854287921688</v>
       </c>
     </row>
     <row r="9" spans="1:31">
@@ -4835,94 +4835,94 @@
         <v>2027</v>
       </c>
       <c r="B9">
-        <v>84.52714394902355</v>
+        <v>84.86811282388945</v>
       </c>
       <c r="C9">
-        <v>3.76344834935833</v>
+        <v>4.883937905167994</v>
       </c>
       <c r="D9">
-        <v>42.23744549290257</v>
+        <v>42.30586736373884</v>
       </c>
       <c r="E9">
-        <v>2.121935275849374</v>
+        <v>2.954051275819456</v>
       </c>
       <c r="F9">
-        <v>42.28969845612102</v>
+        <v>42.56224546015061</v>
       </c>
       <c r="G9">
-        <v>2.373571036439651</v>
+        <v>3.101658934329819</v>
       </c>
       <c r="H9">
-        <v>12.64831049181471</v>
+        <v>12.84160845427565</v>
       </c>
       <c r="I9">
-        <v>0.9200883684962664</v>
+        <v>1.104470001512879</v>
       </c>
       <c r="J9">
-        <v>12.89856572486099</v>
+        <v>12.68942739622258</v>
       </c>
       <c r="K9">
-        <v>0.8334499426325832</v>
+        <v>1.004245437577372</v>
       </c>
       <c r="L9">
-        <v>4.189957719288737</v>
+        <v>4.223267403169661</v>
       </c>
       <c r="M9">
-        <v>0.3642925354396193</v>
+        <v>0.3812609655310361</v>
       </c>
       <c r="N9">
-        <v>8.350961841446074</v>
+        <v>8.51536799877861</v>
       </c>
       <c r="O9">
-        <v>0.6210356278618581</v>
+        <v>0.7108900520179583</v>
       </c>
       <c r="P9">
-        <v>4.201902678710495</v>
+        <v>4.292574207704114</v>
       </c>
       <c r="Q9">
-        <v>0.3705299609679102</v>
+        <v>0.4587471135393274</v>
       </c>
       <c r="R9">
-        <v>12.64831049181471</v>
+        <v>12.84160845427565</v>
       </c>
       <c r="S9">
-        <v>0.9200883684962664</v>
+        <v>1.104470001512879</v>
       </c>
       <c r="T9">
-        <v>8.988417149989237</v>
+        <v>8.860575938619558</v>
       </c>
       <c r="U9">
-        <v>0.6362561075671742</v>
+        <v>0.8078186390980115</v>
       </c>
       <c r="V9">
-        <v>1.968476450284495</v>
+        <v>1.911777847007847</v>
       </c>
       <c r="W9">
-        <v>0.19401227011084</v>
+        <v>0.2277912910321383</v>
       </c>
       <c r="X9">
-        <v>1.941672124587264</v>
+        <v>1.917073610595181</v>
       </c>
       <c r="Y9">
-        <v>0.2274952249894093</v>
+        <v>0.2179776473161518</v>
       </c>
       <c r="Z9">
-        <v>4.189957719288737</v>
+        <v>4.223267403169661</v>
       </c>
       <c r="AA9">
-        <v>0.3642925354396193</v>
+        <v>0.3812609655310361</v>
       </c>
       <c r="AB9">
-        <v>8.350961841446074</v>
+        <v>8.51536799877861</v>
       </c>
       <c r="AC9">
-        <v>0.6210356278618581</v>
+        <v>0.7108900520179583</v>
       </c>
       <c r="AD9">
-        <v>19.78024101673869</v>
+        <v>19.67668418100878</v>
       </c>
       <c r="AE9">
-        <v>0.9821075683319498</v>
+        <v>1.015931994436633</v>
       </c>
     </row>
     <row r="10" spans="1:31">
@@ -4930,94 +4930,94 @@
         <v>2028</v>
       </c>
       <c r="B10">
-        <v>90.23045228268819</v>
+        <v>89.62109067769259</v>
       </c>
       <c r="C10">
-        <v>4.485520429864262</v>
+        <v>4.189512316083251</v>
       </c>
       <c r="D10">
-        <v>44.92700299847004</v>
+        <v>44.69817609096683</v>
       </c>
       <c r="E10">
-        <v>2.688700176913707</v>
+        <v>2.794568904378915</v>
       </c>
       <c r="F10">
-        <v>45.30344928421816</v>
+        <v>44.92291458672575</v>
       </c>
       <c r="G10">
-        <v>2.784287454913319</v>
+        <v>2.208267552910768</v>
       </c>
       <c r="H10">
-        <v>13.63295290508933</v>
+        <v>13.6312573248781</v>
       </c>
       <c r="I10">
-        <v>1.01253120690945</v>
+        <v>0.7666174003338795</v>
       </c>
       <c r="J10">
-        <v>13.59314046785313</v>
+        <v>13.32761976152768</v>
       </c>
       <c r="K10">
-        <v>1.052036106457539</v>
+        <v>0.9213969089643308</v>
       </c>
       <c r="L10">
-        <v>4.496284112588188</v>
+        <v>4.49450090721648</v>
       </c>
       <c r="M10">
-        <v>0.3756466144609517</v>
+        <v>0.3026479397399137</v>
       </c>
       <c r="N10">
-        <v>9.033633500022813</v>
+        <v>8.938504151823178</v>
       </c>
       <c r="O10">
-        <v>0.6890781402312799</v>
+        <v>0.697804799515082</v>
       </c>
       <c r="P10">
-        <v>4.547438298664695</v>
+        <v>4.531032441280297</v>
       </c>
       <c r="Q10">
-        <v>0.3468465818112295</v>
+        <v>0.3526194668556297</v>
       </c>
       <c r="R10">
-        <v>13.63295290508933</v>
+        <v>13.6312573248781</v>
       </c>
       <c r="S10">
-        <v>1.01253120690945</v>
+        <v>0.7666174003338795</v>
       </c>
       <c r="T10">
-        <v>9.557451610352333</v>
+        <v>9.412482301035364</v>
       </c>
       <c r="U10">
-        <v>0.8043303814493752</v>
+        <v>0.6911733532412513</v>
       </c>
       <c r="V10">
-        <v>2.016919600947907</v>
+        <v>1.955966056393147</v>
       </c>
       <c r="W10">
-        <v>0.2303055881628594</v>
+        <v>0.2445426274139792</v>
       </c>
       <c r="X10">
-        <v>2.018769256552894</v>
+        <v>1.959171404099167</v>
       </c>
       <c r="Y10">
-        <v>0.2023385714083736</v>
+        <v>0.253048887290182</v>
       </c>
       <c r="Z10">
-        <v>4.496284112588188</v>
+        <v>4.49450090721648</v>
       </c>
       <c r="AA10">
-        <v>0.3756466144609517</v>
+        <v>0.3026479397399137</v>
       </c>
       <c r="AB10">
-        <v>9.033633500022813</v>
+        <v>8.938504151823178</v>
       </c>
       <c r="AC10">
-        <v>0.6890781402312799</v>
+        <v>0.697804799515082</v>
       </c>
       <c r="AD10">
-        <v>20.94292490947764</v>
+        <v>20.9672564226662</v>
       </c>
       <c r="AE10">
-        <v>0.8497780303697596</v>
+        <v>1.154695854882883</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -5025,94 +5025,94 @@
         <v>2029</v>
       </c>
       <c r="B11">
-        <v>95.01838190940835</v>
+        <v>94.31428446599043</v>
       </c>
       <c r="C11">
-        <v>5.208394711938013</v>
+        <v>4.137013492600257</v>
       </c>
       <c r="D11">
-        <v>47.18696589869393</v>
+        <v>46.71362166309305</v>
       </c>
       <c r="E11">
-        <v>3.226150977677583</v>
+        <v>2.356507191209092</v>
       </c>
       <c r="F11">
-        <v>47.83141601071441</v>
+        <v>47.60066280289733</v>
       </c>
       <c r="G11">
-        <v>3.082449061314084</v>
+        <v>2.840155337949516</v>
       </c>
       <c r="H11">
-        <v>14.32110139271151</v>
+        <v>14.29274578846276</v>
       </c>
       <c r="I11">
-        <v>1.091146217177604</v>
+        <v>1.082916149717871</v>
       </c>
       <c r="J11">
-        <v>14.23894240734701</v>
+        <v>14.26597854247887</v>
       </c>
       <c r="K11">
-        <v>1.062801087705537</v>
+        <v>1.209731296497269</v>
       </c>
       <c r="L11">
-        <v>4.885219859425988</v>
+        <v>4.795947106172685</v>
       </c>
       <c r="M11">
-        <v>0.4567578190125983</v>
+        <v>0.3416063029546367</v>
       </c>
       <c r="N11">
-        <v>9.552830200393817</v>
+        <v>9.463899791507281</v>
       </c>
       <c r="O11">
-        <v>0.7691787493552715</v>
+        <v>0.6647863384782884</v>
       </c>
       <c r="P11">
-        <v>4.833322150836089</v>
+        <v>4.782091574275732</v>
       </c>
       <c r="Q11">
-        <v>0.4891600201634535</v>
+        <v>0.373369628950974</v>
       </c>
       <c r="R11">
-        <v>14.32110139271151</v>
+        <v>14.29274578846276</v>
       </c>
       <c r="S11">
-        <v>1.091146217177604</v>
+        <v>1.082916149717871</v>
       </c>
       <c r="T11">
-        <v>9.924052845216686</v>
+        <v>9.977088274915102</v>
       </c>
       <c r="U11">
-        <v>0.7225426685285243</v>
+        <v>0.8558623947192535</v>
       </c>
       <c r="V11">
-        <v>2.149164308645058</v>
+        <v>2.156215370974239</v>
       </c>
       <c r="W11">
-        <v>0.2603933473688148</v>
+        <v>0.2847152942312051</v>
       </c>
       <c r="X11">
-        <v>2.165725253485271</v>
+        <v>2.132674896589536</v>
       </c>
       <c r="Y11">
-        <v>0.2373158726812129</v>
+        <v>0.2476314137520236</v>
       </c>
       <c r="Z11">
-        <v>4.885219859425988</v>
+        <v>4.795947106172685</v>
       </c>
       <c r="AA11">
-        <v>0.4567578190125983</v>
+        <v>0.3416063029546367</v>
       </c>
       <c r="AB11">
-        <v>9.552830200393817</v>
+        <v>9.463899791507281</v>
       </c>
       <c r="AC11">
-        <v>0.7691787493552715</v>
+        <v>0.6647863384782884</v>
       </c>
       <c r="AD11">
-        <v>22.38405371969056</v>
+        <v>22.27709200526461</v>
       </c>
       <c r="AE11">
-        <v>1.028057269222813</v>
+        <v>0.9273972148694812</v>
       </c>
     </row>
     <row r="12" spans="1:31">
@@ -5120,94 +5120,94 @@
         <v>2030</v>
       </c>
       <c r="B12">
-        <v>99.42235283871709</v>
+        <v>99.27711959442895</v>
       </c>
       <c r="C12">
-        <v>5.08324786003172</v>
+        <v>5.473152138004454</v>
       </c>
       <c r="D12">
-        <v>49.4927125039103</v>
+        <v>49.88904369521111</v>
       </c>
       <c r="E12">
-        <v>3.154942025807223</v>
+        <v>3.154512556188495</v>
       </c>
       <c r="F12">
-        <v>49.92964033480677</v>
+        <v>49.38807589921784</v>
       </c>
       <c r="G12">
-        <v>2.961295963602595</v>
+        <v>3.074464946833483</v>
       </c>
       <c r="H12">
-        <v>15.00639394352056</v>
+        <v>14.90532943582564</v>
       </c>
       <c r="I12">
-        <v>1.154018429648017</v>
+        <v>1.096212176212633</v>
       </c>
       <c r="J12">
-        <v>14.85424203783409</v>
+        <v>14.76094190085541</v>
       </c>
       <c r="K12">
-        <v>0.9540327555423793</v>
+        <v>0.99504767779554</v>
       </c>
       <c r="L12">
-        <v>5.044998987881861</v>
+        <v>4.989182765651758</v>
       </c>
       <c r="M12">
-        <v>0.4710481037418239</v>
+        <v>0.4599339965992398</v>
       </c>
       <c r="N12">
-        <v>9.999709909429322</v>
+        <v>9.813863240041295</v>
       </c>
       <c r="O12">
-        <v>0.7020366838355512</v>
+        <v>0.7049375870861179</v>
       </c>
       <c r="P12">
-        <v>5.024295456140931</v>
+        <v>4.918758556843729</v>
       </c>
       <c r="Q12">
-        <v>0.4228737567025853</v>
+        <v>0.4474645897169992</v>
       </c>
       <c r="R12">
-        <v>15.00639394352056</v>
+        <v>14.90532943582564</v>
       </c>
       <c r="S12">
-        <v>1.154018429648017</v>
+        <v>1.096212176212633</v>
       </c>
       <c r="T12">
-        <v>10.45691026148424</v>
+        <v>10.462669284221</v>
       </c>
       <c r="U12">
-        <v>0.787209932848938</v>
+        <v>0.7318798942058651</v>
       </c>
       <c r="V12">
-        <v>2.196450260462893</v>
+        <v>2.136701592248032</v>
       </c>
       <c r="W12">
-        <v>0.2502311133378295</v>
+        <v>0.2662853906664726</v>
       </c>
       <c r="X12">
-        <v>2.200881515886955</v>
+        <v>2.161571024386381</v>
       </c>
       <c r="Y12">
-        <v>0.2175809994576081</v>
+        <v>0.2674766228741145</v>
       </c>
       <c r="Z12">
-        <v>5.044998987881861</v>
+        <v>4.989182765651758</v>
       </c>
       <c r="AA12">
-        <v>0.4710481037418239</v>
+        <v>0.4599339965992398</v>
       </c>
       <c r="AB12">
-        <v>9.999709909429322</v>
+        <v>9.813863240041295</v>
       </c>
       <c r="AC12">
-        <v>0.7020366838355512</v>
+        <v>0.7049375870861179</v>
       </c>
       <c r="AD12">
-        <v>23.54953965161856</v>
+        <v>23.54283603561003</v>
       </c>
       <c r="AE12">
-        <v>0.9122841611698583</v>
+        <v>1.116846005764225</v>
       </c>
     </row>
     <row r="13" spans="1:31">
@@ -5215,94 +5215,94 @@
         <v>2031</v>
       </c>
       <c r="B13">
-        <v>5.011216553464253</v>
+        <v>5.046383764281989</v>
       </c>
       <c r="C13">
-        <v>0.2292841370770076</v>
+        <v>0.2602800521832477</v>
       </c>
       <c r="D13">
-        <v>2.509172638871949</v>
+        <v>2.516449050367034</v>
       </c>
       <c r="E13">
-        <v>0.1381153215691751</v>
+        <v>0.1594675911934764</v>
       </c>
       <c r="F13">
-        <v>2.502043914592303</v>
+        <v>2.529934713914956</v>
       </c>
       <c r="G13">
-        <v>0.158576794664126</v>
+        <v>0.1520727439010073</v>
       </c>
       <c r="H13">
-        <v>0.7596366597052966</v>
+        <v>0.7592246612147905</v>
       </c>
       <c r="I13">
-        <v>0.05550176946161853</v>
+        <v>0.05328076449870083</v>
       </c>
       <c r="J13">
-        <v>0.7415795730217256</v>
+        <v>0.7597809619879478</v>
       </c>
       <c r="K13">
-        <v>0.05442132136665763</v>
+        <v>0.05768937258565341</v>
       </c>
       <c r="L13">
-        <v>0.2518854168942823</v>
+        <v>0.2533822973340614</v>
       </c>
       <c r="M13">
-        <v>0.02303882422572827</v>
+        <v>0.02233134164523593</v>
       </c>
       <c r="N13">
-        <v>0.4957067588384166</v>
+        <v>0.5040290711017317</v>
       </c>
       <c r="O13">
-        <v>0.0384418760006444</v>
+        <v>0.03612856873116038</v>
       </c>
       <c r="P13">
-        <v>0.2532355061325826</v>
+        <v>0.2535177222764243</v>
       </c>
       <c r="Q13">
-        <v>0.02502909919430259</v>
+        <v>0.01927549764928673</v>
       </c>
       <c r="R13">
-        <v>0.7596366597052966</v>
+        <v>0.7592246612147905</v>
       </c>
       <c r="S13">
-        <v>0.05550176946161853</v>
+        <v>0.05328076449870083</v>
       </c>
       <c r="T13">
-        <v>0.5177255640845507</v>
+        <v>0.5332222589507275</v>
       </c>
       <c r="U13">
-        <v>0.04091577914927617</v>
+        <v>0.04557621063381766</v>
       </c>
       <c r="V13">
-        <v>0.1114267663795013</v>
+        <v>0.1123391360133082</v>
       </c>
       <c r="W13">
-        <v>0.0107148479271449</v>
+        <v>0.01142468203676117</v>
       </c>
       <c r="X13">
-        <v>0.1124272425576737</v>
+        <v>0.1142195670239121</v>
       </c>
       <c r="Y13">
-        <v>0.0141665915831577</v>
+        <v>0.01151420267934259</v>
       </c>
       <c r="Z13">
-        <v>0.2518854168942823</v>
+        <v>0.2533822973340614</v>
       </c>
       <c r="AA13">
-        <v>0.02303882422572827</v>
+        <v>0.02233134164523593</v>
       </c>
       <c r="AB13">
-        <v>0.4957067588384166</v>
+        <v>0.5040290711017317</v>
       </c>
       <c r="AC13">
-        <v>0.0384418760006444</v>
+        <v>0.03612856873116038</v>
       </c>
       <c r="AD13">
-        <v>24.77010441214048</v>
+        <v>24.69461403891093</v>
       </c>
       <c r="AE13">
-        <v>1.134343656537446</v>
+        <v>1.05129662415143</v>
       </c>
     </row>
     <row r="14" spans="1:31">
@@ -5310,94 +5310,94 @@
         <v>2032</v>
       </c>
       <c r="B14">
-        <v>108.8945978523869</v>
+        <v>110.9178339764738</v>
       </c>
       <c r="C14">
-        <v>5.486443721008545</v>
+        <v>5.401220712484889</v>
       </c>
       <c r="D14">
-        <v>54.61388932534805</v>
+        <v>55.60861733096337</v>
       </c>
       <c r="E14">
-        <v>3.55681132794463</v>
+        <v>2.991928559305624</v>
       </c>
       <c r="F14">
-        <v>54.28070852703883</v>
+        <v>55.30921664551046</v>
       </c>
       <c r="G14">
-        <v>3.023335094827607</v>
+        <v>3.623408980509161</v>
       </c>
       <c r="H14">
-        <v>16.19748663512407</v>
+        <v>16.68749143970151</v>
       </c>
       <c r="I14">
-        <v>1.066421802495912</v>
+        <v>1.323158926481071</v>
       </c>
       <c r="J14">
-        <v>16.31275156394348</v>
+        <v>16.63681107599711</v>
       </c>
       <c r="K14">
-        <v>1.033137036081139</v>
+        <v>1.224178271732787</v>
       </c>
       <c r="L14">
-        <v>5.471908413386766</v>
+        <v>5.470780271043788</v>
       </c>
       <c r="M14">
-        <v>0.5002676378574867</v>
+        <v>0.493850276501604</v>
       </c>
       <c r="N14">
-        <v>10.86919406525164</v>
+        <v>11.08771529183974</v>
       </c>
       <c r="O14">
-        <v>0.7631495141572844</v>
+        <v>0.8499455516965474</v>
       </c>
       <c r="P14">
-        <v>5.429367849332878</v>
+        <v>5.426418566928302</v>
       </c>
       <c r="Q14">
-        <v>0.4965650860185318</v>
+        <v>0.4693840671395986</v>
       </c>
       <c r="R14">
-        <v>16.19748663512407</v>
+        <v>16.68749143970151</v>
       </c>
       <c r="S14">
-        <v>1.066421802495912</v>
+        <v>1.323158926481071</v>
       </c>
       <c r="T14">
-        <v>11.38832483379432</v>
+        <v>11.69306140412173</v>
       </c>
       <c r="U14">
-        <v>0.869066432132623</v>
+        <v>1.033676132793627</v>
       </c>
       <c r="V14">
-        <v>2.488967277320244</v>
+        <v>2.482689129129677</v>
       </c>
       <c r="W14">
-        <v>0.2253689059864823</v>
+        <v>0.2637258170757748</v>
       </c>
       <c r="X14">
-        <v>2.435459452828916</v>
+        <v>2.46106054274569</v>
       </c>
       <c r="Y14">
-        <v>0.2378165329115204</v>
+        <v>0.2640679722236727</v>
       </c>
       <c r="Z14">
-        <v>5.471908413386766</v>
+        <v>5.470780271043788</v>
       </c>
       <c r="AA14">
-        <v>0.5002676378574867</v>
+        <v>0.493850276501604</v>
       </c>
       <c r="AB14">
-        <v>10.86919406525164</v>
+        <v>11.08771529183974</v>
       </c>
       <c r="AC14">
-        <v>0.7631495141572844</v>
+        <v>0.8499455516965474</v>
       </c>
       <c r="AD14">
-        <v>9.636244132684487</v>
+        <v>9.60559855233476</v>
       </c>
       <c r="AE14">
-        <v>0.8403565304243213</v>
+        <v>0.8994416898651936</v>
       </c>
     </row>
     <row r="15" spans="1:31">
@@ -5405,94 +5405,94 @@
         <v>2033</v>
       </c>
       <c r="B15">
-        <v>115.2276053223648</v>
+        <v>115.1877856463926</v>
       </c>
       <c r="C15">
-        <v>5.950913196551721</v>
+        <v>5.289855100063174</v>
       </c>
       <c r="D15">
-        <v>57.70835169746343</v>
+        <v>58.03138237413513</v>
       </c>
       <c r="E15">
-        <v>3.03327306737529</v>
+        <v>3.417283946677877</v>
       </c>
       <c r="F15">
-        <v>57.51925362490137</v>
+        <v>57.15640327225742</v>
       </c>
       <c r="G15">
-        <v>3.776472326109317</v>
+        <v>3.321066813527721</v>
       </c>
       <c r="H15">
-        <v>17.07812554744611</v>
+        <v>17.02147141387436</v>
       </c>
       <c r="I15">
-        <v>1.145740404285225</v>
+        <v>1.160321541693116</v>
       </c>
       <c r="J15">
-        <v>17.33402857623943</v>
+        <v>17.17670250412552</v>
       </c>
       <c r="K15">
-        <v>1.358733111345778</v>
+        <v>1.25385120873871</v>
       </c>
       <c r="L15">
-        <v>5.836008386525083</v>
+        <v>5.711110344740043</v>
       </c>
       <c r="M15">
-        <v>0.5726760377121558</v>
+        <v>0.4399553717626132</v>
       </c>
       <c r="N15">
-        <v>11.45412924122571</v>
+        <v>11.48748869509247</v>
       </c>
       <c r="O15">
-        <v>1.042727985648523</v>
+        <v>0.8709188131690128</v>
       </c>
       <c r="P15">
-        <v>5.816961873465037</v>
+        <v>5.759630314425035</v>
       </c>
       <c r="Q15">
-        <v>0.5103953710973063</v>
+        <v>0.4301287068192056</v>
       </c>
       <c r="R15">
-        <v>17.07812554744611</v>
+        <v>17.02147141387436</v>
       </c>
       <c r="S15">
-        <v>1.145740404285225</v>
+        <v>1.160321541693116</v>
       </c>
       <c r="T15">
-        <v>12.13138484586523</v>
+        <v>11.95744262641431</v>
       </c>
       <c r="U15">
-        <v>1.025109145798196</v>
+        <v>0.9145062903286971</v>
       </c>
       <c r="V15">
-        <v>2.607947817412902</v>
+        <v>2.606223014254564</v>
       </c>
       <c r="W15">
-        <v>0.3079220637891067</v>
+        <v>0.2984902353379048</v>
       </c>
       <c r="X15">
-        <v>2.594695912961299</v>
+        <v>2.613036863456645</v>
       </c>
       <c r="Y15">
-        <v>0.2938952839513732</v>
+        <v>0.2902851014099179</v>
       </c>
       <c r="Z15">
-        <v>5.836008386525083</v>
+        <v>5.711110344740043</v>
       </c>
       <c r="AA15">
-        <v>0.5726760377121558</v>
+        <v>0.4399553717626132</v>
       </c>
       <c r="AB15">
-        <v>11.45412924122571</v>
+        <v>11.48748869509247</v>
       </c>
       <c r="AC15">
-        <v>1.042727985648523</v>
+        <v>0.8709188131690128</v>
       </c>
       <c r="AD15">
-        <v>21.35404435493049</v>
+        <v>21.88898523029462</v>
       </c>
       <c r="AE15">
-        <v>1.056338940331217</v>
+        <v>1.478051895809845</v>
       </c>
     </row>
     <row r="16" spans="1:31">
@@ -5500,94 +5500,94 @@
         <v>2034</v>
       </c>
       <c r="B16">
-        <v>119.525315350423</v>
+        <v>122.025480975533</v>
       </c>
       <c r="C16">
-        <v>6.341866247963319</v>
+        <v>6.152010326103419</v>
       </c>
       <c r="D16">
-        <v>60.59413585314783</v>
+        <v>60.97121655145308</v>
       </c>
       <c r="E16">
-        <v>3.64567695935763</v>
+        <v>3.983107678364416</v>
       </c>
       <c r="F16">
-        <v>58.93117949727523</v>
+        <v>61.05426442407994</v>
       </c>
       <c r="G16">
-        <v>3.683269102803629</v>
+        <v>3.625418166328167</v>
       </c>
       <c r="H16">
-        <v>17.68203759953254</v>
+        <v>18.2419947147597</v>
       </c>
       <c r="I16">
-        <v>1.210491913240147</v>
+        <v>1.438337209433062</v>
       </c>
       <c r="J16">
-        <v>17.69331581335859</v>
+        <v>18.3036583450084</v>
       </c>
       <c r="K16">
-        <v>1.488477296703509</v>
+        <v>1.183439539699172</v>
       </c>
       <c r="L16">
-        <v>5.902300389519151</v>
+        <v>6.132537749849072</v>
       </c>
       <c r="M16">
-        <v>0.5247597275483888</v>
+        <v>0.5325337876042112</v>
       </c>
       <c r="N16">
-        <v>11.82369597497599</v>
+        <v>12.16536364736068</v>
       </c>
       <c r="O16">
-        <v>0.8371129651663353</v>
+        <v>0.8711794185207589</v>
       </c>
       <c r="P16">
-        <v>5.829829719888949</v>
+        <v>6.210709967102081</v>
       </c>
       <c r="Q16">
-        <v>0.4487976328858077</v>
+        <v>0.5287810067454886</v>
       </c>
       <c r="R16">
-        <v>17.68203759953254</v>
+        <v>18.2419947147597</v>
       </c>
       <c r="S16">
-        <v>1.210491913240147</v>
+        <v>1.438337209433062</v>
       </c>
       <c r="T16">
-        <v>12.37642998580819</v>
+        <v>12.86837476120751</v>
       </c>
       <c r="U16">
-        <v>1.146211295379303</v>
+        <v>0.8908117117014677</v>
       </c>
       <c r="V16">
-        <v>2.667299057990749</v>
+        <v>2.740627581564403</v>
       </c>
       <c r="W16">
-        <v>0.3197802160407173</v>
+        <v>0.3023422221271012</v>
       </c>
       <c r="X16">
-        <v>2.649586769559653</v>
+        <v>2.694656002236501</v>
       </c>
       <c r="Y16">
-        <v>0.3116585625189456</v>
+        <v>0.3058796881401592</v>
       </c>
       <c r="Z16">
-        <v>5.902300389519151</v>
+        <v>6.132537749849072</v>
       </c>
       <c r="AA16">
-        <v>0.5247597275483888</v>
+        <v>0.5325337876042112</v>
       </c>
       <c r="AB16">
-        <v>11.82369597497599</v>
+        <v>12.16536364736068</v>
       </c>
       <c r="AC16">
-        <v>0.8371129651663353</v>
+        <v>0.8711794185207589</v>
       </c>
       <c r="AD16">
-        <v>26.28136179859146</v>
+        <v>26.31046133501425</v>
       </c>
       <c r="AE16">
-        <v>1.26625716955997</v>
+        <v>1.378957846987393</v>
       </c>
     </row>
     <row r="17" spans="1:31">
@@ -5595,94 +5595,94 @@
         <v>2035</v>
       </c>
       <c r="B17">
-        <v>124.8467785100477</v>
+        <v>124.8445067301145</v>
       </c>
       <c r="C17">
-        <v>5.387063913470782</v>
+        <v>6.279277255262588</v>
       </c>
       <c r="D17">
-        <v>62.34629623956686</v>
+        <v>62.28352474032938</v>
       </c>
       <c r="E17">
-        <v>3.389225800036392</v>
+        <v>3.322006115780427</v>
       </c>
       <c r="F17">
-        <v>62.50048227048083</v>
+        <v>62.56098198978508</v>
       </c>
       <c r="G17">
-        <v>3.829274790756971</v>
+        <v>4.117312294621188</v>
       </c>
       <c r="H17">
-        <v>18.96787917100703</v>
+        <v>18.8307590826936</v>
       </c>
       <c r="I17">
-        <v>1.365846639359742</v>
+        <v>1.622275117766364</v>
       </c>
       <c r="J17">
-        <v>18.67836163377644</v>
+        <v>18.72004497963149</v>
       </c>
       <c r="K17">
-        <v>1.425483016147012</v>
+        <v>1.370209498062934</v>
       </c>
       <c r="L17">
-        <v>6.208974410742561</v>
+        <v>6.188691110004747</v>
       </c>
       <c r="M17">
-        <v>0.4980283967701086</v>
+        <v>0.5907256342848827</v>
       </c>
       <c r="N17">
-        <v>12.42424857798092</v>
+        <v>12.53238896469883</v>
       </c>
       <c r="O17">
-        <v>0.9259788029891967</v>
+        <v>1.004166740793158</v>
       </c>
       <c r="P17">
-        <v>6.221018476973866</v>
+        <v>6.289097852756404</v>
       </c>
       <c r="Q17">
-        <v>0.6118553339773527</v>
+        <v>0.6438808749410359</v>
       </c>
       <c r="R17">
-        <v>18.96787917100703</v>
+        <v>18.8307590826936</v>
       </c>
       <c r="S17">
-        <v>1.365846639359742</v>
+        <v>1.622275117766364</v>
       </c>
       <c r="T17">
-        <v>13.06851123812248</v>
+        <v>13.17644017675353</v>
       </c>
       <c r="U17">
-        <v>1.054508935269745</v>
+        <v>1.103013250212525</v>
       </c>
       <c r="V17">
-        <v>2.783641807698909</v>
+        <v>2.743690316435498</v>
       </c>
       <c r="W17">
-        <v>0.3317547570811415</v>
+        <v>0.3690960893504699</v>
       </c>
       <c r="X17">
-        <v>2.82620858795506</v>
+        <v>2.799914486442463</v>
       </c>
       <c r="Y17">
-        <v>0.3359021360652148</v>
+        <v>0.3284302808704931</v>
       </c>
       <c r="Z17">
-        <v>6.208974410742561</v>
+        <v>6.188691110004747</v>
       </c>
       <c r="AA17">
-        <v>0.4980283967701086</v>
+        <v>0.5907256342848827</v>
       </c>
       <c r="AB17">
-        <v>12.42424857798092</v>
+        <v>12.53238896469883</v>
       </c>
       <c r="AC17">
-        <v>0.9259788029891967</v>
+        <v>1.004166740793158</v>
       </c>
       <c r="AD17">
-        <v>28.66069954198206</v>
+        <v>29.33435593745356</v>
       </c>
       <c r="AE17">
-        <v>1.381818955101963</v>
+        <v>1.421023086650693</v>
       </c>
     </row>
     <row r="18" spans="1:31">
@@ -5690,94 +5690,94 @@
         <v>2036</v>
       </c>
       <c r="B18">
-        <v>129.8456555818816</v>
+        <v>129.3963362209523</v>
       </c>
       <c r="C18">
-        <v>7.421724308938145</v>
+        <v>6.054262708239057</v>
       </c>
       <c r="D18">
-        <v>64.97696354430258</v>
+        <v>64.81059226773804</v>
       </c>
       <c r="E18">
-        <v>4.522666147531498</v>
+        <v>3.73970204495098</v>
       </c>
       <c r="F18">
-        <v>64.868692037579</v>
+        <v>64.58574395321429</v>
       </c>
       <c r="G18">
-        <v>4.055416558434745</v>
+        <v>4.000356701187898</v>
       </c>
       <c r="H18">
-        <v>19.34889361359264</v>
+        <v>19.51166260062699</v>
       </c>
       <c r="I18">
-        <v>1.486803210049731</v>
+        <v>1.423438125321671</v>
       </c>
       <c r="J18">
-        <v>19.42812072948646</v>
+        <v>19.37874462522888</v>
       </c>
       <c r="K18">
-        <v>1.474702064200804</v>
+        <v>1.367245752951439</v>
       </c>
       <c r="L18">
-        <v>6.473640939545785</v>
+        <v>6.484432932561573</v>
       </c>
       <c r="M18">
-        <v>0.5756625500856003</v>
+        <v>0.5809457077157002</v>
       </c>
       <c r="N18">
-        <v>13.09285726948059</v>
+        <v>12.74267854495926</v>
       </c>
       <c r="O18">
-        <v>0.9106740387387529</v>
+        <v>0.8539211424085852</v>
       </c>
       <c r="P18">
-        <v>6.525179485473545</v>
+        <v>6.468225249837579</v>
       </c>
       <c r="Q18">
-        <v>0.6008785195124396</v>
+        <v>0.5918973880283589</v>
       </c>
       <c r="R18">
-        <v>19.34889361359264</v>
+        <v>19.51166260062699</v>
       </c>
       <c r="S18">
-        <v>1.486803210049731</v>
+        <v>1.423438125321671</v>
       </c>
       <c r="T18">
-        <v>13.54507262076005</v>
+        <v>13.6265336444259</v>
       </c>
       <c r="U18">
-        <v>1.158780303292815</v>
+        <v>1.133212470269705</v>
       </c>
       <c r="V18">
-        <v>2.95600625396453</v>
+        <v>2.85884534675406</v>
       </c>
       <c r="W18">
-        <v>0.3556241383114043</v>
+        <v>0.2883275588469095</v>
       </c>
       <c r="X18">
-        <v>2.927041854761871</v>
+        <v>2.893365634048918</v>
       </c>
       <c r="Y18">
-        <v>0.3266798266281889</v>
+        <v>0.2729934636410205</v>
       </c>
       <c r="Z18">
-        <v>6.473640939545785</v>
+        <v>6.484432932561573</v>
       </c>
       <c r="AA18">
-        <v>0.5756625500856003</v>
+        <v>0.5809457077157002</v>
       </c>
       <c r="AB18">
-        <v>13.09285726948059</v>
+        <v>12.74267854495926</v>
       </c>
       <c r="AC18">
-        <v>0.9106740387387529</v>
+        <v>0.8539211424085852</v>
       </c>
       <c r="AD18">
-        <v>30.80132938749169</v>
+        <v>30.99646291182011</v>
       </c>
       <c r="AE18">
-        <v>1.492468402434688</v>
+        <v>1.410994189303072</v>
       </c>
     </row>
     <row r="19" spans="1:31">
@@ -5785,94 +5785,94 @@
         <v>2037</v>
       </c>
       <c r="B19">
-        <v>133.6315862893624</v>
+        <v>135.2270933913799</v>
       </c>
       <c r="C19">
-        <v>7.309829009149282</v>
+        <v>6.57908773878568</v>
       </c>
       <c r="D19">
-        <v>66.66550133085474</v>
+        <v>67.51898995574371</v>
       </c>
       <c r="E19">
-        <v>4.474557492046713</v>
+        <v>4.183966170984545</v>
       </c>
       <c r="F19">
-        <v>66.96608495850759</v>
+        <v>67.70810343563622</v>
       </c>
       <c r="G19">
-        <v>4.309312388907045</v>
+        <v>4.703491308376162</v>
       </c>
       <c r="H19">
-        <v>20.206483699169</v>
+        <v>20.55063971994376</v>
       </c>
       <c r="I19">
-        <v>1.612010998945121</v>
+        <v>1.624906647044885</v>
       </c>
       <c r="J19">
-        <v>20.18490372557429</v>
+        <v>20.11322545398282</v>
       </c>
       <c r="K19">
-        <v>1.731354454488202</v>
+        <v>1.692017718292406</v>
       </c>
       <c r="L19">
-        <v>6.614976079943837</v>
+        <v>6.758870412299561</v>
       </c>
       <c r="M19">
-        <v>0.6262386980270339</v>
+        <v>0.6659729840002754</v>
       </c>
       <c r="N19">
-        <v>13.27670635545043</v>
+        <v>13.60893520957135</v>
       </c>
       <c r="O19">
-        <v>0.9516826965879958</v>
+        <v>1.004370330535445</v>
       </c>
       <c r="P19">
-        <v>6.683015098370034</v>
+        <v>6.676432639838722</v>
       </c>
       <c r="Q19">
-        <v>0.4852461349431368</v>
+        <v>0.6603651759771947</v>
       </c>
       <c r="R19">
-        <v>20.206483699169</v>
+        <v>20.55063971994376</v>
       </c>
       <c r="S19">
-        <v>1.612010998945121</v>
+        <v>1.624906647044885</v>
       </c>
       <c r="T19">
-        <v>14.05299836375852</v>
+        <v>13.99744355597358</v>
       </c>
       <c r="U19">
-        <v>1.241789809440645</v>
+        <v>1.373997902300041</v>
       </c>
       <c r="V19">
-        <v>3.059300321470742</v>
+        <v>3.071601730779327</v>
       </c>
       <c r="W19">
-        <v>0.3807767003956389</v>
+        <v>0.3473585448953688</v>
       </c>
       <c r="X19">
-        <v>3.072605040345029</v>
+        <v>3.044180167229915</v>
       </c>
       <c r="Y19">
-        <v>0.3625083255067754</v>
+        <v>0.3421902528566375</v>
       </c>
       <c r="Z19">
-        <v>6.614976079943837</v>
+        <v>6.758870412299561</v>
       </c>
       <c r="AA19">
-        <v>0.6262386980270339</v>
+        <v>0.6659729840002754</v>
       </c>
       <c r="AB19">
-        <v>13.27670635545043</v>
+        <v>13.60893520957135</v>
       </c>
       <c r="AC19">
-        <v>0.9516826965879958</v>
+        <v>1.004370330535445</v>
       </c>
       <c r="AD19">
-        <v>32.1114711158643</v>
+        <v>32.34738383504492</v>
       </c>
       <c r="AE19">
-        <v>1.586697590581737</v>
+        <v>1.460338983119478</v>
       </c>
     </row>
     <row r="20" spans="1:31">
@@ -5880,94 +5880,94 @@
         <v>2038</v>
       </c>
       <c r="B20">
-        <v>139.9198337620148</v>
+        <v>139.5382284064632</v>
       </c>
       <c r="C20">
-        <v>6.792866796915363</v>
+        <v>6.025231796033881</v>
       </c>
       <c r="D20">
-        <v>70.25897728758328</v>
+        <v>69.09879068618861</v>
       </c>
       <c r="E20">
-        <v>4.796714109142961</v>
+        <v>3.809540151740219</v>
       </c>
       <c r="F20">
-        <v>69.66085647443154</v>
+        <v>70.43943772027463</v>
       </c>
       <c r="G20">
-        <v>3.855469135934479</v>
+        <v>3.893043060861943</v>
       </c>
       <c r="H20">
-        <v>20.93807319596776</v>
+        <v>21.27363710562902</v>
       </c>
       <c r="I20">
-        <v>1.420620298552668</v>
+        <v>1.453947078265124</v>
       </c>
       <c r="J20">
-        <v>21.00410544100226</v>
+        <v>21.04073599302389</v>
       </c>
       <c r="K20">
-        <v>1.35653909318722</v>
+        <v>1.324781117726469</v>
       </c>
       <c r="L20">
-        <v>6.853928406813221</v>
+        <v>7.029787089900319</v>
       </c>
       <c r="M20">
-        <v>0.6918275100891028</v>
+        <v>0.5715421002209852</v>
       </c>
       <c r="N20">
-        <v>13.95322761352638</v>
+        <v>14.04228541530751</v>
       </c>
       <c r="O20">
-        <v>0.9709227651063269</v>
+        <v>1.085440030540354</v>
       </c>
       <c r="P20">
-        <v>6.911521817121931</v>
+        <v>7.052992116413869</v>
       </c>
       <c r="Q20">
-        <v>0.6545884466046961</v>
+        <v>0.5516203789120813</v>
       </c>
       <c r="R20">
-        <v>20.93807319596776</v>
+        <v>21.27363710562902</v>
       </c>
       <c r="S20">
-        <v>1.420620298552668</v>
+        <v>1.453947078265124</v>
       </c>
       <c r="T20">
-        <v>14.67886142602912</v>
+        <v>14.82266657408241</v>
       </c>
       <c r="U20">
-        <v>1.040463820746219</v>
+        <v>1.106317277240517</v>
       </c>
       <c r="V20">
-        <v>3.168430878558727</v>
+        <v>3.106165351652931</v>
       </c>
       <c r="W20">
-        <v>0.3597452266627261</v>
+        <v>0.320116613656072</v>
       </c>
       <c r="X20">
-        <v>3.156813136414413</v>
+        <v>3.111904067288543</v>
       </c>
       <c r="Y20">
-        <v>0.3388605286829787</v>
+        <v>0.3080904010403683</v>
       </c>
       <c r="Z20">
-        <v>6.853928406813221</v>
+        <v>7.029787089900319</v>
       </c>
       <c r="AA20">
-        <v>0.6918275100891028</v>
+        <v>0.5715421002209852</v>
       </c>
       <c r="AB20">
-        <v>13.95322761352638</v>
+        <v>14.04228541530751</v>
       </c>
       <c r="AC20">
-        <v>0.9709227651063269</v>
+        <v>1.085440030540354</v>
       </c>
       <c r="AD20">
-        <v>33.47266392190529</v>
+        <v>33.75126330880285</v>
       </c>
       <c r="AE20">
-        <v>1.767156864419818</v>
+        <v>1.765698967897193</v>
       </c>
     </row>
     <row r="21" spans="1:31">
@@ -5975,94 +5975,94 @@
         <v>2039</v>
       </c>
       <c r="B21">
-        <v>144.1950076340099</v>
+        <v>146.2824655931328</v>
       </c>
       <c r="C21">
-        <v>9.088156132107665</v>
+        <v>7.372205087771479</v>
       </c>
       <c r="D21">
-        <v>72.11686628040013</v>
+        <v>73.14347124857392</v>
       </c>
       <c r="E21">
-        <v>5.375929011230484</v>
+        <v>4.534704115088528</v>
       </c>
       <c r="F21">
-        <v>72.07814135360975</v>
+        <v>73.13899434455894</v>
       </c>
       <c r="G21">
-        <v>5.221392837656436</v>
+        <v>4.773787209169798</v>
       </c>
       <c r="H21">
-        <v>21.48712660000849</v>
+        <v>21.85959623069977</v>
       </c>
       <c r="I21">
-        <v>1.894327262716648</v>
+        <v>1.812068037356565</v>
       </c>
       <c r="J21">
-        <v>21.59075588428399</v>
+        <v>21.83805958843362</v>
       </c>
       <c r="K21">
-        <v>1.707689616405746</v>
+        <v>1.636035230037175</v>
       </c>
       <c r="L21">
-        <v>7.328498253362774</v>
+        <v>7.374855011365423</v>
       </c>
       <c r="M21">
-        <v>0.7270408256098997</v>
+        <v>0.6117474697996507</v>
       </c>
       <c r="N21">
-        <v>14.45880202822606</v>
+        <v>14.78729650801519</v>
       </c>
       <c r="O21">
-        <v>1.366373221736296</v>
+        <v>1.166246846642087</v>
       </c>
       <c r="P21">
-        <v>7.212958587728428</v>
+        <v>7.279187006044944</v>
       </c>
       <c r="Q21">
-        <v>0.6746588708901174</v>
+        <v>0.6244584334785095</v>
       </c>
       <c r="R21">
-        <v>21.48712660000849</v>
+        <v>21.85959623069977</v>
       </c>
       <c r="S21">
-        <v>1.894327262716648</v>
+        <v>1.812068037356565</v>
       </c>
       <c r="T21">
-        <v>15.10726325510366</v>
+        <v>15.18357195296129</v>
       </c>
       <c r="U21">
-        <v>1.39990355711588</v>
+        <v>1.287971701652551</v>
       </c>
       <c r="V21">
-        <v>3.245246497677166</v>
+        <v>3.329240420027364</v>
       </c>
       <c r="W21">
-        <v>0.3764392730526144</v>
+        <v>0.3071318116150806</v>
       </c>
       <c r="X21">
-        <v>3.238246131503166</v>
+        <v>3.325247215444961</v>
       </c>
       <c r="Y21">
-        <v>0.3755698910833398</v>
+        <v>0.3735031043351929</v>
       </c>
       <c r="Z21">
-        <v>7.328498253362774</v>
+        <v>7.374855011365423</v>
       </c>
       <c r="AA21">
-        <v>0.7270408256098997</v>
+        <v>0.6117474697996507</v>
       </c>
       <c r="AB21">
-        <v>14.45880202822606</v>
+        <v>14.78729650801519</v>
       </c>
       <c r="AC21">
-        <v>1.366373221736296</v>
+        <v>1.166246846642087</v>
       </c>
       <c r="AD21">
-        <v>34.84934155448439</v>
+        <v>35.26513542598485</v>
       </c>
       <c r="AE21">
-        <v>1.558374448772369</v>
+        <v>1.39913276977437</v>
       </c>
     </row>
     <row r="22" spans="1:31">
@@ -6070,94 +6070,94 @@
         <v>2040</v>
       </c>
       <c r="B22">
-        <v>149.0854072357391</v>
+        <v>151.3868022622216</v>
       </c>
       <c r="C22">
-        <v>7.538872662458288</v>
+        <v>7.56263811731498</v>
       </c>
       <c r="D22">
-        <v>73.78692225142612</v>
+        <v>75.60309571168665</v>
       </c>
       <c r="E22">
-        <v>4.610673252253872</v>
+        <v>4.70356354834256</v>
       </c>
       <c r="F22">
-        <v>75.29848498431296</v>
+        <v>75.78370655053493</v>
       </c>
       <c r="G22">
-        <v>4.672333035244393</v>
+        <v>4.413796057221927</v>
       </c>
       <c r="H22">
-        <v>22.55574344660516</v>
+        <v>22.75001889846906</v>
       </c>
       <c r="I22">
-        <v>1.793148131430177</v>
+        <v>1.500719122497374</v>
       </c>
       <c r="J22">
-        <v>22.50354001626601</v>
+        <v>22.58611775110939</v>
       </c>
       <c r="K22">
-        <v>1.717126532837474</v>
+        <v>1.714511090034928</v>
       </c>
       <c r="L22">
-        <v>7.610605911612124</v>
+        <v>7.628609962977174</v>
       </c>
       <c r="M22">
-        <v>0.5486833799733757</v>
+        <v>0.5919402327046179</v>
       </c>
       <c r="N22">
-        <v>15.16492612887253</v>
+        <v>15.12594056499614</v>
       </c>
       <c r="O22">
-        <v>1.270124344695937</v>
+        <v>1.112107509518935</v>
       </c>
       <c r="P22">
-        <v>7.463669480957143</v>
+        <v>7.693019372983148</v>
       </c>
       <c r="Q22">
-        <v>0.6256049088259888</v>
+        <v>0.724323545836035</v>
       </c>
       <c r="R22">
-        <v>22.55574344660516</v>
+        <v>22.75001889846906</v>
       </c>
       <c r="S22">
-        <v>1.793148131430177</v>
+        <v>1.500719122497374</v>
       </c>
       <c r="T22">
-        <v>15.82750202336664</v>
+        <v>15.89264968265675</v>
       </c>
       <c r="U22">
-        <v>1.226116296305393</v>
+        <v>1.369472733816881</v>
       </c>
       <c r="V22">
-        <v>3.358266002334761</v>
+        <v>3.360611114895775</v>
       </c>
       <c r="W22">
-        <v>0.4051478894702281</v>
+        <v>0.3529234533740993</v>
       </c>
       <c r="X22">
-        <v>3.317771990564613</v>
+        <v>3.332856953556867</v>
       </c>
       <c r="Y22">
-        <v>0.4098642837762938</v>
+        <v>0.3380754313748723</v>
       </c>
       <c r="Z22">
-        <v>7.610605911612124</v>
+        <v>7.628609962977174</v>
       </c>
       <c r="AA22">
-        <v>0.5486833799733757</v>
+        <v>0.5919402327046179</v>
       </c>
       <c r="AB22">
-        <v>15.16492612887253</v>
+        <v>15.12594056499614</v>
       </c>
       <c r="AC22">
-        <v>1.270124344695937</v>
+        <v>1.112107509518935</v>
       </c>
       <c r="AD22">
-        <v>35.9622227058607</v>
+        <v>36.40703505016783</v>
       </c>
       <c r="AE22">
-        <v>2.002671071566923</v>
+        <v>1.809521333674022</v>
       </c>
     </row>
   </sheetData>
@@ -6240,64 +6240,64 @@
         <v>2020</v>
       </c>
       <c r="B2">
-        <v>25.24457228895476</v>
+        <v>24.93369522757344</v>
       </c>
       <c r="C2">
-        <v>1.292897462832222</v>
+        <v>1.590028788623875</v>
       </c>
       <c r="D2">
-        <v>25.24457228895476</v>
+        <v>24.93369522757344</v>
       </c>
       <c r="E2">
-        <v>1.292897462832222</v>
+        <v>1.590028788623875</v>
       </c>
       <c r="F2">
-        <v>2.484871516158154</v>
+        <v>2.491942122795375</v>
       </c>
       <c r="G2">
-        <v>0.2097810819799739</v>
+        <v>0.1899998456736323</v>
       </c>
       <c r="H2">
-        <v>2.484871516158154</v>
+        <v>2.491942122795375</v>
       </c>
       <c r="I2">
-        <v>0.2097810819799739</v>
+        <v>0.1899998456736323</v>
       </c>
       <c r="J2">
-        <v>12.65902960445379</v>
+        <v>12.73283269514515</v>
       </c>
       <c r="K2">
-        <v>0.9036777241148544</v>
+        <v>0.9278519377298627</v>
       </c>
       <c r="L2">
-        <v>12.65902960445379</v>
+        <v>12.73283269514515</v>
       </c>
       <c r="M2">
-        <v>0.9036777241148544</v>
+        <v>0.9278519377298627</v>
       </c>
       <c r="N2">
-        <v>8.600170882560404</v>
+        <v>8.56962792607181</v>
       </c>
       <c r="O2">
-        <v>0.6127156752418262</v>
+        <v>0.592871009928847</v>
       </c>
       <c r="P2">
-        <v>8.600170882560404</v>
+        <v>8.56962792607181</v>
       </c>
       <c r="Q2">
-        <v>0.6127156752418262</v>
+        <v>0.592871009928847</v>
       </c>
       <c r="R2">
-        <v>1.168452305346305</v>
+        <v>1.13636657460469</v>
       </c>
       <c r="S2">
-        <v>0.114166934431957</v>
+        <v>0.1179270492316192</v>
       </c>
       <c r="T2">
-        <v>1.168452305346305</v>
+        <v>1.13636657460469</v>
       </c>
       <c r="U2">
-        <v>0.114166934431957</v>
+        <v>0.1179270492316192</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -6305,64 +6305,64 @@
         <v>2021</v>
       </c>
       <c r="B3">
-        <v>27.25683682824483</v>
+        <v>27.92612905479805</v>
       </c>
       <c r="C3">
-        <v>1.694331535370261</v>
+        <v>1.787898130014453</v>
       </c>
       <c r="D3">
-        <v>52.50140911719959</v>
+        <v>52.85982428237151</v>
       </c>
       <c r="E3">
-        <v>2.137426836779183</v>
+        <v>2.367065321341603</v>
       </c>
       <c r="F3">
-        <v>2.723422159344876</v>
+        <v>2.676220490347101</v>
       </c>
       <c r="G3">
-        <v>0.2450846217271386</v>
+        <v>0.2088956814597114</v>
       </c>
       <c r="H3">
-        <v>5.20829367550303</v>
+        <v>5.168162613142478</v>
       </c>
       <c r="I3">
-        <v>0.3433263798282535</v>
+        <v>0.3067426230157618</v>
       </c>
       <c r="J3">
-        <v>5.798670812734977</v>
+        <v>5.96656126996985</v>
       </c>
       <c r="K3">
-        <v>1.183380027709805</v>
+        <v>1.287516860031949</v>
       </c>
       <c r="L3">
-        <v>18.45770041718877</v>
+        <v>18.69939396511499</v>
       </c>
       <c r="M3">
-        <v>1.073054149109127</v>
+        <v>1.08192546192595</v>
       </c>
       <c r="N3">
-        <v>17.56019440240843</v>
+        <v>17.59357622682309</v>
       </c>
       <c r="O3">
-        <v>1.047111425868614</v>
+        <v>1.0629427103336</v>
       </c>
       <c r="P3">
-        <v>26.16036528496883</v>
+        <v>26.16320415289491</v>
       </c>
       <c r="Q3">
-        <v>1.488984270479633</v>
+        <v>1.400346741800231</v>
       </c>
       <c r="R3">
-        <v>1.235874756408689</v>
+        <v>1.213117141625872</v>
       </c>
       <c r="S3">
-        <v>0.1321268927049191</v>
+        <v>0.1528961677706777</v>
       </c>
       <c r="T3">
-        <v>2.404327061754993</v>
+        <v>2.349483716230563</v>
       </c>
       <c r="U3">
-        <v>0.1921453479923979</v>
+        <v>0.1916166430470466</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -6370,64 +6370,64 @@
         <v>2022</v>
       </c>
       <c r="B4">
-        <v>30.03334825807666</v>
+        <v>29.61222656201005</v>
       </c>
       <c r="C4">
-        <v>1.948460192300637</v>
+        <v>2.150513417462997</v>
       </c>
       <c r="D4">
-        <v>82.53475737527624</v>
+        <v>82.47205084438156</v>
       </c>
       <c r="E4">
-        <v>2.978717555729351</v>
+        <v>3.271027182527804</v>
       </c>
       <c r="F4">
-        <v>3.006887947509259</v>
+        <v>3.018136154226663</v>
       </c>
       <c r="G4">
-        <v>0.2389280696980747</v>
+        <v>0.217434079800197</v>
       </c>
       <c r="H4">
-        <v>8.21518162301229</v>
+        <v>8.186298767369138</v>
       </c>
       <c r="I4">
-        <v>0.481818146979107</v>
+        <v>0.3536785029163119</v>
       </c>
       <c r="J4">
-        <v>3.392310520067643</v>
+        <v>3.21366858303265</v>
       </c>
       <c r="K4">
-        <v>1.197680223287449</v>
+        <v>1.268690561202157</v>
       </c>
       <c r="L4">
-        <v>21.85001093725641</v>
+        <v>21.91306254814764</v>
       </c>
       <c r="M4">
-        <v>1.357304790758269</v>
+        <v>1.269244495810864</v>
       </c>
       <c r="N4">
-        <v>22.17712826451774</v>
+        <v>22.15395125560236</v>
       </c>
       <c r="O4">
-        <v>1.136403777944439</v>
+        <v>0.9938663479577045</v>
       </c>
       <c r="P4">
-        <v>48.33749354948657</v>
+        <v>48.31715540849726</v>
       </c>
       <c r="Q4">
-        <v>2.310013604497542</v>
+        <v>2.106078445318095</v>
       </c>
       <c r="R4">
-        <v>1.369950946552552</v>
+        <v>1.316826622002215</v>
       </c>
       <c r="S4">
-        <v>0.1225055319518751</v>
+        <v>0.1279129817570687</v>
       </c>
       <c r="T4">
-        <v>3.774278008307546</v>
+        <v>3.666310338232777</v>
       </c>
       <c r="U4">
-        <v>0.250247048862179</v>
+        <v>0.1805390216304069</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -6435,64 +6435,64 @@
         <v>2023</v>
       </c>
       <c r="B5">
-        <v>32.85914439918344</v>
+        <v>32.86430365325857</v>
       </c>
       <c r="C5">
-        <v>2.117106146119645</v>
+        <v>1.748522882642226</v>
       </c>
       <c r="D5">
-        <v>115.3939017744597</v>
+        <v>115.3363544976401</v>
       </c>
       <c r="E5">
-        <v>3.853754562162668</v>
+        <v>3.705551852604059</v>
       </c>
       <c r="F5">
-        <v>3.270148964915929</v>
+        <v>3.22415294038328</v>
       </c>
       <c r="G5">
-        <v>0.2989070823864001</v>
+        <v>0.3063726819111079</v>
       </c>
       <c r="H5">
-        <v>11.48533058792822</v>
+        <v>11.41045170775242</v>
       </c>
       <c r="I5">
-        <v>0.6342903803349277</v>
+        <v>0.4300972407827036</v>
       </c>
       <c r="J5">
-        <v>2.589276847743114</v>
+        <v>2.693002457397076</v>
       </c>
       <c r="K5">
-        <v>1.41790394267414</v>
+        <v>1.632618357722674</v>
       </c>
       <c r="L5">
-        <v>24.43928778499951</v>
+        <v>24.60606500554473</v>
       </c>
       <c r="M5">
-        <v>1.553603729856215</v>
+        <v>1.963440346474424</v>
       </c>
       <c r="N5">
-        <v>25.11105233792843</v>
+        <v>25.14643873089473</v>
       </c>
       <c r="O5">
-        <v>1.117311953352604</v>
+        <v>0.8849793304987514</v>
       </c>
       <c r="P5">
-        <v>73.44854588741504</v>
+        <v>73.46359413939199</v>
       </c>
       <c r="Q5">
-        <v>3.078154208284171</v>
+        <v>2.401144272783458</v>
       </c>
       <c r="R5">
-        <v>1.466138368796604</v>
+        <v>1.449383179009512</v>
       </c>
       <c r="S5">
-        <v>0.1321272348826124</v>
+        <v>0.1438978069184357</v>
       </c>
       <c r="T5">
-        <v>5.240416377104151</v>
+        <v>5.115693517242289</v>
       </c>
       <c r="U5">
-        <v>0.2786315563742572</v>
+        <v>0.2158032911877994</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -6500,64 +6500,64 @@
         <v>2024</v>
       </c>
       <c r="B6">
-        <v>35.16400611814424</v>
+        <v>34.59721590316347</v>
       </c>
       <c r="C6">
-        <v>2.508619216375895</v>
+        <v>2.077633478016621</v>
       </c>
       <c r="D6">
-        <v>150.5579078926039</v>
+        <v>149.9335704008037</v>
       </c>
       <c r="E6">
-        <v>4.350836892430388</v>
+        <v>4.399226950024668</v>
       </c>
       <c r="F6">
-        <v>3.513370745836997</v>
+        <v>3.353917233575354</v>
       </c>
       <c r="G6">
-        <v>0.3112305609813006</v>
+        <v>0.2989452746843664</v>
       </c>
       <c r="H6">
-        <v>14.99870133376521</v>
+        <v>14.76436894132778</v>
       </c>
       <c r="I6">
-        <v>0.7137001008290718</v>
+        <v>0.5462520303298477</v>
       </c>
       <c r="J6">
-        <v>2.331345011026452</v>
+        <v>1.749306011693355</v>
       </c>
       <c r="K6">
-        <v>1.393117223040397</v>
+        <v>1.341501913322641</v>
       </c>
       <c r="L6">
-        <v>26.77063279602598</v>
+        <v>26.35537101723807</v>
       </c>
       <c r="M6">
-        <v>1.6588593612711</v>
+        <v>2.015478704563612</v>
       </c>
       <c r="N6">
-        <v>27.64726563319951</v>
+        <v>27.37504176722278</v>
       </c>
       <c r="O6">
-        <v>1.021096865480792</v>
+        <v>1.207291684922913</v>
       </c>
       <c r="P6">
-        <v>101.0958115206145</v>
+        <v>100.8386359066147</v>
       </c>
       <c r="Q6">
-        <v>3.636067991203257</v>
+        <v>2.879398203402223</v>
       </c>
       <c r="R6">
-        <v>1.566243108164528</v>
+        <v>1.555514184750827</v>
       </c>
       <c r="S6">
-        <v>0.1712629689624998</v>
+        <v>0.1573442342470988</v>
       </c>
       <c r="T6">
-        <v>6.806659485268675</v>
+        <v>6.671207701993115</v>
       </c>
       <c r="U6">
-        <v>0.3248192131494401</v>
+        <v>0.2962683450376763</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -6565,64 +6565,64 @@
         <v>2025</v>
       </c>
       <c r="B7">
-        <v>38.18852699382029</v>
+        <v>37.79767415513756</v>
       </c>
       <c r="C7">
-        <v>2.057279295579067</v>
+        <v>2.187334068987437</v>
       </c>
       <c r="D7">
-        <v>188.7464348864242</v>
+        <v>187.7312445559411</v>
       </c>
       <c r="E7">
-        <v>4.263798288179835</v>
+        <v>4.517669666540544</v>
       </c>
       <c r="F7">
-        <v>3.856350193621868</v>
+        <v>3.72350867552538</v>
       </c>
       <c r="G7">
-        <v>0.341385204407016</v>
+        <v>0.3205270362669346</v>
       </c>
       <c r="H7">
-        <v>18.85505152738708</v>
+        <v>18.48787761685316</v>
       </c>
       <c r="I7">
-        <v>0.7278201291612036</v>
+        <v>0.6292043807971599</v>
       </c>
       <c r="J7">
-        <v>2.300984470201051</v>
+        <v>2.398421292265052</v>
       </c>
       <c r="K7">
-        <v>1.27032106223554</v>
+        <v>1.273864739291117</v>
       </c>
       <c r="L7">
-        <v>29.07161726622702</v>
+        <v>28.75379230950312</v>
       </c>
       <c r="M7">
-        <v>1.673015554005384</v>
+        <v>1.976185843685793</v>
       </c>
       <c r="N7">
-        <v>30.11605336420187</v>
+        <v>29.69519778141469</v>
       </c>
       <c r="O7">
-        <v>1.260094323425523</v>
+        <v>1.187250590814606</v>
       </c>
       <c r="P7">
-        <v>131.2118648848164</v>
+        <v>130.5338336880295</v>
       </c>
       <c r="Q7">
-        <v>4.252444730329182</v>
+        <v>3.395972218128291</v>
       </c>
       <c r="R7">
-        <v>1.700046466242333</v>
+        <v>1.708715579005971</v>
       </c>
       <c r="S7">
-        <v>0.1932168817230498</v>
+        <v>0.194027726949354</v>
       </c>
       <c r="T7">
-        <v>8.506705951511011</v>
+        <v>8.379923280999089</v>
       </c>
       <c r="U7">
-        <v>0.3294757657681614</v>
+        <v>0.4080412229093355</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -6630,64 +6630,64 @@
         <v>2026</v>
       </c>
       <c r="B8">
-        <v>39.93354781927816</v>
+        <v>39.95680617240585</v>
       </c>
       <c r="C8">
-        <v>2.336288837900946</v>
+        <v>2.418027437595694</v>
       </c>
       <c r="D8">
-        <v>228.6799827057023</v>
+        <v>227.6880507283469</v>
       </c>
       <c r="E8">
-        <v>5.269964830073368</v>
+        <v>5.173798919849612</v>
       </c>
       <c r="F8">
-        <v>4.008532857385351</v>
+        <v>3.928974108546273</v>
       </c>
       <c r="G8">
-        <v>0.308942617972202</v>
+        <v>0.2636642645666054</v>
       </c>
       <c r="H8">
-        <v>22.86358438477243</v>
+        <v>22.41685172539943</v>
       </c>
       <c r="I8">
-        <v>0.8143232171988247</v>
+        <v>0.7153996893522249</v>
       </c>
       <c r="J8">
-        <v>2.01798149174912</v>
+        <v>2.188735640796153</v>
       </c>
       <c r="K8">
-        <v>1.447416680069343</v>
+        <v>1.371007883197509</v>
       </c>
       <c r="L8">
-        <v>31.08959875797614</v>
+        <v>30.94252795029929</v>
       </c>
       <c r="M8">
-        <v>1.83606869759148</v>
+        <v>2.134906501498125</v>
       </c>
       <c r="N8">
-        <v>32.26105918200535</v>
+        <v>31.98550059757269</v>
       </c>
       <c r="O8">
-        <v>1.305648083240188</v>
+        <v>1.109066553143443</v>
       </c>
       <c r="P8">
-        <v>163.4729240668217</v>
+        <v>162.5193342856022</v>
       </c>
       <c r="Q8">
-        <v>4.8930846237492</v>
+        <v>3.780244942849549</v>
       </c>
       <c r="R8">
-        <v>1.849308421133686</v>
+        <v>1.817135747166626</v>
       </c>
       <c r="S8">
-        <v>0.1766462304681818</v>
+        <v>0.2188167620735024</v>
       </c>
       <c r="T8">
-        <v>10.3560143726447</v>
+        <v>10.19705902816572</v>
       </c>
       <c r="U8">
-        <v>0.3636654606755941</v>
+        <v>0.4396672205498469</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -6695,64 +6695,64 @@
         <v>2027</v>
       </c>
       <c r="B9">
-        <v>42.23744549290257</v>
+        <v>42.30586736373884</v>
       </c>
       <c r="C9">
-        <v>2.121935275849374</v>
+        <v>2.954051275819456</v>
       </c>
       <c r="D9">
-        <v>270.9174281986049</v>
+        <v>269.9939180920858</v>
       </c>
       <c r="E9">
-        <v>5.818093958805822</v>
+        <v>5.320975578247422</v>
       </c>
       <c r="F9">
-        <v>4.201902678710495</v>
+        <v>4.292574207704114</v>
       </c>
       <c r="G9">
-        <v>0.3705299609679102</v>
+        <v>0.4587471135393274</v>
       </c>
       <c r="H9">
-        <v>27.06548706348293</v>
+        <v>26.70942593310354</v>
       </c>
       <c r="I9">
-        <v>0.9715334219775682</v>
+        <v>0.8146028897904473</v>
       </c>
       <c r="J9">
-        <v>1.856486625065263</v>
+        <v>2.025500211886428</v>
       </c>
       <c r="K9">
-        <v>1.821937480836472</v>
+        <v>2.091420535263929</v>
       </c>
       <c r="L9">
-        <v>32.94608538304142</v>
+        <v>32.9680281621857</v>
       </c>
       <c r="M9">
-        <v>2.177532727728843</v>
+        <v>2.24915589284132</v>
       </c>
       <c r="N9">
-        <v>34.289637027758</v>
+        <v>34.32709742996489</v>
       </c>
       <c r="O9">
-        <v>1.308287338770345</v>
+        <v>1.366150161722689</v>
       </c>
       <c r="P9">
-        <v>197.7625610945797</v>
+        <v>196.8464317155671</v>
       </c>
       <c r="Q9">
-        <v>5.477195729934168</v>
+        <v>4.228045907553543</v>
       </c>
       <c r="R9">
-        <v>1.941672124587264</v>
+        <v>1.917073610595181</v>
       </c>
       <c r="S9">
-        <v>0.2274952249894093</v>
+        <v>0.2179776473161518</v>
       </c>
       <c r="T9">
-        <v>12.29768649723196</v>
+        <v>12.1141326387609</v>
       </c>
       <c r="U9">
-        <v>0.4442235432170952</v>
+        <v>0.4665339909622283</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -6760,64 +6760,64 @@
         <v>2028</v>
       </c>
       <c r="B10">
-        <v>44.92700299847004</v>
+        <v>44.69817609096683</v>
       </c>
       <c r="C10">
-        <v>2.688700176913707</v>
+        <v>2.794568904378915</v>
       </c>
       <c r="D10">
-        <v>315.844431197075</v>
+        <v>314.6920941830527</v>
       </c>
       <c r="E10">
-        <v>6.237018415632991</v>
+        <v>5.868136121882362</v>
       </c>
       <c r="F10">
-        <v>4.547438298664695</v>
+        <v>4.531032441280297</v>
       </c>
       <c r="G10">
-        <v>0.3468465818112295</v>
+        <v>0.3526194668556297</v>
       </c>
       <c r="H10">
-        <v>31.61292536214762</v>
+        <v>31.24045837438384</v>
       </c>
       <c r="I10">
-        <v>1.080167684580152</v>
+        <v>0.8898177838589132</v>
       </c>
       <c r="J10">
-        <v>2.247479605964027</v>
+        <v>2.076483203247268</v>
       </c>
       <c r="K10">
-        <v>1.951357431763098</v>
+        <v>1.475243214828834</v>
       </c>
       <c r="L10">
-        <v>35.19356498900544</v>
+        <v>35.04451136543296</v>
       </c>
       <c r="M10">
-        <v>2.156079949423262</v>
+        <v>2.326883968819653</v>
       </c>
       <c r="N10">
-        <v>36.48976212303654</v>
+        <v>36.356227538099</v>
       </c>
       <c r="O10">
-        <v>1.235850215823681</v>
+        <v>1.515922279942779</v>
       </c>
       <c r="P10">
-        <v>234.2523232176162</v>
+        <v>233.2026592536661</v>
       </c>
       <c r="Q10">
-        <v>5.999560886789039</v>
+        <v>4.852782066915324</v>
       </c>
       <c r="R10">
-        <v>2.018769256552894</v>
+        <v>1.959171404099167</v>
       </c>
       <c r="S10">
-        <v>0.2023385714083736</v>
+        <v>0.253048887290182</v>
       </c>
       <c r="T10">
-        <v>14.31645575378486</v>
+        <v>14.07330404286007</v>
       </c>
       <c r="U10">
-        <v>0.4889984974859284</v>
+        <v>0.5264506355814648</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -6825,64 +6825,64 @@
         <v>2029</v>
       </c>
       <c r="B11">
-        <v>47.18696589869393</v>
+        <v>46.71362166309305</v>
       </c>
       <c r="C11">
-        <v>3.226150977677583</v>
+        <v>2.356507191209092</v>
       </c>
       <c r="D11">
-        <v>363.0313970957687</v>
+        <v>361.4057158461458</v>
       </c>
       <c r="E11">
-        <v>6.735047338091514</v>
+        <v>6.653034150619689</v>
       </c>
       <c r="F11">
-        <v>4.833322150836089</v>
+        <v>4.782091574275732</v>
       </c>
       <c r="G11">
-        <v>0.4891600201634535</v>
+        <v>0.373369628950974</v>
       </c>
       <c r="H11">
-        <v>36.44624751298371</v>
+        <v>36.02254994865957</v>
       </c>
       <c r="I11">
-        <v>1.09556463792634</v>
+        <v>0.9660031126392159</v>
       </c>
       <c r="J11">
-        <v>1.861100518237636</v>
+        <v>1.992742058113251</v>
       </c>
       <c r="K11">
-        <v>2.121876001201401</v>
+        <v>1.872274072058833</v>
       </c>
       <c r="L11">
-        <v>37.05466550724307</v>
+        <v>37.03725342354621</v>
       </c>
       <c r="M11">
-        <v>2.526239935748113</v>
+        <v>2.597312106331659</v>
       </c>
       <c r="N11">
-        <v>38.97126808815541</v>
+        <v>38.69315427391881</v>
       </c>
       <c r="O11">
-        <v>1.553986320949175</v>
+        <v>1.430227030087739</v>
       </c>
       <c r="P11">
-        <v>273.2235913057717</v>
+        <v>271.8958135275849</v>
       </c>
       <c r="Q11">
-        <v>6.508320366763047</v>
+        <v>5.605404741953973</v>
       </c>
       <c r="R11">
-        <v>2.165725253485271</v>
+        <v>2.132674896589536</v>
       </c>
       <c r="S11">
-        <v>0.2373158726812129</v>
+        <v>0.2476314137520236</v>
       </c>
       <c r="T11">
-        <v>16.48218100727012</v>
+        <v>16.2059789394496</v>
       </c>
       <c r="U11">
-        <v>0.5657258298233565</v>
+        <v>0.5231375154715626</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -6890,64 +6890,64 @@
         <v>2030</v>
       </c>
       <c r="B12">
-        <v>49.4927125039103</v>
+        <v>49.88904369521111</v>
       </c>
       <c r="C12">
-        <v>3.154942025807223</v>
+        <v>3.154512556188495</v>
       </c>
       <c r="D12">
-        <v>412.5241095996792</v>
+        <v>411.2947595413568</v>
       </c>
       <c r="E12">
-        <v>7.769755967285789</v>
+        <v>6.780158395882254</v>
       </c>
       <c r="F12">
-        <v>5.024295456140931</v>
+        <v>4.918758556843729</v>
       </c>
       <c r="G12">
-        <v>0.4228737567025853</v>
+        <v>0.4474645897169992</v>
       </c>
       <c r="H12">
-        <v>41.47054296912463</v>
+        <v>40.9413085055033</v>
       </c>
       <c r="I12">
-        <v>1.12856630102679</v>
+        <v>0.9826000857408677</v>
       </c>
       <c r="J12">
-        <v>1.913764553386256</v>
+        <v>1.825162684436606</v>
       </c>
       <c r="K12">
-        <v>1.804144444674681</v>
+        <v>1.998925062944983</v>
       </c>
       <c r="L12">
-        <v>38.96843006062931</v>
+        <v>38.86241610798282</v>
       </c>
       <c r="M12">
-        <v>2.679458459930493</v>
+        <v>2.761927407603656</v>
       </c>
       <c r="N12">
-        <v>40.79069880939264</v>
+        <v>40.48258363355112</v>
       </c>
       <c r="O12">
-        <v>1.580284403500426</v>
+        <v>1.547096005853698</v>
       </c>
       <c r="P12">
-        <v>314.0142901151644</v>
+        <v>312.378397161136</v>
       </c>
       <c r="Q12">
-        <v>6.564889246538141</v>
+        <v>5.767196767010084</v>
       </c>
       <c r="R12">
-        <v>2.200881515886955</v>
+        <v>2.161571024386381</v>
       </c>
       <c r="S12">
-        <v>0.2175809994576081</v>
+        <v>0.2674766228741145</v>
       </c>
       <c r="T12">
-        <v>18.68306252315708</v>
+        <v>18.36754996383598</v>
       </c>
       <c r="U12">
-        <v>0.6219643092382943</v>
+        <v>0.5794073547011325</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -6955,64 +6955,64 @@
         <v>2031</v>
       </c>
       <c r="B13">
-        <v>2.509172638871949</v>
+        <v>2.516449050367034</v>
       </c>
       <c r="C13">
-        <v>0.1381153215691751</v>
+        <v>0.1594675911934764</v>
       </c>
       <c r="D13">
-        <v>415.0332822385511</v>
+        <v>413.8112085917239</v>
       </c>
       <c r="E13">
-        <v>7.788108815971229</v>
+        <v>6.76587723660972</v>
       </c>
       <c r="F13">
-        <v>0.2532355061325826</v>
+        <v>0.2535177222764243</v>
       </c>
       <c r="G13">
-        <v>0.02502909919430259</v>
+        <v>0.01927549764928673</v>
       </c>
       <c r="H13">
-        <v>41.72377847525724</v>
+        <v>41.19482622777972</v>
       </c>
       <c r="I13">
-        <v>1.130184878902656</v>
+        <v>0.985151147954003</v>
       </c>
       <c r="J13">
-        <v>-23.49274218835064</v>
+        <v>-23.40216711874541</v>
       </c>
       <c r="K13">
-        <v>1.151917632073774</v>
+        <v>1.041134092410104</v>
       </c>
       <c r="L13">
-        <v>15.47568787227868</v>
+        <v>15.46024898923742</v>
       </c>
       <c r="M13">
-        <v>2.133958826608299</v>
+        <v>2.4066954876355</v>
       </c>
       <c r="N13">
-        <v>25.62912335425268</v>
+        <v>25.56436454336002</v>
       </c>
       <c r="O13">
-        <v>1.134171941615763</v>
+        <v>1.068086390408266</v>
       </c>
       <c r="P13">
-        <v>339.643413469417</v>
+        <v>337.9427617044959</v>
       </c>
       <c r="Q13">
-        <v>6.614785233415631</v>
+        <v>6.056635567881816</v>
       </c>
       <c r="R13">
-        <v>0.1124272425576737</v>
+        <v>0.1142195670239121</v>
       </c>
       <c r="S13">
-        <v>0.0141665915831577</v>
+        <v>0.01151420267934259</v>
       </c>
       <c r="T13">
-        <v>18.79548976571475</v>
+        <v>18.48176953085989</v>
       </c>
       <c r="U13">
-        <v>0.6221532454039098</v>
+        <v>0.5790047964437615</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -7020,64 +7020,64 @@
         <v>2032</v>
       </c>
       <c r="B14">
-        <v>54.61388932534805</v>
+        <v>55.60861733096337</v>
       </c>
       <c r="C14">
-        <v>3.55681132794463</v>
+        <v>2.991928559305624</v>
       </c>
       <c r="D14">
-        <v>469.6471715638992</v>
+        <v>469.4198259226872</v>
       </c>
       <c r="E14">
-        <v>8.574419556604461</v>
+        <v>7.826111290373449</v>
       </c>
       <c r="F14">
-        <v>5.429367849332878</v>
+        <v>5.426418566928302</v>
       </c>
       <c r="G14">
-        <v>0.4965650860185318</v>
+        <v>0.4693840671395986</v>
       </c>
       <c r="H14">
-        <v>47.15314632459012</v>
+        <v>46.62124479470801</v>
       </c>
       <c r="I14">
-        <v>1.245894341862282</v>
+        <v>1.082045905470891</v>
       </c>
       <c r="J14">
-        <v>17.9495673362339</v>
+        <v>18.77495429148849</v>
       </c>
       <c r="K14">
-        <v>1.6879472040412</v>
+        <v>2.318984823225424</v>
       </c>
       <c r="L14">
-        <v>33.42525520851259</v>
+        <v>34.23520328072592</v>
       </c>
       <c r="M14">
-        <v>2.331640435186754</v>
+        <v>2.554507128110833</v>
       </c>
       <c r="N14">
-        <v>28.46631388864314</v>
+        <v>28.64678324434797</v>
       </c>
       <c r="O14">
-        <v>1.475696887960477</v>
+        <v>1.629103070229647</v>
       </c>
       <c r="P14">
-        <v>368.1097273580602</v>
+        <v>366.589544948844</v>
       </c>
       <c r="Q14">
-        <v>6.601400383958803</v>
+        <v>5.798604822675242</v>
       </c>
       <c r="R14">
-        <v>2.435459452828916</v>
+        <v>2.46106054274569</v>
       </c>
       <c r="S14">
-        <v>0.2378165329115204</v>
+        <v>0.2640679722236727</v>
       </c>
       <c r="T14">
-        <v>21.23094921854367</v>
+        <v>20.94283007360558</v>
       </c>
       <c r="U14">
-        <v>0.6692395718977807</v>
+        <v>0.6093012770889895</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -7085,64 +7085,64 @@
         <v>2033</v>
       </c>
       <c r="B15">
-        <v>57.70835169746343</v>
+        <v>58.03138237413513</v>
       </c>
       <c r="C15">
-        <v>3.03327306737529</v>
+        <v>3.417283946677877</v>
       </c>
       <c r="D15">
-        <v>527.3555232613627</v>
+        <v>527.4512082968224</v>
       </c>
       <c r="E15">
-        <v>9.26308415965218</v>
+        <v>8.938536371617136</v>
       </c>
       <c r="F15">
-        <v>5.816961873465037</v>
+        <v>5.759630314425035</v>
       </c>
       <c r="G15">
-        <v>0.5103953710973063</v>
+        <v>0.4301287068192056</v>
       </c>
       <c r="H15">
-        <v>52.97010819805515</v>
+        <v>52.38087510913306</v>
       </c>
       <c r="I15">
-        <v>1.274134742558203</v>
+        <v>1.128235627221035</v>
       </c>
       <c r="J15">
-        <v>7.855466038380841</v>
+        <v>7.089928809994053</v>
       </c>
       <c r="K15">
-        <v>2.110636477826218</v>
+        <v>2.167612811839302</v>
       </c>
       <c r="L15">
-        <v>41.28072124689343</v>
+        <v>41.32513209071995</v>
       </c>
       <c r="M15">
-        <v>2.925462985952767</v>
+        <v>2.905459727660625</v>
       </c>
       <c r="N15">
-        <v>41.25212980009419</v>
+        <v>41.69380728438168</v>
       </c>
       <c r="O15">
-        <v>1.959430747416879</v>
+        <v>1.981152364138368</v>
       </c>
       <c r="P15">
-        <v>409.3618571581545</v>
+        <v>408.2833522332257</v>
       </c>
       <c r="Q15">
-        <v>7.126330574841709</v>
+        <v>6.426086457169534</v>
       </c>
       <c r="R15">
-        <v>2.594695912961299</v>
+        <v>2.613036863456645</v>
       </c>
       <c r="S15">
-        <v>0.2938952839513732</v>
+        <v>0.2902851014099179</v>
       </c>
       <c r="T15">
-        <v>23.82564513150497</v>
+        <v>23.55586693706223</v>
       </c>
       <c r="U15">
-        <v>0.7638321875652028</v>
+        <v>0.7191552164879529</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -7150,64 +7150,64 @@
         <v>2034</v>
       </c>
       <c r="B16">
-        <v>60.59413585314783</v>
+        <v>60.97121655145308</v>
       </c>
       <c r="C16">
-        <v>3.64567695935763</v>
+        <v>3.983107678364416</v>
       </c>
       <c r="D16">
-        <v>587.9496591145104</v>
+        <v>588.4224248482757</v>
       </c>
       <c r="E16">
-        <v>10.20758415433445</v>
+        <v>10.20624250835343</v>
       </c>
       <c r="F16">
-        <v>5.829829719888949</v>
+        <v>6.210709967102081</v>
       </c>
       <c r="G16">
-        <v>0.4487976328858077</v>
+        <v>0.5287810067454886</v>
       </c>
       <c r="H16">
-        <v>58.7999379179441</v>
+        <v>58.59158507623513</v>
       </c>
       <c r="I16">
-        <v>1.293874768745314</v>
+        <v>1.273797629732938</v>
       </c>
       <c r="J16">
-        <v>3.777105786749266</v>
+        <v>4.799908140952938</v>
       </c>
       <c r="K16">
-        <v>2.572353863091811</v>
+        <v>2.386517842493487</v>
       </c>
       <c r="L16">
-        <v>45.0578270336427</v>
+        <v>46.1250402316729</v>
       </c>
       <c r="M16">
-        <v>2.975657777584393</v>
+        <v>3.305541205442448</v>
       </c>
       <c r="N16">
-        <v>46.67465722107734</v>
+        <v>47.34899031378843</v>
       </c>
       <c r="O16">
-        <v>1.829859765562761</v>
+        <v>2.102894598777572</v>
       </c>
       <c r="P16">
-        <v>456.0365143792317</v>
+        <v>455.6323425470138</v>
       </c>
       <c r="Q16">
-        <v>7.511164942811011</v>
+        <v>7.486964110202122</v>
       </c>
       <c r="R16">
-        <v>2.649586769559653</v>
+        <v>2.694656002236501</v>
       </c>
       <c r="S16">
-        <v>0.3116585625189456</v>
+        <v>0.3058796881401592</v>
       </c>
       <c r="T16">
-        <v>26.47523190106463</v>
+        <v>26.25052293929873</v>
       </c>
       <c r="U16">
-        <v>0.8056857930953938</v>
+        <v>0.741053549045572</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -7215,64 +7215,64 @@
         <v>2035</v>
       </c>
       <c r="B17">
-        <v>62.34629623956686</v>
+        <v>62.28352474032938</v>
       </c>
       <c r="C17">
-        <v>3.389225800036392</v>
+        <v>3.322006115780427</v>
       </c>
       <c r="D17">
-        <v>650.2959553540773</v>
+        <v>650.7059495886047</v>
       </c>
       <c r="E17">
-        <v>10.80055541159546</v>
+        <v>10.79172747353362</v>
       </c>
       <c r="F17">
-        <v>6.221018476973866</v>
+        <v>6.289097852756404</v>
       </c>
       <c r="G17">
-        <v>0.6118553339773527</v>
+        <v>0.6438808749410359</v>
       </c>
       <c r="H17">
-        <v>65.02095639491795</v>
+        <v>64.88068292899155</v>
       </c>
       <c r="I17">
-        <v>1.415780563776691</v>
+        <v>1.371564551354937</v>
       </c>
       <c r="J17">
-        <v>3.375690867147451</v>
+        <v>2.67284332199358</v>
       </c>
       <c r="K17">
-        <v>2.388085014489334</v>
+        <v>3.113404202389501</v>
       </c>
       <c r="L17">
-        <v>48.43351790079015</v>
+        <v>48.79788355366649</v>
       </c>
       <c r="M17">
-        <v>3.216277618926057</v>
+        <v>3.878703829831859</v>
       </c>
       <c r="N17">
-        <v>50.07756433840444</v>
+        <v>50.79912632859264</v>
       </c>
       <c r="O17">
-        <v>1.95958584284104</v>
+        <v>1.900308488656943</v>
       </c>
       <c r="P17">
-        <v>506.114078717636</v>
+        <v>506.4314688756068</v>
       </c>
       <c r="Q17">
-        <v>7.949050558076616</v>
+        <v>8.101621582285716</v>
       </c>
       <c r="R17">
-        <v>2.82620858795506</v>
+        <v>2.799914486442463</v>
       </c>
       <c r="S17">
-        <v>0.3359021360652148</v>
+        <v>0.3284302808704931</v>
       </c>
       <c r="T17">
-        <v>29.30144048901967</v>
+        <v>29.0504374257412</v>
       </c>
       <c r="U17">
-        <v>0.8589584377112051</v>
+        <v>0.7672146620953973</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -7280,64 +7280,64 @@
         <v>2036</v>
       </c>
       <c r="B18">
-        <v>64.97696354430258</v>
+        <v>64.81059226773804</v>
       </c>
       <c r="C18">
-        <v>4.522666147531498</v>
+        <v>3.73970204495098</v>
       </c>
       <c r="D18">
-        <v>715.2729188983801</v>
+        <v>715.5165418563428</v>
       </c>
       <c r="E18">
-        <v>12.93107657026719</v>
+        <v>12.18779726167716</v>
       </c>
       <c r="F18">
-        <v>6.525179485473545</v>
+        <v>6.468225249837579</v>
       </c>
       <c r="G18">
-        <v>0.6008785195124396</v>
+        <v>0.5918973880283589</v>
       </c>
       <c r="H18">
-        <v>71.54613588039149</v>
+        <v>71.34890817882912</v>
       </c>
       <c r="I18">
-        <v>1.536610492041193</v>
+        <v>1.492522640178811</v>
       </c>
       <c r="J18">
-        <v>2.092636846860996</v>
+        <v>2.141733333232775</v>
       </c>
       <c r="K18">
-        <v>2.885445766551347</v>
+        <v>2.728525610434126</v>
       </c>
       <c r="L18">
-        <v>50.52615474765116</v>
+        <v>50.93961688689927</v>
       </c>
       <c r="M18">
-        <v>3.641777397779502</v>
+        <v>4.144714823115647</v>
       </c>
       <c r="N18">
-        <v>53.32383385048259</v>
+        <v>53.08241973609501</v>
       </c>
       <c r="O18">
-        <v>2.115960451861295</v>
+        <v>1.918086846436759</v>
       </c>
       <c r="P18">
-        <v>559.4379125681186</v>
+        <v>559.5138886117019</v>
       </c>
       <c r="Q18">
-        <v>8.985878492849272</v>
+        <v>8.224405683864267</v>
       </c>
       <c r="R18">
-        <v>2.927041854761871</v>
+        <v>2.893365634048918</v>
       </c>
       <c r="S18">
-        <v>0.3266798266281889</v>
+        <v>0.2729934636410205</v>
       </c>
       <c r="T18">
-        <v>32.22848234378155</v>
+        <v>31.94380305979012</v>
       </c>
       <c r="U18">
-        <v>0.9383782340451418</v>
+        <v>0.8000969757969962</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -7345,64 +7345,64 @@
         <v>2037</v>
       </c>
       <c r="B19">
-        <v>66.66550133085474</v>
+        <v>67.51898995574371</v>
       </c>
       <c r="C19">
-        <v>4.474557492046713</v>
+        <v>4.183966170984545</v>
       </c>
       <c r="D19">
-        <v>781.9384202292343</v>
+        <v>783.0355318120866</v>
       </c>
       <c r="E19">
-        <v>12.99229139462749</v>
+        <v>12.66683847912759</v>
       </c>
       <c r="F19">
-        <v>6.683015098370034</v>
+        <v>6.676432639838722</v>
       </c>
       <c r="G19">
-        <v>0.4852461349431368</v>
+        <v>0.6603651759771947</v>
       </c>
       <c r="H19">
-        <v>78.22915097876152</v>
+        <v>78.02534081866786</v>
       </c>
       <c r="I19">
-        <v>1.531552128318842</v>
+        <v>1.565733027658497</v>
       </c>
       <c r="J19">
-        <v>2.148010947063213</v>
+        <v>2.200699440872402</v>
       </c>
       <c r="K19">
-        <v>3.007678438825952</v>
+        <v>3.143199580432587</v>
       </c>
       <c r="L19">
-        <v>52.67416569471435</v>
+        <v>53.14031632777167</v>
       </c>
       <c r="M19">
-        <v>4.028415645750123</v>
+        <v>4.35350677530796</v>
       </c>
       <c r="N19">
-        <v>55.06245387272931</v>
+        <v>55.78679118769517</v>
       </c>
       <c r="O19">
-        <v>2.344993651833193</v>
+        <v>1.956746148352347</v>
       </c>
       <c r="P19">
-        <v>614.500366440848</v>
+        <v>615.300679799397</v>
       </c>
       <c r="Q19">
-        <v>10.27319731793617</v>
+        <v>7.985519555444954</v>
       </c>
       <c r="R19">
-        <v>3.072605040345029</v>
+        <v>3.044180167229915</v>
       </c>
       <c r="S19">
-        <v>0.3625083255067754</v>
+        <v>0.3421902528566375</v>
       </c>
       <c r="T19">
-        <v>35.30108738412657</v>
+        <v>34.98798322702002</v>
       </c>
       <c r="U19">
-        <v>1.088129840816065</v>
+        <v>0.8932366818353302</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -7410,64 +7410,64 @@
         <v>2038</v>
       </c>
       <c r="B20">
-        <v>70.25897728758328</v>
+        <v>69.09879068618861</v>
       </c>
       <c r="C20">
-        <v>4.796714109142961</v>
+        <v>3.809540151740219</v>
       </c>
       <c r="D20">
-        <v>852.197397516818</v>
+        <v>852.1343224982754</v>
       </c>
       <c r="E20">
-        <v>14.29930616279333</v>
+        <v>12.78026549422087</v>
       </c>
       <c r="F20">
-        <v>6.911521817121931</v>
+        <v>7.052992116413869</v>
       </c>
       <c r="G20">
-        <v>0.6545884466046961</v>
+        <v>0.5516203789120813</v>
       </c>
       <c r="H20">
-        <v>85.14067279588343</v>
+        <v>85.0783329350817</v>
       </c>
       <c r="I20">
-        <v>1.664126510829166</v>
+        <v>1.708725571828805</v>
       </c>
       <c r="J20">
-        <v>2.144270700091563</v>
+        <v>2.34504037090859</v>
       </c>
       <c r="K20">
-        <v>2.650833145526752</v>
+        <v>2.995255858252389</v>
       </c>
       <c r="L20">
-        <v>54.81843639480592</v>
+        <v>55.48535669868024</v>
       </c>
       <c r="M20">
-        <v>3.542311739604998</v>
+        <v>3.559501614987398</v>
       </c>
       <c r="N20">
-        <v>57.44825082080364</v>
+        <v>57.92950116566362</v>
       </c>
       <c r="O20">
-        <v>2.4297111108634</v>
+        <v>2.317399247337109</v>
       </c>
       <c r="P20">
-        <v>671.9486172616519</v>
+        <v>673.2301809650604</v>
       </c>
       <c r="Q20">
-        <v>11.50376666037205</v>
+        <v>8.494717484980848</v>
       </c>
       <c r="R20">
-        <v>3.156813136414413</v>
+        <v>3.111904067288543</v>
       </c>
       <c r="S20">
-        <v>0.3388605286829787</v>
+        <v>0.3080904010403683</v>
       </c>
       <c r="T20">
-        <v>38.45790052054099</v>
+        <v>38.09988729430856</v>
       </c>
       <c r="U20">
-        <v>1.188604542038078</v>
+        <v>0.9485641171251863</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -7475,64 +7475,64 @@
         <v>2039</v>
       </c>
       <c r="B21">
-        <v>72.11686628040013</v>
+        <v>73.14347124857392</v>
       </c>
       <c r="C21">
-        <v>5.375929011230484</v>
+        <v>4.534704115088528</v>
       </c>
       <c r="D21">
-        <v>924.3142637972182</v>
+        <v>925.2777937468489</v>
       </c>
       <c r="E21">
-        <v>15.14872001704742</v>
+        <v>14.99499386263324</v>
       </c>
       <c r="F21">
-        <v>7.212958587728428</v>
+        <v>7.279187006044944</v>
       </c>
       <c r="G21">
-        <v>0.6746588708901174</v>
+        <v>0.6244584334785095</v>
       </c>
       <c r="H21">
-        <v>92.3536313836119</v>
+        <v>92.35751994112665</v>
       </c>
       <c r="I21">
-        <v>1.953030866011956</v>
+        <v>1.976361104650174</v>
       </c>
       <c r="J21">
-        <v>1.745048300627772</v>
+        <v>1.778032757676218</v>
       </c>
       <c r="K21">
-        <v>3.238669944709621</v>
+        <v>3.11823013975448</v>
       </c>
       <c r="L21">
-        <v>56.56348469543367</v>
+        <v>57.26338945635648</v>
       </c>
       <c r="M21">
-        <v>3.923107143283765</v>
+        <v>3.673178759135357</v>
       </c>
       <c r="N21">
-        <v>59.88188833375038</v>
+        <v>60.75652736539284</v>
       </c>
       <c r="O21">
-        <v>2.739736788279725</v>
+        <v>2.351943378346264</v>
       </c>
       <c r="P21">
-        <v>731.8305055954021</v>
+        <v>733.9867083304537</v>
       </c>
       <c r="Q21">
-        <v>12.7708622260959</v>
+        <v>9.288526403638327</v>
       </c>
       <c r="R21">
-        <v>3.238246131503166</v>
+        <v>3.325247215444961</v>
       </c>
       <c r="S21">
-        <v>0.3755698910833398</v>
+        <v>0.3735031043351929</v>
       </c>
       <c r="T21">
-        <v>41.69614665204416</v>
+        <v>41.42513450975352</v>
       </c>
       <c r="U21">
-        <v>1.227812277251108</v>
+        <v>1.097010995201092</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -7540,64 +7540,64 @@
         <v>2040</v>
       </c>
       <c r="B22">
-        <v>73.78692225142612</v>
+        <v>75.60309571168665</v>
       </c>
       <c r="C22">
-        <v>4.610673252253872</v>
+        <v>4.70356354834256</v>
       </c>
       <c r="D22">
-        <v>998.1011860486436</v>
+        <v>1000.880889458536</v>
       </c>
       <c r="E22">
-        <v>15.59333503377854</v>
+        <v>15.08907395305574</v>
       </c>
       <c r="F22">
-        <v>7.463669480957143</v>
+        <v>7.693019372983148</v>
       </c>
       <c r="G22">
-        <v>0.6256049088259888</v>
+        <v>0.724323545836035</v>
       </c>
       <c r="H22">
-        <v>99.81730086456905</v>
+        <v>100.0505393141098</v>
       </c>
       <c r="I22">
-        <v>1.994421218874057</v>
+        <v>2.137801545863355</v>
       </c>
       <c r="J22">
-        <v>2.421022764111095</v>
+        <v>2.235633530957987</v>
       </c>
       <c r="K22">
-        <v>3.537262510295854</v>
+        <v>3.462576681081537</v>
       </c>
       <c r="L22">
-        <v>58.98450745954476</v>
+        <v>59.49902298731444</v>
       </c>
       <c r="M22">
-        <v>4.144680873155503</v>
+        <v>4.29409162620629</v>
       </c>
       <c r="N22">
-        <v>62.0960207486801</v>
+        <v>62.5221966930369</v>
       </c>
       <c r="O22">
-        <v>2.661711440231772</v>
+        <v>2.125548396017513</v>
       </c>
       <c r="P22">
-        <v>793.9265263440823</v>
+        <v>796.5089050234903</v>
       </c>
       <c r="Q22">
-        <v>13.78999497599116</v>
+        <v>9.909244576389197</v>
       </c>
       <c r="R22">
-        <v>3.317771990564613</v>
+        <v>3.332856953556867</v>
       </c>
       <c r="S22">
-        <v>0.4098642837762938</v>
+        <v>0.3380754313748723</v>
       </c>
       <c r="T22">
-        <v>45.01391864260878</v>
+        <v>44.75799146331042</v>
       </c>
       <c r="U22">
-        <v>1.304788383796971</v>
+        <v>1.18380769213087</v>
       </c>
     </row>
   </sheetData>
